--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC48296-C1DE-4803-9434-ECAE5AB50DF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47902CD7-B101-4EFC-96D1-A686FA0B5277}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7275" yWindow="4590" windowWidth="20160" windowHeight="18585" activeTab="4" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
+    <workbookView xWindow="16335" yWindow="1500" windowWidth="28035" windowHeight="20805" activeTab="4" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
   <sheets>
     <sheet name="RSFSR" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="115">
   <si>
     <t>год</t>
   </si>
@@ -184,19 +184,211 @@
     <t>Узбек.</t>
   </si>
   <si>
-    <t xml:space="preserve">сумма </t>
-  </si>
-  <si>
     <t>Казак.</t>
   </si>
   <si>
-    <t>фактич.</t>
+    <t>Численность населения губернии в 1915 году составляла 1.9 млн. чел.</t>
   </si>
   <si>
-    <t>Новороссия включает территорию Бессарабской губернии, преобладающая правобережная часть которой в 1926 и 1939 гг. не входила в состав СССР.</t>
+    <t>Величины в полях с зелёным фоном вычислены ретропрогнозом динамики демографического перехода.</t>
   </si>
   <si>
-    <t>Численность населения губернии в 1915 году составляла 1.9 млн. чел.</t>
+    <t>Величины в полях с синим фоном представляют фактические значения по переписям населения.</t>
+  </si>
+  <si>
+    <t>https://www.demoscope.ru/weekly/pril.php</t>
+  </si>
+  <si>
+    <t>ЦСУ СССР, "Итоги Всесоюзной переписи населения 1959 года. СССР. Сводный том", М. : Госстатиздат, 1962, стр. 54</t>
+  </si>
+  <si>
+    <t>В.Б. Жиромская, Ю.А. Поляков, "Всесоюзная перепись населения 1937 года. Общие итоги. Сборник документов и материалов", М. : РОССПЭН, 2007, стр. 32, 46-47, 52-55</t>
+  </si>
+  <si>
+    <t>Источники сведений переписей:</t>
+  </si>
+  <si>
+    <t>Значения для республик в 1939 взяты без коррекции на приписки, для всего СССР -- с поправкой по В.Б. Жиромской</t>
+  </si>
+  <si>
+    <t>1970, 1979, 1989</t>
+  </si>
+  <si>
+    <t>До 1914 года в состав России и соответственно Малороссии не входили:</t>
+  </si>
+  <si>
+    <t>Почти полностью/основная часть не входила: Тернопольская (кроме северного Кременецкого уезда/части Волыни), Черновицкая (кроме Хотинского уезда/сев Бессарабии).</t>
+  </si>
+  <si>
+    <t>Численность добавочных после 1939-1945 гг. территорий, по переписям 1959-1989 гг.:</t>
+  </si>
+  <si>
+    <t>Львовская</t>
+  </si>
+  <si>
+    <t>Ивано-Франковская</t>
+  </si>
+  <si>
+    <t>Закарпатская</t>
+  </si>
+  <si>
+    <t>Тернопольская</t>
+  </si>
+  <si>
+    <t>Черновицкая</t>
+  </si>
+  <si>
+    <t>Тува</t>
+  </si>
+  <si>
+    <t>всего</t>
+  </si>
+  <si>
+    <t>Львовская, Ивано-Франковская (до 1962 года -- Станиславская), Закарпатская области</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СССР фактич. </t>
+  </si>
+  <si>
+    <t>фактическая численность населения СССР по переписям</t>
+  </si>
+  <si>
+    <t>границы таксона не включают Туву</t>
+  </si>
+  <si>
+    <t>и не входивших в состав России до 1914 года, и поэтому не входящих в состав таксонов РСФСР-1991, Новороссии, Малороссии и Белоруссии</t>
+  </si>
+  <si>
+    <t>СССР
+фактич.</t>
+  </si>
+  <si>
+    <t>подавстрийские
+земли
+и Тува</t>
+  </si>
+  <si>
+    <t>подавстрийские земли и Тува</t>
+  </si>
+  <si>
+    <t>%
+потерь</t>
+  </si>
+  <si>
+    <t>величина
+потерь</t>
+  </si>
+  <si>
+    <t>ЦСУ СССР, "Всесоюзная перепись населения 1926 года", М. 1929, т. 17 отдел 1 (Союз СССР), стр. 2</t>
+  </si>
+  <si>
+    <t>Серым цветом помечены земли не входившие на дату переписи в состав СССР.</t>
+  </si>
+  <si>
+    <t>Киргизия в 1926 году входила в состав РСФСР, но не входит в состав таксона РСФСР-1991</t>
+  </si>
+  <si>
+    <t>Казакская АССР в 1926 входила в состав РСФСР, но не входит в состав таксона РСФСР-1991</t>
+  </si>
+  <si>
+    <t>Численность населения для Киргизии и Казахстана см. ЦСУ СССР, "Всесоюзная перепись населения 1926 года", т. 9 (РСФСР), М. 1929, стр. 24</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Таджикистан в 1926 году входил в состав Узбекистана и учтён вместе с ним</t>
+  </si>
+  <si>
+    <t>Население всего СССР по переписи = 147,028 тыс. чел., но после поправок на недоучёт = 148,530</t>
+  </si>
+  <si>
+    <t>В.Б. Жиромская, “Численность населения России в 1939 г. : Поиск истины” // “Население России в 1920-1950-е годы: Численность, потери, миграции”, ИРИ РАН, М. 1994, стр. 32, 35, 38-40;</t>
+  </si>
+  <si>
+    <t>тж. В.Б. Жиромская, Ю.А. Поляков и др., “Всесоюзная перепись населения 1939 года. Основные итоги. Россия”, М. : ИРИ РАН, 1999, стр. 10-11, 15-16.</t>
+  </si>
+  <si>
+    <t>см. АДХ, "Население Советского Союза 1922-1991", М. : Наука, 1993, стр. 21</t>
+  </si>
+  <si>
+    <t>Численность населения на 2020:</t>
+  </si>
+  <si>
+    <t>Россия</t>
+  </si>
+  <si>
+    <t>Украина</t>
+  </si>
+  <si>
+    <t>включая подавстрийские земли</t>
+  </si>
+  <si>
+    <t>включая Туву</t>
+  </si>
+  <si>
+    <t xml:space="preserve">всего </t>
+  </si>
+  <si>
+    <t>для 2020 г. указана суммарная численность населения РФ (включая Туву), Украины (с подавстрийскими землями) и Белоруссии</t>
+  </si>
+  <si>
+    <t>Желтым цветом помечены земли входившие на дату переписи в административный состав других республик.</t>
+  </si>
+  <si>
+    <t>На момент переписей 1926, 1937 и 1939 гг. в состав СССР не входила почти целиком Бессарабская губерния</t>
+  </si>
+  <si>
+    <t>и частично Волынская, Гродненская и Минская губернии (западные части которых были в составе Польши).</t>
+  </si>
+  <si>
+    <t>Таксон Новороссия включает территорию Бессарабской губернии, преобладающая правобережная часть которой в 1926 и 1939 гг. не входила в состав СССР.</t>
+  </si>
+  <si>
+    <t>Таксон Малороссия включает Волынскую губернию.</t>
+  </si>
+  <si>
+    <t>Таксон Белоруссия включаяет Гродненскую и Минскую губернии.</t>
+  </si>
+  <si>
+    <t>части таксонов Новроссия, Малороссия, Белоруссия находившиеся в 1926-1939 гг. вне состава СССР</t>
+  </si>
+  <si>
+    <t>сумма 
+без
+вне СССР</t>
+  </si>
+  <si>
+    <t>фактическая численность (по переписям) территорий присоединённых в 1939-1945 гг.</t>
+  </si>
+  <si>
+    <t>сумма без вне СССР</t>
+  </si>
+  <si>
+    <t>сумма колонок от РСФСР-1991 по Эстонию минус "НР, МР, БР вне СССР"</t>
+  </si>
+  <si>
+    <t>представляет ожидаемую численность населения территории в текущих (на момент переписи) границах СССР</t>
+  </si>
+  <si>
+    <t>Оценка численность населения этих территорий на конец 1939 года = 13,000 чел. (АДХ-СССР, стр. 52)</t>
+  </si>
+  <si>
+    <t>Величины для 1937 и 1926 получаются отсюда обратной реконструкцией.</t>
+  </si>
+  <si>
+    <t>часть
+НР + МР + БР
+вне СССР</t>
+  </si>
+  <si>
+    <t>часть НР + МР + БР вне СССР</t>
+  </si>
+  <si>
+    <t>При 0.8% - 1.2% прироста величина населения на начало 1937 г. составит 12.7-12.6 млн. чел.</t>
+  </si>
+  <si>
+    <t>А на конец 1926 года - 11.7-11.1 млн. чел.</t>
   </si>
 </sst>
 </file>
@@ -208,7 +400,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,19 +431,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -265,8 +459,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -274,11 +486,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -312,23 +552,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,16 +947,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -4935,11 +5217,11 @@
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="20" t="s">
+      <c r="D126" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
+      <c r="E126" s="23"/>
+      <c r="F126" s="23"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
@@ -5310,16 +5592,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -6325,7 +6607,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>569.30922363769901</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="19">
         <f ca="1" xml:space="preserve"> NR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-14.879150185448719</v>
       </c>
@@ -6365,7 +6647,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>577.15933865391332</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="19">
         <f ca="1" xml:space="preserve"> NR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-14.879150185448719</v>
       </c>
@@ -6405,7 +6687,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>575.29094863703881</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="19">
         <f ca="1" xml:space="preserve"> NR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-14.879150185448719</v>
       </c>
@@ -9589,11 +9871,11 @@
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="20" t="s">
+      <c r="D126" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
+      <c r="E126" s="23"/>
+      <c r="F126" s="23"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
@@ -9964,16 +10246,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -10059,7 +10341,7 @@
         <f>E7*F7/1000</f>
         <v>458.06012393128867</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="19">
         <f ca="1" xml:space="preserve"> MR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-11.241352262922582</v>
       </c>
@@ -10099,7 +10381,7 @@
         <f t="shared" ref="H8:H71" ca="1" si="3">E8*F8/1000</f>
         <v>456.23438486914682</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="19">
         <f ca="1" xml:space="preserve"> MR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-30.185112557847674</v>
       </c>
@@ -10139,7 +10421,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>455.63042953772191</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="19">
         <f ca="1" xml:space="preserve"> MR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>301.85112557847674</v>
       </c>
@@ -10179,7 +10461,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>470.4835422759449</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="19">
         <f ca="1" xml:space="preserve"> MR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>181.11067534708604</v>
       </c>
@@ -10219,7 +10501,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>482.6634155367725</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="19">
         <f ca="1" xml:space="preserve"> MR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>120.7404502313907</v>
       </c>
@@ -10259,7 +10541,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>489.63679522054355</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="19"/>
       <c r="J12" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.6732680000000024</v>
@@ -10296,7 +10578,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>492.30944167500178</v>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="19"/>
       <c r="J13" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.6917139999999928</v>
@@ -10333,7 +10615,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>493.49322977795714</v>
       </c>
-      <c r="I14" s="21"/>
+      <c r="I14" s="19"/>
       <c r="J14" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.7174140000000082</v>
@@ -10370,7 +10652,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>494.70116822155211</v>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="19"/>
       <c r="J15" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.7390380000000023</v>
@@ -10407,7 +10689,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>496.43856972924095</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="19"/>
       <c r="J16" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.7623199999999937</v>
@@ -10444,7 +10726,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>498.20077159394566</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="19"/>
       <c r="J17" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.7815259999999955</v>
@@ -10481,7 +10763,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>499.96524482749993</v>
       </c>
-      <c r="I18" s="21"/>
+      <c r="I18" s="19"/>
       <c r="J18" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8048079999999931</v>
@@ -10518,7 +10800,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>501.74921276213678</v>
       </c>
-      <c r="I19" s="21"/>
+      <c r="I19" s="19"/>
       <c r="J19" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8240140000000062</v>
@@ -10555,7 +10837,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>502.96265741465658</v>
       </c>
-      <c r="I20" s="21"/>
+      <c r="I20" s="19"/>
       <c r="J20" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8497140000000025</v>
@@ -10592,7 +10874,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>504.75818327234555</v>
       </c>
-      <c r="I21" s="21"/>
+      <c r="I21" s="19"/>
       <c r="J21" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8811480000000094</v>
@@ -10629,7 +10911,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>507.78113454597451</v>
       </c>
-      <c r="I22" s="21"/>
+      <c r="I22" s="19"/>
       <c r="J22" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8995940000000042</v>
@@ -10666,7 +10948,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>515.02864376002208</v>
       </c>
-      <c r="I23" s="21"/>
+      <c r="I23" s="19"/>
       <c r="J23" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8970380000000024</v>
@@ -10703,7 +10985,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>519.91139912621907</v>
       </c>
-      <c r="I24" s="21"/>
+      <c r="I24" s="19"/>
       <c r="J24" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.9041539999999924</v>
@@ -10740,7 +11022,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>523.58556297215523</v>
       </c>
-      <c r="I25" s="21"/>
+      <c r="I25" s="19"/>
       <c r="J25" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.9120300000000059</v>
@@ -10777,7 +11059,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>525.9829303374853</v>
       </c>
-      <c r="I26" s="21"/>
+      <c r="I26" s="19"/>
       <c r="J26" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.89213399999999</v>
@@ -10814,7 +11096,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>528.82390824706442</v>
       </c>
-      <c r="I27" s="21"/>
+      <c r="I27" s="19"/>
       <c r="J27" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.9391119999999999</v>
@@ -10851,7 +11133,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>531.17015558101025</v>
       </c>
-      <c r="I28" s="21"/>
+      <c r="I28" s="19"/>
       <c r="J28" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.9885080000000042</v>
@@ -10888,7 +11170,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>537.02764364523887</v>
       </c>
-      <c r="I29" s="21"/>
+      <c r="I29" s="19"/>
       <c r="J29" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0176620000000014</v>
@@ -10925,7 +11207,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>544.43461676396498</v>
       </c>
-      <c r="I30" s="21"/>
+      <c r="I30" s="19"/>
       <c r="J30" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0134480000000021</v>
@@ -10962,7 +11244,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>556.79550835584303</v>
       </c>
-      <c r="I31" s="21"/>
+      <c r="I31" s="19"/>
       <c r="J31" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0086119999999905</v>
@@ -10999,7 +11281,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>567.2658278303403</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="19">
         <f ca="1" xml:space="preserve"> MR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-18.735587104870969</v>
       </c>
@@ -11039,7 +11321,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>573.15273417930689</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="19">
         <f ca="1" xml:space="preserve"> MR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-18.735587104870969</v>
       </c>
@@ -11079,7 +11361,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>569.38114522306751</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="19">
         <f ca="1" xml:space="preserve"> MR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-18.735587104870969</v>
       </c>
@@ -11119,7 +11401,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>560.85466376471197</v>
       </c>
-      <c r="I35" s="21"/>
+      <c r="I35" s="19"/>
       <c r="J35" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0413599999999934</v>
@@ -14264,11 +14546,11 @@
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="20" t="s">
+      <c r="D126" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
+      <c r="E126" s="23"/>
+      <c r="F126" s="23"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
@@ -14638,16 +14920,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -14733,7 +15015,7 @@
         <f>E7*F7/1000</f>
         <v>249.7451219703506</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="19">
         <f ca="1" xml:space="preserve"> BR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-6.4659861277635216</v>
       </c>
@@ -14773,7 +15055,7 @@
         <f t="shared" ref="H8:H71" ca="1" si="3">E8*F8/1000</f>
         <v>249.10002867363002</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="19">
         <f ca="1" xml:space="preserve"> BR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-17.362370157883532</v>
       </c>
@@ -14813,7 +15095,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>249.1265495984712</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="19">
         <f ca="1" xml:space="preserve"> BR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>173.62370157883532</v>
       </c>
@@ -14853,7 +15135,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>257.62017791738242</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="19">
         <f ca="1" xml:space="preserve"> BR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>104.17422094730118</v>
       </c>
@@ -14893,7 +15175,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>264.67592868535752</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="19">
         <f ca="1" xml:space="preserve"> BR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>69.449480631534129</v>
       </c>
@@ -14933,7 +15215,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>268.89512950033725</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="19"/>
       <c r="J12" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8262320000000036</v>
@@ -14970,7 +15252,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>270.76962561701743</v>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="19"/>
       <c r="J13" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8432360000000074</v>
@@ -15007,7 +15289,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>271.82512815693326</v>
       </c>
-      <c r="I14" s="21"/>
+      <c r="I14" s="19"/>
       <c r="J14" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8671159999999996</v>
@@ -15044,7 +15326,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>272.89151907113092</v>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="19"/>
       <c r="J15" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.8868920000000067</v>
@@ -15081,7 +15363,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>274.24789724488232</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="19"/>
       <c r="J16" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.9084799999999973</v>
@@ -15118,7 +15400,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>275.616688806046</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="19"/>
       <c r="J17" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.925964000000006</v>
@@ -15155,7 +15437,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>276.9853504288505</v>
       </c>
-      <c r="I18" s="21"/>
+      <c r="I18" s="19"/>
       <c r="J18" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.9475519999999926</v>
@@ -15192,7 +15474,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>278.36344149771548</v>
       </c>
-      <c r="I19" s="21"/>
+      <c r="I19" s="19"/>
       <c r="J19" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.965036</v>
@@ -15229,7 +15511,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>279.42309768839544</v>
       </c>
-      <c r="I20" s="21"/>
+      <c r="I20" s="19"/>
       <c r="J20" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>1.9889159999999966</v>
@@ -15266,7 +15548,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>280.8038717580356</v>
       </c>
-      <c r="I21" s="21"/>
+      <c r="I21" s="19"/>
       <c r="J21" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0187120000000074</v>
@@ -15303,7 +15585,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>282.86700416865631</v>
       </c>
-      <c r="I22" s="21"/>
+      <c r="I22" s="19"/>
       <c r="J22" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0357160000000021</v>
@@ -15340,7 +15622,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>287.28759609945968</v>
       </c>
-      <c r="I23" s="21"/>
+      <c r="I23" s="19"/>
       <c r="J23" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0325720000000009</v>
@@ -15377,7 +15659,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>290.39698691501752</v>
       </c>
-      <c r="I24" s="21"/>
+      <c r="I24" s="19"/>
       <c r="J24" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0385959999999992</v>
@@ -15414,7 +15696,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>292.83502227821384</v>
       </c>
-      <c r="I25" s="21"/>
+      <c r="I25" s="19"/>
       <c r="J25" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0451000000000006</v>
@@ -15451,7 +15733,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>294.55995600868778</v>
       </c>
-      <c r="I26" s="21"/>
+      <c r="I26" s="19"/>
       <c r="J26" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0233559999999939</v>
@@ -15488,7 +15770,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>296.53235366428089</v>
       </c>
-      <c r="I27" s="21"/>
+      <c r="I27" s="19"/>
       <c r="J27" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.0690880000000105</v>
@@ -15525,7 +15807,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>298.22775357226573</v>
       </c>
-      <c r="I28" s="21"/>
+      <c r="I28" s="19"/>
       <c r="J28" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.1171120000000045</v>
@@ -15562,7 +15844,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>301.89666716532162</v>
       </c>
-      <c r="I29" s="21"/>
+      <c r="I29" s="19"/>
       <c r="J29" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.1454680000000024</v>
@@ -15599,7 +15881,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>306.44401534495813</v>
       </c>
-      <c r="I30" s="21"/>
+      <c r="I30" s="19"/>
       <c r="J30" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.1405120000000069</v>
@@ -15636,7 +15918,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>313.79190814646375</v>
       </c>
-      <c r="I31" s="21"/>
+      <c r="I31" s="19"/>
       <c r="J31" s="9">
         <f t="shared" ca="1" si="4"/>
         <v>2.1359279999999954</v>
@@ -15673,7 +15955,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>320.09164637257186</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="19">
         <f ca="1" xml:space="preserve"> BR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-10.776643546272537</v>
       </c>
@@ -15713,7 +15995,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>323.82352979729569</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="19">
         <f ca="1" xml:space="preserve"> BR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-10.776643546272537</v>
       </c>
@@ -15753,7 +16035,7 @@
         <f t="shared" ca="1" si="3"/>
         <v>322.09734777137908</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="19">
         <f ca="1" xml:space="preserve"> BR!F6 / RSFSR!F6 * INDIRECT("'RSFSR'!" &amp; ADDRESS(ROW(), COLUMN()))</f>
         <v>-10.776643546272537</v>
       </c>
@@ -18937,11 +19219,11 @@
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="20" t="s">
+      <c r="D126" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
+      <c r="E126" s="23"/>
+      <c r="F126" s="23"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
@@ -19289,15 +19571,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8D6E65-2B95-4A9B-AD02-8B2F5D0F409E}">
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:W91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
@@ -19309,529 +19591,1147 @@
     <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="16.42578125" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="40" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U5" s="18"/>
+      <c r="V5" s="18"/>
+    </row>
+    <row r="6" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6" s="7" t="s">
+      <c r="L6" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="O6" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="Q6" s="7" t="s">
+      <c r="Q6" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="S7" s="23"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
+      <c r="R6" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="S6" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="T6" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="U6" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="V6" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="W6" s="39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T7" s="21"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
         <v>1926</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <f ca="1">RSFSR!F128</f>
         <v>106845.8166895476</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <f ca="1">NR!F128</f>
         <v>18019.280954398353</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="26">
         <f ca="1">MR!F128</f>
         <v>22210.409745857956</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="26">
         <f ca="1">BR!F128</f>
         <v>12962.051806097428</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="S8" s="22">
-        <f ca="1">SUM(C8:Q8)</f>
-        <v>160037.55919590133</v>
-      </c>
-      <c r="T8" s="22"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="G8" s="31">
+        <v>2315</v>
+      </c>
+      <c r="H8" s="31">
+        <v>880</v>
+      </c>
+      <c r="I8" s="31">
+        <v>2666</v>
+      </c>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="42">
+        <v>6503</v>
+      </c>
+      <c r="M8" s="42">
+        <v>993</v>
+      </c>
+      <c r="N8" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="O8" s="31">
+        <v>1001</v>
+      </c>
+      <c r="P8" s="31">
+        <v>5273</v>
+      </c>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="45"/>
+      <c r="S8" s="46">
+        <v>11400</v>
+      </c>
+      <c r="T8" s="27">
+        <f ca="1">SUM(C8:R8) - S8</f>
+        <v>168268.55919590133</v>
+      </c>
+      <c r="U8" s="41">
+        <v>148530</v>
+      </c>
+      <c r="V8" s="29">
+        <f t="shared" ref="V8:V13" ca="1" si="0">100 * (T8-U8) / T8</f>
+        <v>11.730390567450771</v>
+      </c>
+      <c r="W8" s="27">
+        <f t="shared" ref="W8:W13" ca="1" si="1">T8-U8</f>
+        <v>19738.559195901325</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
         <v>1937</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <f ca="1">RSFSR!F129</f>
         <v>130704.49149186898</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="26">
         <f ca="1">NR!F129</f>
         <v>22382.063873054278</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="26">
         <f ca="1">MR!F129</f>
         <v>26743.345769715615</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="26">
         <f ca="1">BR!F129</f>
         <v>15820.711339210739</v>
       </c>
-      <c r="G9" s="25">
-        <v>2953</v>
-      </c>
-      <c r="H9" s="25">
-        <v>1194</v>
-      </c>
-      <c r="I9" s="25">
-        <v>3320</v>
-      </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25">
-        <v>4820</v>
-      </c>
-      <c r="M9" s="25">
-        <v>1306</v>
-      </c>
-      <c r="N9" s="25">
-        <v>1356</v>
-      </c>
-      <c r="O9" s="25">
-        <v>1135</v>
-      </c>
-      <c r="P9" s="25">
-        <v>5691</v>
-      </c>
-      <c r="Q9" s="22"/>
-      <c r="S9" s="22">
-        <f t="shared" ref="S9:S15" ca="1" si="0">SUM(C9:Q9)</f>
-        <v>217425.61247384961</v>
-      </c>
-      <c r="T9" s="25">
+      <c r="G9" s="31">
+        <v>3057</v>
+      </c>
+      <c r="H9" s="31">
+        <v>1209</v>
+      </c>
+      <c r="I9" s="31">
+        <v>3377</v>
+      </c>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="31">
+        <v>5120</v>
+      </c>
+      <c r="M9" s="31">
+        <v>1370</v>
+      </c>
+      <c r="N9" s="31">
+        <v>1382</v>
+      </c>
+      <c r="O9" s="31">
+        <v>1169</v>
+      </c>
+      <c r="P9" s="31">
+        <v>5847</v>
+      </c>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="46">
+        <v>12700</v>
+      </c>
+      <c r="T9" s="27">
+        <f t="shared" ref="T9:T15" ca="1" si="2">SUM(C9:R9) - S9</f>
+        <v>205481.61247384961</v>
+      </c>
+      <c r="U9" s="41">
         <v>162039</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
+      <c r="V9" s="29">
+        <f t="shared" ca="1" si="0"/>
+        <v>21.141849117705505</v>
+      </c>
+      <c r="W9" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>43442.612473849615</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
         <v>1939</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <f ca="1">RSFSR!F130</f>
         <v>136512.00079842543</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <f ca="1">NR!F130</f>
         <v>23439.059721823676</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="26">
         <f ca="1">MR!F130</f>
         <v>27821.07172486337</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="26">
         <f ca="1">BR!F130</f>
         <v>16500.649945916142</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="31">
         <v>3205.15</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="31">
         <v>1282.338</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="31">
         <v>3540.0230000000001</v>
       </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22">
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="31">
         <v>6151.1019999999999</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="31">
         <v>1458.213</v>
       </c>
-      <c r="N10" s="22">
+      <c r="N10" s="31">
         <v>1484.44</v>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="31">
         <v>1251.883</v>
       </c>
-      <c r="P10" s="22">
+      <c r="P10" s="31">
         <v>6271.2690000000002</v>
       </c>
-      <c r="Q10" s="22"/>
-      <c r="S10" s="22">
+      <c r="Q10" s="44"/>
+      <c r="R10" s="45"/>
+      <c r="S10" s="46">
+        <v>13000</v>
+      </c>
+      <c r="T10" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>215917.20019102859</v>
+      </c>
+      <c r="U10" s="41">
+        <v>167650</v>
+      </c>
+      <c r="V10" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>228917.20019102859</v>
-      </c>
-      <c r="T10" s="22">
-        <v>167650</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+        <v>22.35449521776177</v>
+      </c>
+      <c r="W10" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>48267.200191028591</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="30">
         <v>1959</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <f ca="1">RSFSR!F131</f>
         <v>220688.70840674659</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="26">
         <f ca="1">NR!F131</f>
         <v>38635.638851153497</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="26">
         <f ca="1">MR!F131</f>
         <v>42650.011568127789</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="26">
         <f ca="1">BR!F131</f>
         <v>25877.14291319147</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="31">
         <v>3697.7170000000001</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="31">
         <v>1763.048</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="31">
         <v>4044.0450000000001</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11" s="31">
         <v>2093.4580000000001</v>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="31">
         <v>2711.4450000000002</v>
       </c>
-      <c r="L11" s="22">
+      <c r="L11" s="31">
         <v>9309.8469999999998</v>
       </c>
-      <c r="M11" s="22">
+      <c r="M11" s="31">
         <v>2065.837</v>
       </c>
-      <c r="N11" s="22">
+      <c r="N11" s="31">
         <v>1979.8969999999999</v>
       </c>
-      <c r="O11" s="22">
+      <c r="O11" s="31">
         <v>1516.375</v>
       </c>
-      <c r="P11" s="22">
+      <c r="P11" s="31">
         <v>8105.7039999999997</v>
       </c>
-      <c r="Q11" s="22">
+      <c r="Q11" s="31">
         <v>1196.7909999999999</v>
       </c>
-      <c r="S11" s="22">
+      <c r="R11" s="31">
+        <f>H81</f>
+        <v>6155</v>
+      </c>
+      <c r="S11" s="46"/>
+      <c r="T11" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>372490.6657392194</v>
+      </c>
+      <c r="U11" s="41">
+        <v>208826.65</v>
+      </c>
+      <c r="V11" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>366335.6657392194</v>
-      </c>
-      <c r="T11" s="22">
-        <v>208826.65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+        <v>43.937749531098461</v>
+      </c>
+      <c r="W11" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>163664.01573921941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="30">
         <v>1970</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <f ca="1">RSFSR!F132</f>
         <v>317618.5255269864</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="26">
         <f ca="1">NR!F132</f>
         <v>55638.996828728697</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="26">
         <f ca="1">MR!F132</f>
         <v>58250.317096030019</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="26">
         <f ca="1">BR!F132</f>
         <v>35665.175743035215</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="31">
         <v>5117</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="31">
         <v>2492</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="32">
         <v>4686.3999999999996</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="32">
         <v>2364.1</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="32">
         <v>3128.2</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="32">
         <v>12848.6</v>
       </c>
-      <c r="M12" s="24">
+      <c r="M12" s="32">
         <v>2932.8</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="32">
         <v>2899.6</v>
       </c>
-      <c r="O12" s="24">
+      <c r="O12" s="32">
         <v>2158.9</v>
       </c>
-      <c r="P12" s="24">
+      <c r="P12" s="32">
         <v>11959.6</v>
       </c>
-      <c r="Q12" s="24">
+      <c r="Q12" s="32">
         <v>1356.1</v>
       </c>
-      <c r="S12" s="22">
+      <c r="R12" s="31">
+        <f t="shared" ref="R12:R14" si="3">H82</f>
+        <v>6964</v>
+      </c>
+      <c r="S12" s="46"/>
+      <c r="T12" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>526080.31519478024</v>
+      </c>
+      <c r="U12" s="41">
+        <v>241720</v>
+      </c>
+      <c r="V12" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>519116.3151947803</v>
-      </c>
-      <c r="T12" s="22">
-        <v>241720</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+        <v>54.052643100606488</v>
+      </c>
+      <c r="W12" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>284360.31519478024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="30">
         <v>1979</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <f ca="1">RSFSR!F133</f>
         <v>445922.55198754626</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="26">
         <f ca="1">NR!F133</f>
         <v>77821.056177823426</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="26">
         <f ca="1">MR!F133</f>
         <v>77590.700867184496</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="26">
         <f ca="1">BR!F133</f>
         <v>47791.781706532427</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="31">
         <v>6028</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="31">
         <v>3031</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="31">
         <v>5015</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="31">
         <v>2521</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="31">
         <v>3398</v>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="31">
         <v>14685</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="31">
         <v>3529</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="31">
         <v>3801</v>
       </c>
-      <c r="O13" s="26">
+      <c r="O13" s="31">
         <v>2759</v>
       </c>
-      <c r="P13" s="22">
+      <c r="P13" s="31">
         <v>15391</v>
       </c>
-      <c r="Q13" s="22">
+      <c r="Q13" s="31">
         <v>1466</v>
       </c>
-      <c r="S13" s="22">
+      <c r="R13" s="31">
+        <f t="shared" si="3"/>
+        <v>7372</v>
+      </c>
+      <c r="S13" s="46"/>
+      <c r="T13" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>718122.09073908674</v>
+      </c>
+      <c r="U13" s="41">
+        <v>262436</v>
+      </c>
+      <c r="V13" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>710750.09073908674</v>
-      </c>
-      <c r="T13" s="22">
-        <v>262436</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+        <v>63.455239243524382</v>
+      </c>
+      <c r="W13" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>455686.09073908674</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="30">
         <v>1989</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <f ca="1">RSFSR!F134</f>
         <v>644973.97216546303</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="26">
         <f ca="1">NR!F134</f>
         <v>111938.11167520715</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="26">
         <f ca="1">MR!F134</f>
         <v>105847.79298962053</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="26">
         <f ca="1">BR!F134</f>
         <v>65568.562017865115</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="31">
         <v>7038</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="31">
         <v>3288</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="31">
         <v>5443</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="31">
         <v>2680</v>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="31">
         <v>3690</v>
       </c>
-      <c r="L14" s="22">
+      <c r="L14" s="31">
         <v>16537</v>
       </c>
-      <c r="M14" s="22">
+      <c r="M14" s="31">
         <v>4290</v>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="31">
         <v>5109</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="31">
         <v>3534</v>
       </c>
-      <c r="P14" s="22">
+      <c r="P14" s="31">
         <v>19905</v>
       </c>
-      <c r="Q14" s="22">
+      <c r="Q14" s="31">
         <v>1573</v>
       </c>
-      <c r="S14" s="22">
-        <f t="shared" ca="1" si="0"/>
-        <v>1001415.4388481559</v>
-      </c>
-      <c r="T14" s="22">
+      <c r="R14" s="31">
+        <f t="shared" si="3"/>
+        <v>7839</v>
+      </c>
+      <c r="S14" s="46"/>
+      <c r="T14" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>1009254.4388481559</v>
+      </c>
+      <c r="U14" s="41">
         <v>286731</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="V14" s="29">
+        <f ca="1">100 * (T14-U14) / T14</f>
+        <v>71.589820270967451</v>
+      </c>
+      <c r="W14" s="27">
+        <f ca="1">T14-U14</f>
+        <v>722523.4388481559</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="30">
         <v>2020</v>
       </c>
-      <c r="C15" s="27">
+      <c r="B15" s="28"/>
+      <c r="C15" s="26">
         <f>RSFSR!F135</f>
         <v>1405423.5653519635</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="26">
         <f ca="1">NR!F135</f>
         <v>240865.84529590677</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="26">
         <f ca="1">MR!F135</f>
         <v>203586.30699195914</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="26">
         <f ca="1">BR!F135</f>
         <v>127579.75240628255</v>
       </c>
-      <c r="S15" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="27">
+        <f t="shared" ca="1" si="2"/>
         <v>1977455.4700461121</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="U15" s="27">
+        <f>C91</f>
+        <v>198061</v>
+      </c>
+      <c r="V15" s="29">
+        <f ca="1">100 * (T15-U15) / T15</f>
+        <v>89.984047529758953</v>
+      </c>
+      <c r="W15" s="27">
+        <f ca="1">T15-U15</f>
+        <v>1779394.4700461121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="7"/>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="7"/>
+      <c r="D32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="7"/>
+      <c r="D33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="7"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="7"/>
+      <c r="D35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="7"/>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="7"/>
+      <c r="D37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="7"/>
+      <c r="D38" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="7"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="7"/>
+      <c r="D40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="7"/>
+      <c r="D41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="7"/>
+      <c r="D42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="7"/>
+      <c r="D43" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="7"/>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="7"/>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="7"/>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="7"/>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="7"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="7"/>
+      <c r="D50" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="33">
+        <v>1926</v>
+      </c>
+      <c r="E54" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="33"/>
+      <c r="E55" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="33"/>
+      <c r="E56" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="33"/>
+      <c r="E57" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="33"/>
+      <c r="E58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="33"/>
+      <c r="E59" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="33"/>
+      <c r="E60" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="33">
+        <v>1937</v>
+      </c>
+      <c r="E62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="33">
+        <v>1959</v>
+      </c>
+      <c r="E64" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B66" s="33">
+        <v>1939</v>
+      </c>
+      <c r="E66" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="33"/>
+      <c r="E67" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="33"/>
+      <c r="E68" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="33"/>
+      <c r="E69" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="24"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" s="24"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B74" s="24"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B76" s="24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B77" s="24"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="24"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B79" s="24"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B80" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G80" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="34">
+        <v>1959</v>
+      </c>
+      <c r="B81" s="35">
+        <v>2108</v>
+      </c>
+      <c r="C81" s="35">
+        <v>1095</v>
+      </c>
+      <c r="D81" s="35">
+        <v>920</v>
+      </c>
+      <c r="E81" s="35">
+        <v>1086</v>
+      </c>
+      <c r="F81" s="35">
+        <v>774</v>
+      </c>
+      <c r="G81" s="35">
+        <v>172</v>
+      </c>
+      <c r="H81" s="35">
+        <f t="shared" ref="H81:H83" si="4">SUM(B81:G81)</f>
+        <v>6155</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="34">
+        <v>1970</v>
+      </c>
+      <c r="B82" s="35">
+        <v>2429</v>
+      </c>
+      <c r="C82" s="35">
+        <v>1249</v>
+      </c>
+      <c r="D82" s="35">
+        <v>1057</v>
+      </c>
+      <c r="E82" s="35">
+        <v>1153</v>
+      </c>
+      <c r="F82" s="35">
+        <v>845</v>
+      </c>
+      <c r="G82" s="35">
+        <v>231</v>
+      </c>
+      <c r="H82" s="35">
+        <f t="shared" si="4"/>
+        <v>6964</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="34">
+        <v>1979</v>
+      </c>
+      <c r="B83" s="35">
+        <v>2569</v>
+      </c>
+      <c r="C83" s="35">
+        <v>1327</v>
+      </c>
+      <c r="D83" s="35">
+        <v>1156</v>
+      </c>
+      <c r="E83" s="35">
+        <v>1162</v>
+      </c>
+      <c r="F83" s="35">
+        <v>890</v>
+      </c>
+      <c r="G83" s="35">
+        <v>268</v>
+      </c>
+      <c r="H83" s="35">
+        <f t="shared" si="4"/>
+        <v>7372</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="34">
+        <v>1989</v>
+      </c>
+      <c r="B84" s="35">
+        <v>2748</v>
+      </c>
+      <c r="C84" s="35">
+        <v>1423</v>
+      </c>
+      <c r="D84" s="35">
+        <v>1252</v>
+      </c>
+      <c r="E84" s="35">
+        <v>1169</v>
+      </c>
+      <c r="F84" s="35">
+        <v>938</v>
+      </c>
+      <c r="G84" s="35">
+        <v>309</v>
+      </c>
+      <c r="H84" s="35">
+        <f>SUM(B84:G84)</f>
+        <v>7839</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>91</v>
+      </c>
+      <c r="C88" s="20">
+        <v>146749</v>
+      </c>
+      <c r="E88" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>92</v>
+      </c>
+      <c r="C89" s="20">
+        <v>9410</v>
+      </c>
+      <c r="E89" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" s="20">
+        <v>41902</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C91" s="20">
+        <f>SUM(C88:C90)</f>
+        <v>198061</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="H81:H84" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47902CD7-B101-4EFC-96D1-A686FA0B5277}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E310FFF2-1C6B-4DFC-9DA0-1A0292044A08}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16335" yWindow="1500" windowWidth="28035" windowHeight="20805" activeTab="4" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
+    <workbookView xWindow="1830" yWindow="1350" windowWidth="28035" windowHeight="20805" activeTab="4" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
   <sheets>
     <sheet name="RSFSR" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,11 @@
     <sheet name="MR" sheetId="4" r:id="rId3"/>
     <sheet name="BR" sheetId="3" r:id="rId4"/>
     <sheet name="USSR" sheetId="6" r:id="rId5"/>
+    <sheet name="RB-RD" sheetId="7" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="URK_2020_1989">USSR!$E$102</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="139">
   <si>
     <t>год</t>
   </si>
@@ -115,9 +119,6 @@
     <t>Ожидаемая численность населеления на даты состоявшихся переписей населения</t>
   </si>
   <si>
-    <t>Ретропрогноз динамики демографического перехода для населения территории РСФСР-1991</t>
-  </si>
-  <si>
     <t>Ретропрогноз динамики демографического перехода для населения территории Новороссии</t>
   </si>
   <si>
@@ -131,9 +132,6 @@
   </si>
   <si>
     <t>1910-1914</t>
-  </si>
-  <si>
-    <t>Ретропрогноз динамики демографического перехода для населения территории СССР-1991</t>
   </si>
   <si>
     <t>на дату переписи</t>
@@ -390,6 +388,86 @@
   <si>
     <t>А на конец 1926 года - 11.7-11.1 млн. чел.</t>
   </si>
+  <si>
+    <t>Модель скоростей спадания смертности и рождаемости в ходе демографического перехода</t>
+  </si>
+  <si>
+    <t>по примеру Мексики.</t>
+  </si>
+  <si>
+    <t>Уровень 1909 года принят за 1.0.</t>
+  </si>
+  <si>
+    <t>роджаемость</t>
+  </si>
+  <si>
+    <t>относительно 1909</t>
+  </si>
+  <si>
+    <t>RB</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>смертность
+(RD)</t>
+  </si>
+  <si>
+    <t>рождаемость
+(RB)</t>
+  </si>
+  <si>
+    <t>Значения относительных величин (RB и RD) сглажены фильтром Савицкого-Голея с шириной окна 13 лет для рождаемости и 9 лет для смертности.</t>
+  </si>
+  <si>
+    <t>1 янв</t>
+  </si>
+  <si>
+    <t>Население Тувы (2020) = Росстат, "Российский статистический ежегодник 2020", стр. 62</t>
+  </si>
+  <si>
+    <t>Последняя перепись населения на Украине прошла в 2001 году</t>
+  </si>
+  <si>
+    <t>Держстат України: Population (by estimate) as of January 1, 2020. Average annual populations January-December 2019</t>
+  </si>
+  <si>
+    <t>Оценка численности населения Украины на 2020 год:</t>
+  </si>
+  <si>
+    <t>Численность украинских областей оценена пропорцинально их численности по переписи 1989 года, численности населения УССР в 1989 году</t>
+  </si>
+  <si>
+    <t>Укр + Крым</t>
+  </si>
+  <si>
+    <t>и численности населения территории бывш. УССР в 2020 году</t>
+  </si>
+  <si>
+    <t>Крым 2020</t>
+  </si>
+  <si>
+    <t>УССР 1989</t>
+  </si>
+  <si>
+    <t>УССР 2020</t>
+  </si>
+  <si>
+    <t>https://web.archive.org/web/20200219072131/http://ukrstat.gov.ua/express/expr2020/02/18.pdf</t>
+  </si>
+  <si>
+    <t>УССР 2020/1989</t>
+  </si>
+  <si>
+    <t>Ретропрогноз динамики демографического перехода для населения территории РСФСР-1991 (без Тувы)</t>
+  </si>
+  <si>
+    <t>Ретропрогноз динамики демографического перехода для населения территории СССР</t>
+  </si>
+  <si>
+    <t>Численные значения из приложения М1 к РТСС.</t>
+  </si>
 </sst>
 </file>
 
@@ -478,7 +556,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -514,11 +592,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -555,12 +698,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -611,6 +748,54 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -941,32 +1126,32 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>26</v>
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>4</v>
@@ -995,7 +1180,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -5217,11 +5402,11 @@
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="23" t="s">
+      <c r="D126" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="23"/>
-      <c r="F126" s="23"/>
+      <c r="E126" s="58"/>
+      <c r="F126" s="58"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
@@ -5240,7 +5425,7 @@
         <v>20</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -5418,11 +5603,17 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="2"/>
+      <c r="A136" s="12">
+        <v>2030</v>
+      </c>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
+      <c r="F136" s="6">
+        <f>F120</f>
+        <v>1633084.1380099785</v>
+      </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
@@ -5586,22 +5777,22 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>27</v>
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -5640,7 +5831,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -9871,11 +10062,11 @@
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="23" t="s">
+      <c r="D126" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="23"/>
-      <c r="F126" s="23"/>
+      <c r="E126" s="58"/>
+      <c r="F126" s="58"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
@@ -10072,11 +10263,17 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="2"/>
+      <c r="A136" s="12">
+        <v>2030</v>
+      </c>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
+      <c r="F136" s="6">
+        <f ca="1">F120</f>
+        <v>279690.54437892081</v>
+      </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
@@ -10240,22 +10437,22 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>29</v>
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -10294,7 +10491,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -14546,11 +14743,11 @@
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="23" t="s">
+      <c r="D126" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="23"/>
-      <c r="F126" s="23"/>
+      <c r="E126" s="58"/>
+      <c r="F126" s="58"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
@@ -14747,11 +14944,17 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="2"/>
+      <c r="A136" s="12">
+        <v>2030</v>
+      </c>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
+      <c r="F136" s="6">
+        <f ca="1">F120</f>
+        <v>231276.97799760741</v>
+      </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
@@ -14914,22 +15117,22 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>28</v>
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -14968,7 +15171,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -19219,11 +19422,11 @@
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="23" t="s">
+      <c r="D126" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="23"/>
-      <c r="F126" s="23"/>
+      <c r="E126" s="58"/>
+      <c r="F126" s="58"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
@@ -19420,11 +19623,17 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="2"/>
+      <c r="A136" s="12">
+        <v>2030</v>
+      </c>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
+      <c r="F136" s="6">
+        <f ca="1">F120</f>
+        <v>145402.32407038182</v>
+      </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
@@ -19571,7 +19780,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8D6E65-2B95-4A9B-AD02-8B2F5D0F409E}">
-  <dimension ref="A1:W91"/>
+  <dimension ref="A1:W107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -19596,13 +19805,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
-        <v>32</v>
+      <c r="A1" s="38" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -19610,788 +19819,834 @@
       <c r="V5" s="18"/>
     </row>
     <row r="6" spans="1:23" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="38" t="s">
+      <c r="I6" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="38" t="s">
+      <c r="K6" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="L6" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="N6" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="M6" s="38" t="s">
+      <c r="O6" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="38" t="s">
+      <c r="P6" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="P6" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q6" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="R6" s="39" t="s">
+      <c r="R6" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="S6" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="T6" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="U6" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="V6" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="S6" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="T6" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="U6" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="V6" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="W6" s="39" t="s">
-        <v>78</v>
+      <c r="W6" s="37" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="T7" s="21"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="23">
         <v>1926</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="24">
         <f ca="1">RSFSR!F128</f>
         <v>106845.8166895476</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="24">
         <f ca="1">NR!F128</f>
         <v>18019.280954398353</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="24">
         <f ca="1">MR!F128</f>
         <v>22210.409745857956</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="24">
         <f ca="1">BR!F128</f>
         <v>12962.051806097428</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="29">
         <v>2315</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="29">
         <v>880</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="29">
         <v>2666</v>
       </c>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="42">
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="40">
         <v>6503</v>
       </c>
-      <c r="M8" s="42">
+      <c r="M8" s="40">
         <v>993</v>
       </c>
-      <c r="N8" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="O8" s="31">
+      <c r="N8" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="O8" s="29">
         <v>1001</v>
       </c>
-      <c r="P8" s="31">
+      <c r="P8" s="29">
         <v>5273</v>
       </c>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="46">
+      <c r="Q8" s="42"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="44">
         <v>11400</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="25">
         <f ca="1">SUM(C8:R8) - S8</f>
         <v>168268.55919590133</v>
       </c>
-      <c r="U8" s="41">
+      <c r="U8" s="39">
         <v>148530</v>
       </c>
-      <c r="V8" s="29">
+      <c r="V8" s="27">
         <f t="shared" ref="V8:V13" ca="1" si="0">100 * (T8-U8) / T8</f>
         <v>11.730390567450771</v>
       </c>
-      <c r="W8" s="27">
+      <c r="W8" s="25">
         <f t="shared" ref="W8:W13" ca="1" si="1">T8-U8</f>
         <v>19738.559195901325</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="25">
+      <c r="A9" s="23">
         <v>1937</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="24">
         <f ca="1">RSFSR!F129</f>
         <v>130704.49149186898</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <f ca="1">NR!F129</f>
         <v>22382.063873054278</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="24">
         <f ca="1">MR!F129</f>
         <v>26743.345769715615</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="24">
         <f ca="1">BR!F129</f>
         <v>15820.711339210739</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="29">
         <v>3057</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="29">
         <v>1209</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="29">
         <v>3377</v>
       </c>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="31">
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="29">
         <v>5120</v>
       </c>
-      <c r="M9" s="31">
+      <c r="M9" s="29">
         <v>1370</v>
       </c>
-      <c r="N9" s="31">
+      <c r="N9" s="29">
         <v>1382</v>
       </c>
-      <c r="O9" s="31">
+      <c r="O9" s="29">
         <v>1169</v>
       </c>
-      <c r="P9" s="31">
+      <c r="P9" s="29">
         <v>5847</v>
       </c>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="46">
+      <c r="Q9" s="42"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="44">
         <v>12700</v>
       </c>
-      <c r="T9" s="27">
-        <f t="shared" ref="T9:T15" ca="1" si="2">SUM(C9:R9) - S9</f>
+      <c r="T9" s="25">
+        <f t="shared" ref="T9:T16" ca="1" si="2">SUM(C9:R9) - S9</f>
         <v>205481.61247384961</v>
       </c>
-      <c r="U9" s="41">
+      <c r="U9" s="39">
         <v>162039</v>
       </c>
-      <c r="V9" s="29">
+      <c r="V9" s="27">
         <f t="shared" ca="1" si="0"/>
         <v>21.141849117705505</v>
       </c>
-      <c r="W9" s="27">
+      <c r="W9" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>43442.612473849615</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
+      <c r="A10" s="23">
         <v>1939</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="24">
         <f ca="1">RSFSR!F130</f>
         <v>136512.00079842543</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <f ca="1">NR!F130</f>
         <v>23439.059721823676</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="24">
         <f ca="1">MR!F130</f>
         <v>27821.07172486337</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="24">
         <f ca="1">BR!F130</f>
         <v>16500.649945916142</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="29">
         <v>3205.15</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="29">
         <v>1282.338</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="29">
         <v>3540.0230000000001</v>
       </c>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="31">
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="29">
         <v>6151.1019999999999</v>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="29">
         <v>1458.213</v>
       </c>
-      <c r="N10" s="31">
+      <c r="N10" s="29">
         <v>1484.44</v>
       </c>
-      <c r="O10" s="31">
+      <c r="O10" s="29">
         <v>1251.883</v>
       </c>
-      <c r="P10" s="31">
+      <c r="P10" s="29">
         <v>6271.2690000000002</v>
       </c>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="46">
+      <c r="Q10" s="42"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="44">
         <v>13000</v>
       </c>
-      <c r="T10" s="27">
+      <c r="T10" s="25">
         <f t="shared" ca="1" si="2"/>
         <v>215917.20019102859</v>
       </c>
-      <c r="U10" s="41">
+      <c r="U10" s="39">
         <v>167650</v>
       </c>
-      <c r="V10" s="29">
+      <c r="V10" s="27">
         <f t="shared" ca="1" si="0"/>
         <v>22.35449521776177</v>
       </c>
-      <c r="W10" s="27">
+      <c r="W10" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>48267.200191028591</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A11" s="30">
+      <c r="A11" s="28">
         <v>1959</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="24">
         <f ca="1">RSFSR!F131</f>
         <v>220688.70840674659</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="24">
         <f ca="1">NR!F131</f>
         <v>38635.638851153497</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="24">
         <f ca="1">MR!F131</f>
         <v>42650.011568127789</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="24">
         <f ca="1">BR!F131</f>
         <v>25877.14291319147</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="29">
         <v>3697.7170000000001</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="29">
         <v>1763.048</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="29">
         <v>4044.0450000000001</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="29">
         <v>2093.4580000000001</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="29">
         <v>2711.4450000000002</v>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="29">
         <v>9309.8469999999998</v>
       </c>
-      <c r="M11" s="31">
+      <c r="M11" s="29">
         <v>2065.837</v>
       </c>
-      <c r="N11" s="31">
+      <c r="N11" s="29">
         <v>1979.8969999999999</v>
       </c>
-      <c r="O11" s="31">
+      <c r="O11" s="29">
         <v>1516.375</v>
       </c>
-      <c r="P11" s="31">
+      <c r="P11" s="29">
         <v>8105.7039999999997</v>
       </c>
-      <c r="Q11" s="31">
+      <c r="Q11" s="29">
         <v>1196.7909999999999</v>
       </c>
-      <c r="R11" s="31">
-        <f>H81</f>
+      <c r="R11" s="29">
+        <f>H82</f>
         <v>6155</v>
       </c>
-      <c r="S11" s="46"/>
-      <c r="T11" s="27">
+      <c r="S11" s="44"/>
+      <c r="T11" s="25">
         <f t="shared" ca="1" si="2"/>
         <v>372490.6657392194</v>
       </c>
-      <c r="U11" s="41">
+      <c r="U11" s="39">
         <v>208826.65</v>
       </c>
-      <c r="V11" s="29">
+      <c r="V11" s="27">
         <f t="shared" ca="1" si="0"/>
         <v>43.937749531098461</v>
       </c>
-      <c r="W11" s="27">
+      <c r="W11" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>163664.01573921941</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="30">
+      <c r="A12" s="28">
         <v>1970</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="24">
         <f ca="1">RSFSR!F132</f>
         <v>317618.5255269864</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="24">
         <f ca="1">NR!F132</f>
         <v>55638.996828728697</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="24">
         <f ca="1">MR!F132</f>
         <v>58250.317096030019</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="24">
         <f ca="1">BR!F132</f>
         <v>35665.175743035215</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="29">
         <v>5117</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="29">
         <v>2492</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="30">
         <v>4686.3999999999996</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="30">
         <v>2364.1</v>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="30">
         <v>3128.2</v>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="30">
         <v>12848.6</v>
       </c>
-      <c r="M12" s="32">
+      <c r="M12" s="30">
         <v>2932.8</v>
       </c>
-      <c r="N12" s="32">
+      <c r="N12" s="30">
         <v>2899.6</v>
       </c>
-      <c r="O12" s="32">
+      <c r="O12" s="30">
         <v>2158.9</v>
       </c>
-      <c r="P12" s="32">
+      <c r="P12" s="30">
         <v>11959.6</v>
       </c>
-      <c r="Q12" s="32">
+      <c r="Q12" s="30">
         <v>1356.1</v>
       </c>
-      <c r="R12" s="31">
-        <f t="shared" ref="R12:R14" si="3">H82</f>
+      <c r="R12" s="29">
+        <f t="shared" ref="R12:R15" si="3">H83</f>
         <v>6964</v>
       </c>
-      <c r="S12" s="46"/>
-      <c r="T12" s="27">
+      <c r="S12" s="44"/>
+      <c r="T12" s="25">
         <f t="shared" ca="1" si="2"/>
         <v>526080.31519478024</v>
       </c>
-      <c r="U12" s="41">
+      <c r="U12" s="39">
         <v>241720</v>
       </c>
-      <c r="V12" s="29">
+      <c r="V12" s="27">
         <f t="shared" ca="1" si="0"/>
         <v>54.052643100606488</v>
       </c>
-      <c r="W12" s="27">
+      <c r="W12" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>284360.31519478024</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="30">
+      <c r="A13" s="28">
         <v>1979</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="24">
         <f ca="1">RSFSR!F133</f>
         <v>445922.55198754626</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="24">
         <f ca="1">NR!F133</f>
         <v>77821.056177823426</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="24">
         <f ca="1">MR!F133</f>
         <v>77590.700867184496</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="24">
         <f ca="1">BR!F133</f>
         <v>47791.781706532427</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="29">
         <v>6028</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="29">
         <v>3031</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="29">
         <v>5015</v>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="29">
         <v>2521</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="29">
         <v>3398</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="29">
         <v>14685</v>
       </c>
-      <c r="M13" s="31">
+      <c r="M13" s="29">
         <v>3529</v>
       </c>
-      <c r="N13" s="31">
+      <c r="N13" s="29">
         <v>3801</v>
       </c>
-      <c r="O13" s="31">
+      <c r="O13" s="29">
         <v>2759</v>
       </c>
-      <c r="P13" s="31">
+      <c r="P13" s="29">
         <v>15391</v>
       </c>
-      <c r="Q13" s="31">
+      <c r="Q13" s="29">
         <v>1466</v>
       </c>
-      <c r="R13" s="31">
+      <c r="R13" s="29">
         <f t="shared" si="3"/>
         <v>7372</v>
       </c>
-      <c r="S13" s="46"/>
-      <c r="T13" s="27">
+      <c r="S13" s="44"/>
+      <c r="T13" s="25">
         <f t="shared" ca="1" si="2"/>
         <v>718122.09073908674</v>
       </c>
-      <c r="U13" s="41">
+      <c r="U13" s="39">
         <v>262436</v>
       </c>
-      <c r="V13" s="29">
+      <c r="V13" s="27">
         <f t="shared" ca="1" si="0"/>
         <v>63.455239243524382</v>
       </c>
-      <c r="W13" s="27">
+      <c r="W13" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>455686.09073908674</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
+      <c r="A14" s="28">
         <v>1989</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="24">
         <f ca="1">RSFSR!F134</f>
         <v>644973.97216546303</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="24">
         <f ca="1">NR!F134</f>
         <v>111938.11167520715</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="24">
         <f ca="1">MR!F134</f>
         <v>105847.79298962053</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="24">
         <f ca="1">BR!F134</f>
         <v>65568.562017865115</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="29">
         <v>7038</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="29">
         <v>3288</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="29">
         <v>5443</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="29">
         <v>2680</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="29">
         <v>3690</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="29">
         <v>16537</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="29">
         <v>4290</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="29">
         <v>5109</v>
       </c>
-      <c r="O14" s="31">
+      <c r="O14" s="29">
         <v>3534</v>
       </c>
-      <c r="P14" s="31">
+      <c r="P14" s="29">
         <v>19905</v>
       </c>
-      <c r="Q14" s="31">
+      <c r="Q14" s="29">
         <v>1573</v>
       </c>
-      <c r="R14" s="31">
+      <c r="R14" s="29">
         <f t="shared" si="3"/>
         <v>7839</v>
       </c>
-      <c r="S14" s="46"/>
-      <c r="T14" s="27">
+      <c r="S14" s="44"/>
+      <c r="T14" s="25">
         <f t="shared" ca="1" si="2"/>
         <v>1009254.4388481559</v>
       </c>
-      <c r="U14" s="41">
+      <c r="U14" s="39">
         <v>286731</v>
       </c>
-      <c r="V14" s="29">
+      <c r="V14" s="27">
         <f ca="1">100 * (T14-U14) / T14</f>
         <v>71.589820270967451</v>
       </c>
-      <c r="W14" s="27">
+      <c r="W14" s="25">
         <f ca="1">T14-U14</f>
         <v>722523.4388481559</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="30">
+      <c r="A15" s="28">
         <v>2020</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="26">
+      <c r="B15" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="24">
         <f>RSFSR!F135</f>
         <v>1405423.5653519635</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="24">
         <f ca="1">NR!F135</f>
         <v>240865.84529590677</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="24">
         <f ca="1">MR!F135</f>
         <v>203586.30699195914</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="24">
         <f ca="1">BR!F135</f>
         <v>127579.75240628255</v>
       </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="27">
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="29">
+        <f t="shared" si="3"/>
+        <v>6707.7018392093914</v>
+      </c>
+      <c r="S15" s="45"/>
+      <c r="T15" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>1977455.4700461121</v>
-      </c>
-      <c r="U15" s="27">
-        <f>C91</f>
+        <v>1984163.1718853214</v>
+      </c>
+      <c r="U15" s="25">
+        <f>C97</f>
         <v>198061</v>
       </c>
-      <c r="V15" s="29">
+      <c r="V15" s="27">
         <f ca="1">100 * (T15-U15) / T15</f>
-        <v>89.984047529758953</v>
-      </c>
-      <c r="W15" s="27">
+        <v>90.017907659690835</v>
+      </c>
+      <c r="W15" s="25">
         <f ca="1">T15-U15</f>
-        <v>1779394.4700461121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>51</v>
-      </c>
+        <v>1786102.1718853214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
+        <v>2030</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="24">
+        <f>RSFSR!F136</f>
+        <v>1633084.1380099785</v>
+      </c>
+      <c r="D16" s="24">
+        <f ca="1">NR!F136</f>
+        <v>279690.54437892081</v>
+      </c>
+      <c r="E16" s="24">
+        <f ca="1">MR!F136</f>
+        <v>231276.97799760741</v>
+      </c>
+      <c r="F16" s="24">
+        <f ca="1">BR!F136</f>
+        <v>145402.32407038182</v>
+      </c>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="45"/>
+      <c r="T16" s="25">
+        <f t="shared" ca="1" si="2"/>
+        <v>2289453.9844568889</v>
+      </c>
+      <c r="U16" s="25"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="25"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" t="s">
-        <v>72</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
+      <c r="B23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" t="s">
-        <v>71</v>
-      </c>
+      <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
+      <c r="B25" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
+      <c r="D26" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" t="s">
-        <v>105</v>
-      </c>
+      <c r="B27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="D28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" t="s">
         <v>103</v>
       </c>
     </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>71</v>
+      </c>
+    </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
+      <c r="B31" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
-      <c r="D32" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
+      <c r="D34" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
-      <c r="D35" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
+      <c r="D39" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7"/>
-      <c r="D40" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="7"/>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
       <c r="D42" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="D43" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
+      <c r="D44" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
@@ -20406,332 +20661,2588 @@
       <c r="B48" s="7"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="7"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="7"/>
+      <c r="D51" t="s">
         <v>106</v>
       </c>
-      <c r="D49" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="7"/>
-      <c r="D50" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="31">
+        <v>1926</v>
+      </c>
+      <c r="E55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="31"/>
+      <c r="E56" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="31"/>
+      <c r="E57" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="31"/>
+      <c r="E58" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="31"/>
+      <c r="E59" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="31"/>
+      <c r="E60" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="31"/>
+      <c r="E61" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="31">
+        <v>1937</v>
+      </c>
+      <c r="E63" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B65" s="31">
+        <v>1959</v>
+      </c>
+      <c r="E65" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="31">
+        <v>1939</v>
+      </c>
+      <c r="E67" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B68" s="31"/>
+      <c r="E68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B69" s="31"/>
+      <c r="E69" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B70" s="31"/>
+      <c r="E70" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B72" s="7" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="33">
-        <v>1926</v>
-      </c>
-      <c r="E54" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="33"/>
-      <c r="E55" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="33"/>
-      <c r="E56" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="33"/>
-      <c r="E57" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="33"/>
-      <c r="E58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="33"/>
-      <c r="E59" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="33"/>
-      <c r="E60" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="33">
-        <v>1937</v>
-      </c>
-      <c r="E62" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B64" s="33">
+      <c r="E72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="22"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>57</v>
+      </c>
+      <c r="B74" s="22"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B75" s="22"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B76" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B77" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B78" s="22"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" s="22"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B80" s="22"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B81" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="H81" s="18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="32">
         <v>1959</v>
       </c>
-      <c r="E64" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B66" s="33">
-        <v>1939</v>
-      </c>
-      <c r="E66" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="33"/>
-      <c r="E67" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="33"/>
-      <c r="E68" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="33"/>
-      <c r="E69" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B71" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E71" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B72" s="24"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>59</v>
-      </c>
-      <c r="B73" s="24"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B74" s="24"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B77" s="24"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>61</v>
-      </c>
-      <c r="B78" s="24"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B79" s="24"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B80" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="D80" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E80" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F80" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G80" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H80" s="18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="34">
-        <v>1959</v>
-      </c>
-      <c r="B81" s="35">
+      <c r="B82" s="33">
         <v>2108</v>
       </c>
-      <c r="C81" s="35">
+      <c r="C82" s="33">
         <v>1095</v>
       </c>
-      <c r="D81" s="35">
+      <c r="D82" s="33">
         <v>920</v>
       </c>
-      <c r="E81" s="35">
+      <c r="E82" s="33">
         <v>1086</v>
       </c>
-      <c r="F81" s="35">
+      <c r="F82" s="33">
         <v>774</v>
       </c>
-      <c r="G81" s="35">
+      <c r="G82" s="33">
         <v>172</v>
       </c>
-      <c r="H81" s="35">
-        <f t="shared" ref="H81:H83" si="4">SUM(B81:G81)</f>
+      <c r="H82" s="33">
+        <f t="shared" ref="H82:H84" si="4">SUM(B82:G82)</f>
         <v>6155</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="34">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="32">
         <v>1970</v>
       </c>
-      <c r="B82" s="35">
+      <c r="B83" s="33">
         <v>2429</v>
       </c>
-      <c r="C82" s="35">
+      <c r="C83" s="33">
         <v>1249</v>
       </c>
-      <c r="D82" s="35">
+      <c r="D83" s="33">
         <v>1057</v>
       </c>
-      <c r="E82" s="35">
+      <c r="E83" s="33">
         <v>1153</v>
       </c>
-      <c r="F82" s="35">
+      <c r="F83" s="33">
         <v>845</v>
       </c>
-      <c r="G82" s="35">
+      <c r="G83" s="33">
         <v>231</v>
       </c>
-      <c r="H82" s="35">
+      <c r="H83" s="33">
         <f t="shared" si="4"/>
         <v>6964</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="34">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="32">
         <v>1979</v>
       </c>
-      <c r="B83" s="35">
+      <c r="B84" s="33">
         <v>2569</v>
       </c>
-      <c r="C83" s="35">
+      <c r="C84" s="33">
         <v>1327</v>
       </c>
-      <c r="D83" s="35">
+      <c r="D84" s="33">
         <v>1156</v>
       </c>
-      <c r="E83" s="35">
+      <c r="E84" s="33">
         <v>1162</v>
       </c>
-      <c r="F83" s="35">
+      <c r="F84" s="33">
         <v>890</v>
       </c>
-      <c r="G83" s="35">
+      <c r="G84" s="33">
         <v>268</v>
       </c>
-      <c r="H83" s="35">
+      <c r="H84" s="33">
         <f t="shared" si="4"/>
         <v>7372</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="34">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="32">
         <v>1989</v>
       </c>
-      <c r="B84" s="35">
+      <c r="B85" s="33">
         <v>2748</v>
       </c>
-      <c r="C84" s="35">
+      <c r="C85" s="33">
         <v>1423</v>
       </c>
-      <c r="D84" s="35">
+      <c r="D85" s="33">
         <v>1252</v>
       </c>
-      <c r="E84" s="35">
+      <c r="E85" s="33">
         <v>1169</v>
       </c>
-      <c r="F84" s="35">
+      <c r="F85" s="33">
         <v>938</v>
       </c>
-      <c r="G84" s="35">
+      <c r="G85" s="33">
         <v>309</v>
       </c>
-      <c r="H84" s="35">
-        <f>SUM(B84:G84)</f>
+      <c r="H85" s="33">
+        <f>SUM(B85:G85)</f>
         <v>7839</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="32">
+        <v>2020</v>
+      </c>
+      <c r="B86" s="33">
+        <f>B85*URK_2020_1989</f>
+        <v>2328.574854468447</v>
+      </c>
+      <c r="C86" s="33">
+        <f>C85*URK_2020_1989</f>
+        <v>1205.8085945810044</v>
+      </c>
+      <c r="D86" s="33">
+        <f>D85*URK_2020_1989</f>
+        <v>1060.908194248361</v>
+      </c>
+      <c r="E86" s="33">
+        <f>E85*URK_2020_1989</f>
+        <v>990.57642098748715</v>
+      </c>
+      <c r="F86" s="33">
+        <f>F85*URK_2020_1989</f>
+        <v>794.83377492409147</v>
+      </c>
+      <c r="G86" s="33">
+        <v>327</v>
+      </c>
+      <c r="H86" s="33">
+        <f>SUM(B86:G86)</f>
+        <v>6707.7018392093914</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>89</v>
+      </c>
+      <c r="C94" s="20">
+        <v>146749</v>
+      </c>
+      <c r="E94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
+      <c r="C95" s="20">
+        <v>41902</v>
+      </c>
+      <c r="E95" t="s">
         <v>91</v>
       </c>
-      <c r="C88" s="20">
-        <v>146749</v>
-      </c>
-      <c r="E88" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" s="20">
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>34</v>
+      </c>
+      <c r="C96" s="20">
         <v>9410</v>
       </c>
-      <c r="E89" t="s">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>36</v>
-      </c>
-      <c r="C90" s="20">
-        <v>41902</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>95</v>
-      </c>
-      <c r="C91" s="20">
-        <f>SUM(C88:C90)</f>
+      <c r="C97" s="20">
+        <f>SUM(C94:C96)</f>
         <v>198061</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C98" s="20"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>131</v>
+      </c>
+      <c r="C99" s="6">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>132</v>
+      </c>
+      <c r="C100" s="20">
+        <v>51707</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>133</v>
+      </c>
+      <c r="C101" s="20">
+        <f>C95+C99</f>
+        <v>43815</v>
+      </c>
+      <c r="E101" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" s="20"/>
+      <c r="E102" s="56">
+        <f>C101/C100</f>
+        <v>0.84737076217920204</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="H81:H84" formulaRange="1"/>
+    <ignoredError sqref="H82:H85" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86EBEE66-658C-4218-A060-96E45597FC2B}">
+  <dimension ref="A1:E137"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="59"/>
+    </row>
+    <row r="12" spans="1:5" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="61"/>
+      <c r="B12" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="46">
+        <v>1895</v>
+      </c>
+      <c r="B13" s="48">
+        <v>46.6</v>
+      </c>
+      <c r="C13" s="48">
+        <v>33.6</v>
+      </c>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47">
+        <v>1896</v>
+      </c>
+      <c r="B14" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C14" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47">
+        <v>1897</v>
+      </c>
+      <c r="B15" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C15" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47">
+        <v>1898</v>
+      </c>
+      <c r="B16" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C16" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47">
+        <v>1899</v>
+      </c>
+      <c r="B17" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C17" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47">
+        <v>1900</v>
+      </c>
+      <c r="B18" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C18" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="47">
+        <v>1901</v>
+      </c>
+      <c r="B19" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C19" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="47">
+        <v>1902</v>
+      </c>
+      <c r="B20" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C20" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="47">
+        <v>1903</v>
+      </c>
+      <c r="B21" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C21" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="47">
+        <v>1904</v>
+      </c>
+      <c r="B22" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C22" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="47">
+        <v>1905</v>
+      </c>
+      <c r="B23" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C23" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="47">
+        <v>1906</v>
+      </c>
+      <c r="B24" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C24" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="47">
+        <v>1907</v>
+      </c>
+      <c r="B25" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C25" s="49">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="47">
+        <v>1908</v>
+      </c>
+      <c r="B26" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C26" s="49">
+        <v>33.6</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="47">
+        <v>1909</v>
+      </c>
+      <c r="B27" s="49">
+        <v>46.5</v>
+      </c>
+      <c r="C27" s="49">
+        <v>33.4</v>
+      </c>
+      <c r="D27" s="52">
+        <v>1</v>
+      </c>
+      <c r="E27" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47">
+        <v>1910</v>
+      </c>
+      <c r="B28" s="49">
+        <v>46.5</v>
+      </c>
+      <c r="C28" s="49">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="D28" s="52">
+        <v>0.999</v>
+      </c>
+      <c r="E28" s="52">
+        <v>0.99199999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="47">
+        <v>1911</v>
+      </c>
+      <c r="B29" s="49">
+        <v>46.4</v>
+      </c>
+      <c r="C29" s="49">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="D29" s="52">
+        <v>0.997</v>
+      </c>
+      <c r="E29" s="52">
+        <v>0.98099999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="47">
+        <v>1912</v>
+      </c>
+      <c r="B30" s="49">
+        <v>46.3</v>
+      </c>
+      <c r="C30" s="49">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="D30" s="52">
+        <v>0.995</v>
+      </c>
+      <c r="E30" s="52">
+        <v>0.96699999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="47">
+        <v>1913</v>
+      </c>
+      <c r="B31" s="49">
+        <v>46.2</v>
+      </c>
+      <c r="C31" s="49">
+        <v>31.9</v>
+      </c>
+      <c r="D31" s="52">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="E31" s="52">
+        <v>0.95299999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="47">
+        <v>1914</v>
+      </c>
+      <c r="B32" s="49">
+        <v>46.1</v>
+      </c>
+      <c r="C32" s="49">
+        <v>31.4</v>
+      </c>
+      <c r="D32" s="52">
+        <v>0.99</v>
+      </c>
+      <c r="E32" s="52">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="47">
+        <v>1915</v>
+      </c>
+      <c r="B33" s="49">
+        <v>46</v>
+      </c>
+      <c r="C33" s="49">
+        <v>31</v>
+      </c>
+      <c r="D33" s="52">
+        <v>0.98699999999999999</v>
+      </c>
+      <c r="E33" s="52">
+        <v>0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="47">
+        <v>1916</v>
+      </c>
+      <c r="B34" s="49">
+        <v>45.8</v>
+      </c>
+      <c r="C34" s="49">
+        <v>30.6</v>
+      </c>
+      <c r="D34" s="52">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="E34" s="52">
+        <v>0.91400000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="47">
+        <v>1917</v>
+      </c>
+      <c r="B35" s="49">
+        <v>45.7</v>
+      </c>
+      <c r="C35" s="49">
+        <v>30.1</v>
+      </c>
+      <c r="D35" s="52">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="E35" s="52">
+        <v>0.90100000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="47">
+        <v>1918</v>
+      </c>
+      <c r="B36" s="49">
+        <v>45.6</v>
+      </c>
+      <c r="C36" s="49">
+        <v>29.7</v>
+      </c>
+      <c r="D36" s="52">
+        <v>0.98</v>
+      </c>
+      <c r="E36" s="52">
+        <v>0.88700000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="47">
+        <v>1919</v>
+      </c>
+      <c r="B37" s="49">
+        <v>45.6</v>
+      </c>
+      <c r="C37" s="49">
+        <v>29.2</v>
+      </c>
+      <c r="D37" s="52">
+        <v>0.98</v>
+      </c>
+      <c r="E37" s="52">
+        <v>0.874</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="47">
+        <v>1920</v>
+      </c>
+      <c r="B38" s="49">
+        <v>45.5</v>
+      </c>
+      <c r="C38" s="49">
+        <v>28.8</v>
+      </c>
+      <c r="D38" s="52">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="E38" s="52">
+        <v>0.86299999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="47">
+        <v>1921</v>
+      </c>
+      <c r="B39" s="49">
+        <v>45.4</v>
+      </c>
+      <c r="C39" s="49">
+        <v>28.7</v>
+      </c>
+      <c r="D39" s="52">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="E39" s="52">
+        <v>0.85899999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="47">
+        <v>1922</v>
+      </c>
+      <c r="B40" s="49">
+        <v>45.2</v>
+      </c>
+      <c r="C40" s="49">
+        <v>28.5</v>
+      </c>
+      <c r="D40" s="52">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="E40" s="52">
+        <v>0.85099999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="47">
+        <v>1923</v>
+      </c>
+      <c r="B41" s="49">
+        <v>45</v>
+      </c>
+      <c r="C41" s="49">
+        <v>28.1</v>
+      </c>
+      <c r="D41" s="52">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="E41" s="52">
+        <v>0.84099999999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="47">
+        <v>1924</v>
+      </c>
+      <c r="B42" s="49">
+        <v>44.5</v>
+      </c>
+      <c r="C42" s="49">
+        <v>27.7</v>
+      </c>
+      <c r="D42" s="52">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="E42" s="52">
+        <v>0.82899999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="47">
+        <v>1925</v>
+      </c>
+      <c r="B43" s="49">
+        <v>44.7</v>
+      </c>
+      <c r="C43" s="49">
+        <v>27.3</v>
+      </c>
+      <c r="D43" s="52">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="E43" s="52">
+        <v>0.81799999999999995</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="47">
+        <v>1926</v>
+      </c>
+      <c r="B44" s="49">
+        <v>44.9</v>
+      </c>
+      <c r="C44" s="49">
+        <v>26.9</v>
+      </c>
+      <c r="D44" s="52">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="E44" s="52">
+        <v>0.80600000000000005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="47">
+        <v>1927</v>
+      </c>
+      <c r="B45" s="49">
+        <v>45.1</v>
+      </c>
+      <c r="C45" s="49">
+        <v>26.7</v>
+      </c>
+      <c r="D45" s="52">
+        <v>0.96899999999999997</v>
+      </c>
+      <c r="E45" s="52">
+        <v>0.79900000000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="47">
+        <v>1928</v>
+      </c>
+      <c r="B46" s="49">
+        <v>44.9</v>
+      </c>
+      <c r="C46" s="49">
+        <v>26.5</v>
+      </c>
+      <c r="D46" s="52">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="E46" s="52">
+        <v>0.79400000000000004</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="47">
+        <v>1929</v>
+      </c>
+      <c r="B47" s="49">
+        <v>44.9</v>
+      </c>
+      <c r="C47" s="49">
+        <v>26.6</v>
+      </c>
+      <c r="D47" s="52">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="E47" s="52">
+        <v>0.79600000000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="47">
+        <v>1930</v>
+      </c>
+      <c r="B48" s="49">
+        <v>44.7</v>
+      </c>
+      <c r="C48" s="49">
+        <v>26.6</v>
+      </c>
+      <c r="D48" s="52">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="E48" s="52">
+        <v>0.79500000000000004</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="47">
+        <v>1931</v>
+      </c>
+      <c r="B49" s="49">
+        <v>44.5</v>
+      </c>
+      <c r="C49" s="49">
+        <v>26.4</v>
+      </c>
+      <c r="D49" s="52">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="E49" s="52">
+        <v>0.78800000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="47">
+        <v>1932</v>
+      </c>
+      <c r="B50" s="49">
+        <v>44.2</v>
+      </c>
+      <c r="C50" s="49">
+        <v>25.7</v>
+      </c>
+      <c r="D50" s="52">
+        <v>0.95</v>
+      </c>
+      <c r="E50" s="52">
+        <v>0.76800000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="47">
+        <v>1933</v>
+      </c>
+      <c r="B51" s="49">
+        <v>43.8</v>
+      </c>
+      <c r="C51" s="49">
+        <v>24.8</v>
+      </c>
+      <c r="D51" s="52">
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="E51" s="52">
+        <v>0.74199999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="47">
+        <v>1934</v>
+      </c>
+      <c r="B52" s="49">
+        <v>43.5</v>
+      </c>
+      <c r="C52" s="49">
+        <v>24.3</v>
+      </c>
+      <c r="D52" s="52">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="E52" s="52">
+        <v>0.72699999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="47">
+        <v>1935</v>
+      </c>
+      <c r="B53" s="49">
+        <v>43.2</v>
+      </c>
+      <c r="C53" s="49">
+        <v>23.8</v>
+      </c>
+      <c r="D53" s="52">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="E53" s="52">
+        <v>0.71199999999999997</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="47">
+        <v>1936</v>
+      </c>
+      <c r="B54" s="49">
+        <v>42.8</v>
+      </c>
+      <c r="C54" s="49">
+        <v>23.3</v>
+      </c>
+      <c r="D54" s="52">
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="E54" s="52">
+        <v>0.69799999999999995</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="47">
+        <v>1937</v>
+      </c>
+      <c r="B55" s="49">
+        <v>43.4</v>
+      </c>
+      <c r="C55" s="49">
+        <v>23.3</v>
+      </c>
+      <c r="D55" s="52">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="E55" s="52">
+        <v>0.69599999999999995</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="47">
+        <v>1938</v>
+      </c>
+      <c r="B56" s="49">
+        <v>43.8</v>
+      </c>
+      <c r="C56" s="49">
+        <v>23.3</v>
+      </c>
+      <c r="D56" s="52">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="E56" s="52">
+        <v>0.69699999999999995</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="47">
+        <v>1939</v>
+      </c>
+      <c r="B57" s="49">
+        <v>44.1</v>
+      </c>
+      <c r="C57" s="49">
+        <v>23.2</v>
+      </c>
+      <c r="D57" s="52">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="E57" s="52">
+        <v>0.69399999999999995</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="47">
+        <v>1940</v>
+      </c>
+      <c r="B58" s="49">
+        <v>44.3</v>
+      </c>
+      <c r="C58" s="49">
+        <v>23</v>
+      </c>
+      <c r="D58" s="52">
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="E58" s="52">
+        <v>0.68799999999999994</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="47">
+        <v>1941</v>
+      </c>
+      <c r="B59" s="49">
+        <v>44.5</v>
+      </c>
+      <c r="C59" s="49">
+        <v>22.7</v>
+      </c>
+      <c r="D59" s="52">
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="E59" s="52">
+        <v>0.67900000000000005</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="47">
+        <v>1942</v>
+      </c>
+      <c r="B60" s="49">
+        <v>44.6</v>
+      </c>
+      <c r="C60" s="49">
+        <v>22.4</v>
+      </c>
+      <c r="D60" s="52">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="E60" s="52">
+        <v>0.66900000000000004</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="47">
+        <v>1943</v>
+      </c>
+      <c r="B61" s="49">
+        <v>44.7</v>
+      </c>
+      <c r="C61" s="49">
+        <v>21.9</v>
+      </c>
+      <c r="D61" s="52">
+        <v>0.96</v>
+      </c>
+      <c r="E61" s="52">
+        <v>0.65400000000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="47">
+        <v>1944</v>
+      </c>
+      <c r="B62" s="49">
+        <v>44.8</v>
+      </c>
+      <c r="C62" s="49">
+        <v>20.9</v>
+      </c>
+      <c r="D62" s="52">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="E62" s="52">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="47">
+        <v>1945</v>
+      </c>
+      <c r="B63" s="49">
+        <v>44.9</v>
+      </c>
+      <c r="C63" s="49">
+        <v>19.7</v>
+      </c>
+      <c r="D63" s="52">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="E63" s="52">
+        <v>0.58899999999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="47">
+        <v>1946</v>
+      </c>
+      <c r="B64" s="49">
+        <v>45.1</v>
+      </c>
+      <c r="C64" s="49">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D64" s="52">
+        <v>0.97</v>
+      </c>
+      <c r="E64" s="52">
+        <v>0.55700000000000005</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="47">
+        <v>1947</v>
+      </c>
+      <c r="B65" s="49">
+        <v>45.1</v>
+      </c>
+      <c r="C65" s="49">
+        <v>17.7</v>
+      </c>
+      <c r="D65" s="52">
+        <v>0.96899999999999997</v>
+      </c>
+      <c r="E65" s="52">
+        <v>0.52800000000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="47">
+        <v>1948</v>
+      </c>
+      <c r="B66" s="49">
+        <v>44.8</v>
+      </c>
+      <c r="C66" s="49">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D66" s="52">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="E66" s="52">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="47">
+        <v>1949</v>
+      </c>
+      <c r="B67" s="49">
+        <v>44.8</v>
+      </c>
+      <c r="C67" s="49">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D67" s="52">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="E67" s="52">
+        <v>0.50600000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="47">
+        <v>1950</v>
+      </c>
+      <c r="B68" s="49">
+        <v>45</v>
+      </c>
+      <c r="C68" s="49">
+        <v>16.8</v>
+      </c>
+      <c r="D68" s="52">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="E68" s="52">
+        <v>0.502</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="47">
+        <v>1951</v>
+      </c>
+      <c r="B69" s="49">
+        <v>45</v>
+      </c>
+      <c r="C69" s="49">
+        <v>16.5</v>
+      </c>
+      <c r="D69" s="52">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="E69" s="52">
+        <v>0.49299999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="47">
+        <v>1952</v>
+      </c>
+      <c r="B70" s="49">
+        <v>45.4</v>
+      </c>
+      <c r="C70" s="49">
+        <v>15.8</v>
+      </c>
+      <c r="D70" s="52">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="E70" s="52">
+        <v>0.47299999999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="47">
+        <v>1953</v>
+      </c>
+      <c r="B71" s="49">
+        <v>45.3</v>
+      </c>
+      <c r="C71" s="49">
+        <v>14.8</v>
+      </c>
+      <c r="D71" s="52">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="E71" s="52">
+        <v>0.441</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="47">
+        <v>1954</v>
+      </c>
+      <c r="B72" s="49">
+        <v>45.7</v>
+      </c>
+      <c r="C72" s="49">
+        <v>14.1</v>
+      </c>
+      <c r="D72" s="52">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="E72" s="52">
+        <v>0.42099999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="47">
+        <v>1955</v>
+      </c>
+      <c r="B73" s="49">
+        <v>46.1</v>
+      </c>
+      <c r="C73" s="49">
+        <v>13.3</v>
+      </c>
+      <c r="D73" s="52">
+        <v>0.99</v>
+      </c>
+      <c r="E73" s="52">
+        <v>0.39800000000000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="47">
+        <v>1956</v>
+      </c>
+      <c r="B74" s="49">
+        <v>46.3</v>
+      </c>
+      <c r="C74" s="49">
+        <v>13</v>
+      </c>
+      <c r="D74" s="52">
+        <v>0.995</v>
+      </c>
+      <c r="E74" s="52">
+        <v>0.38800000000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="47">
+        <v>1957</v>
+      </c>
+      <c r="B75" s="49">
+        <v>46.6</v>
+      </c>
+      <c r="C75" s="49">
+        <v>12.5</v>
+      </c>
+      <c r="D75" s="52">
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="E75" s="52">
+        <v>0.374</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="47">
+        <v>1958</v>
+      </c>
+      <c r="B76" s="49">
+        <v>46.5</v>
+      </c>
+      <c r="C76" s="49">
+        <v>12.4</v>
+      </c>
+      <c r="D76" s="52">
+        <v>1</v>
+      </c>
+      <c r="E76" s="52">
+        <v>0.36899999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="47">
+        <v>1959</v>
+      </c>
+      <c r="B77" s="49">
+        <v>46.3</v>
+      </c>
+      <c r="C77" s="49">
+        <v>11.9</v>
+      </c>
+      <c r="D77" s="52">
+        <v>0.996</v>
+      </c>
+      <c r="E77" s="52">
+        <v>0.35499999999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="47">
+        <v>1960</v>
+      </c>
+      <c r="B78" s="49">
+        <v>46.1</v>
+      </c>
+      <c r="C78" s="49">
+        <v>11.6</v>
+      </c>
+      <c r="D78" s="52">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="E78" s="52">
+        <v>0.34599999999999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="47">
+        <v>1961</v>
+      </c>
+      <c r="B79" s="49">
+        <v>46</v>
+      </c>
+      <c r="C79" s="49">
+        <v>11</v>
+      </c>
+      <c r="D79" s="52">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="E79" s="52">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="47">
+        <v>1962</v>
+      </c>
+      <c r="B80" s="49">
+        <v>45.9</v>
+      </c>
+      <c r="C80" s="49">
+        <v>10.7</v>
+      </c>
+      <c r="D80" s="52">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="E80" s="52">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="47">
+        <v>1963</v>
+      </c>
+      <c r="B81" s="49">
+        <v>45.8</v>
+      </c>
+      <c r="C81" s="49">
+        <v>10.5</v>
+      </c>
+      <c r="D81" s="52">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="E81" s="52">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="47">
+        <v>1964</v>
+      </c>
+      <c r="B82" s="49">
+        <v>45.8</v>
+      </c>
+      <c r="C82" s="49">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D82" s="52">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="E82" s="52">
+        <v>0.30399999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="47">
+        <v>1965</v>
+      </c>
+      <c r="B83" s="49">
+        <v>45.5</v>
+      </c>
+      <c r="C83" s="49">
+        <v>10</v>
+      </c>
+      <c r="D83" s="52">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="E83" s="52">
+        <v>0.29899999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="47">
+        <v>1966</v>
+      </c>
+      <c r="B84" s="49">
+        <v>45.3</v>
+      </c>
+      <c r="C84" s="49">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D84" s="52">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="E84" s="52">
+        <v>0.29299999999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="47">
+        <v>1967</v>
+      </c>
+      <c r="B85" s="49">
+        <v>44.7</v>
+      </c>
+      <c r="C85" s="49">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D85" s="52">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="E85" s="52">
+        <v>0.29299999999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="47">
+        <v>1968</v>
+      </c>
+      <c r="B86" s="49">
+        <v>44.3</v>
+      </c>
+      <c r="C86" s="49">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D86" s="52">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="E86" s="52">
+        <v>0.29199999999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="47">
+        <v>1969</v>
+      </c>
+      <c r="B87" s="49">
+        <v>44.4</v>
+      </c>
+      <c r="C87" s="49">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="D87" s="52">
+        <v>0.95399999999999996</v>
+      </c>
+      <c r="E87" s="52">
+        <v>0.28899999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="47">
+        <v>1970</v>
+      </c>
+      <c r="B88" s="49">
+        <v>44.3</v>
+      </c>
+      <c r="C88" s="49">
+        <v>9.5</v>
+      </c>
+      <c r="D88" s="52">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="E88" s="52">
+        <v>0.28399999999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="47">
+        <v>1971</v>
+      </c>
+      <c r="B89" s="49">
+        <v>44.1</v>
+      </c>
+      <c r="C89" s="49">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D89" s="52">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="E89" s="52">
+        <v>0.27400000000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="47">
+        <v>1972</v>
+      </c>
+      <c r="B90" s="49">
+        <v>43.8</v>
+      </c>
+      <c r="C90" s="49">
+        <v>8.6</v>
+      </c>
+      <c r="D90" s="52">
+        <v>0.94</v>
+      </c>
+      <c r="E90" s="52">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="47">
+        <v>1973</v>
+      </c>
+      <c r="B91" s="49">
+        <v>43.1</v>
+      </c>
+      <c r="C91" s="49">
+        <v>8.1</v>
+      </c>
+      <c r="D91" s="52">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="E91" s="52">
+        <v>0.24299999999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="47">
+        <v>1974</v>
+      </c>
+      <c r="B92" s="49">
+        <v>42.3</v>
+      </c>
+      <c r="C92" s="49">
+        <v>7.8</v>
+      </c>
+      <c r="D92" s="52">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="E92" s="52">
+        <v>0.23200000000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="47">
+        <v>1975</v>
+      </c>
+      <c r="B93" s="49">
+        <v>41.3</v>
+      </c>
+      <c r="C93" s="49">
+        <v>7.5</v>
+      </c>
+      <c r="D93" s="52">
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="E93" s="52">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="47">
+        <v>1976</v>
+      </c>
+      <c r="B94" s="49">
+        <v>40.4</v>
+      </c>
+      <c r="C94" s="49">
+        <v>7.2</v>
+      </c>
+      <c r="D94" s="52">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="E94" s="52">
+        <v>0.215</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="47">
+        <v>1977</v>
+      </c>
+      <c r="B95" s="49">
+        <v>39</v>
+      </c>
+      <c r="C95" s="49">
+        <v>7</v>
+      </c>
+      <c r="D95" s="52">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="E95" s="52">
+        <v>0.20799999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="47">
+        <v>1978</v>
+      </c>
+      <c r="B96" s="49">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="C96" s="49">
+        <v>6.8</v>
+      </c>
+      <c r="D96" s="52">
+        <v>0.81</v>
+      </c>
+      <c r="E96" s="52">
+        <v>0.20300000000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="47">
+        <v>1979</v>
+      </c>
+      <c r="B97" s="49">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C97" s="49">
+        <v>6.5</v>
+      </c>
+      <c r="D97" s="52">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="E97" s="52">
+        <v>0.19500000000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="47">
+        <v>1980</v>
+      </c>
+      <c r="B98" s="49">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="C98" s="49">
+        <v>6.2</v>
+      </c>
+      <c r="D98" s="52">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="E98" s="52">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="47">
+        <v>1981</v>
+      </c>
+      <c r="B99" s="49">
+        <v>35.4</v>
+      </c>
+      <c r="C99" s="49">
+        <v>6</v>
+      </c>
+      <c r="D99" s="52">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="E99" s="52">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="47">
+        <v>1982</v>
+      </c>
+      <c r="B100" s="49">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="C100" s="49">
+        <v>5.9</v>
+      </c>
+      <c r="D100" s="52">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="E100" s="52">
+        <v>0.17599999999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="47">
+        <v>1983</v>
+      </c>
+      <c r="B101" s="49">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="C101" s="49">
+        <v>5.7</v>
+      </c>
+      <c r="D101" s="52">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="E101" s="52">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="47">
+        <v>1984</v>
+      </c>
+      <c r="B102" s="49">
+        <v>35.4</v>
+      </c>
+      <c r="C102" s="49">
+        <v>5.6</v>
+      </c>
+      <c r="D102" s="52">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="E102" s="52">
+        <v>0.16600000000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="47">
+        <v>1985</v>
+      </c>
+      <c r="B103" s="49">
+        <v>35.1</v>
+      </c>
+      <c r="C103" s="49">
+        <v>5.4</v>
+      </c>
+      <c r="D103" s="52">
+        <v>0.755</v>
+      </c>
+      <c r="E103" s="52">
+        <v>0.16300000000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="47">
+        <v>1986</v>
+      </c>
+      <c r="B104" s="49">
+        <v>34.6</v>
+      </c>
+      <c r="C104" s="49">
+        <v>5.3</v>
+      </c>
+      <c r="D104" s="52">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="E104" s="52">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="47">
+        <v>1987</v>
+      </c>
+      <c r="B105" s="49">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="C105" s="49">
+        <v>5.3</v>
+      </c>
+      <c r="D105" s="52">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="E105" s="52">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="47">
+        <v>1988</v>
+      </c>
+      <c r="B106" s="49">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="C106" s="49">
+        <v>5.3</v>
+      </c>
+      <c r="D106" s="52">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="E106" s="52">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="47">
+        <v>1989</v>
+      </c>
+      <c r="B107" s="49">
+        <v>31.4</v>
+      </c>
+      <c r="C107" s="49">
+        <v>5.4</v>
+      </c>
+      <c r="D107" s="52">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="E107" s="52">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="47">
+        <v>1990</v>
+      </c>
+      <c r="B108" s="49">
+        <v>30.2</v>
+      </c>
+      <c r="C108" s="49">
+        <v>5.4</v>
+      </c>
+      <c r="D108" s="52">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="E108" s="52">
+        <v>0.16300000000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="47">
+        <v>1991</v>
+      </c>
+      <c r="B109" s="49">
+        <v>28.8</v>
+      </c>
+      <c r="C109" s="49">
+        <v>5.5</v>
+      </c>
+      <c r="D109" s="52">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="E109" s="52">
+        <v>0.16300000000000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="47">
+        <v>1992</v>
+      </c>
+      <c r="B110" s="49">
+        <v>27.6</v>
+      </c>
+      <c r="C110" s="49">
+        <v>5.4</v>
+      </c>
+      <c r="D110" s="52">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="E110" s="52">
+        <v>0.16200000000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="47">
+        <v>1993</v>
+      </c>
+      <c r="B111" s="49">
+        <v>26.5</v>
+      </c>
+      <c r="C111" s="49">
+        <v>5.4</v>
+      </c>
+      <c r="D111" s="52">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="E111" s="52">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="47">
+        <v>1994</v>
+      </c>
+      <c r="B112" s="49">
+        <v>25.9</v>
+      </c>
+      <c r="C112" s="49">
+        <v>5.3</v>
+      </c>
+      <c r="D112" s="52">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="E112" s="52">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="47">
+        <v>1995</v>
+      </c>
+      <c r="B113" s="49">
+        <v>25.5</v>
+      </c>
+      <c r="C113" s="49">
+        <v>5.2</v>
+      </c>
+      <c r="D113" s="52">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="E113" s="52">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="47">
+        <v>1996</v>
+      </c>
+      <c r="B114" s="49">
+        <v>25.3</v>
+      </c>
+      <c r="C114" s="49">
+        <v>5.2</v>
+      </c>
+      <c r="D114" s="52">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="E114" s="52">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="47">
+        <v>1997</v>
+      </c>
+      <c r="B115" s="49">
+        <v>24.9</v>
+      </c>
+      <c r="C115" s="49">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D115" s="52">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="E115" s="52">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="47">
+        <v>1998</v>
+      </c>
+      <c r="B116" s="49">
+        <v>24.4</v>
+      </c>
+      <c r="C116" s="49">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D116" s="52">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="E116" s="52">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="47">
+        <v>1999</v>
+      </c>
+      <c r="B117" s="49">
+        <v>23.9</v>
+      </c>
+      <c r="C117" s="49">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D117" s="52">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="E117" s="52">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="47">
+        <v>2000</v>
+      </c>
+      <c r="B118" s="49">
+        <v>23.4</v>
+      </c>
+      <c r="C118" s="49">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D118" s="52">
+        <v>0.504</v>
+      </c>
+      <c r="E118" s="52">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="47">
+        <v>2001</v>
+      </c>
+      <c r="B119" s="49">
+        <v>23</v>
+      </c>
+      <c r="C119" s="49">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D119" s="52">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="E119" s="52">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="47">
+        <v>2002</v>
+      </c>
+      <c r="B120" s="49">
+        <v>22.6</v>
+      </c>
+      <c r="C120" s="49">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D120" s="52">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="E120" s="52">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="47">
+        <v>2003</v>
+      </c>
+      <c r="B121" s="49">
+        <v>22.2</v>
+      </c>
+      <c r="C121" s="49">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D121" s="52">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="E121" s="52">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="47">
+        <v>2004</v>
+      </c>
+      <c r="B122" s="49">
+        <v>21.8</v>
+      </c>
+      <c r="C122" s="49">
+        <v>5.2</v>
+      </c>
+      <c r="D122" s="52">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="E122" s="52">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="47">
+        <v>2005</v>
+      </c>
+      <c r="B123" s="49">
+        <v>21.5</v>
+      </c>
+      <c r="C123" s="49">
+        <v>5.2</v>
+      </c>
+      <c r="D123" s="52">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="E123" s="52">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="47">
+        <v>2006</v>
+      </c>
+      <c r="B124" s="49">
+        <v>21.1</v>
+      </c>
+      <c r="C124" s="49">
+        <v>5.3</v>
+      </c>
+      <c r="D124" s="52">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="E124" s="52">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="47">
+        <v>2007</v>
+      </c>
+      <c r="B125" s="49">
+        <v>20.7</v>
+      </c>
+      <c r="C125" s="49">
+        <v>5.3</v>
+      </c>
+      <c r="D125" s="52">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="E125" s="52">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="47">
+        <v>2008</v>
+      </c>
+      <c r="B126" s="49">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="C126" s="49">
+        <v>5.4</v>
+      </c>
+      <c r="D126" s="52">
+        <v>0.438</v>
+      </c>
+      <c r="E126" s="52">
+        <v>0.16200000000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="47">
+        <v>2009</v>
+      </c>
+      <c r="B127" s="49">
+        <v>20</v>
+      </c>
+      <c r="C127" s="49">
+        <v>5.5</v>
+      </c>
+      <c r="D127" s="52">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="E127" s="52">
+        <v>0.16400000000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="47">
+        <v>2010</v>
+      </c>
+      <c r="B128" s="49">
+        <v>19.7</v>
+      </c>
+      <c r="C128" s="49">
+        <v>5.6</v>
+      </c>
+      <c r="D128" s="52">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="E128" s="52">
+        <v>0.16600000000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="47">
+        <v>2011</v>
+      </c>
+      <c r="B129" s="49">
+        <v>19.5</v>
+      </c>
+      <c r="C129" s="49">
+        <v>5.7</v>
+      </c>
+      <c r="D129" s="52">
+        <v>0.42</v>
+      </c>
+      <c r="E129" s="52">
+        <v>0.16900000000000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="47">
+        <v>2012</v>
+      </c>
+      <c r="B130" s="49">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="C130" s="49">
+        <v>5.7</v>
+      </c>
+      <c r="D130" s="52">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="E130" s="52">
+        <v>0.16900000000000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="47">
+        <v>2013</v>
+      </c>
+      <c r="B131" s="49">
+        <v>19.2</v>
+      </c>
+      <c r="C131" s="49">
+        <v>5.7</v>
+      </c>
+      <c r="D131" s="52">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="E131" s="52">
+        <v>0.16900000000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="47">
+        <v>2014</v>
+      </c>
+      <c r="B132" s="49">
+        <v>19</v>
+      </c>
+      <c r="C132" s="49">
+        <v>5.6</v>
+      </c>
+      <c r="D132" s="52">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="E132" s="52">
+        <v>0.16900000000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="47">
+        <v>2015</v>
+      </c>
+      <c r="B133" s="49">
+        <v>18.8</v>
+      </c>
+      <c r="C133" s="49">
+        <v>5.7</v>
+      </c>
+      <c r="D133" s="52">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="E133" s="52">
+        <v>0.16900000000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="47">
+        <v>2016</v>
+      </c>
+      <c r="B134" s="49">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="C134" s="49">
+        <v>5.7</v>
+      </c>
+      <c r="D134" s="52">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="E134" s="52">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="47">
+        <v>2017</v>
+      </c>
+      <c r="B135" s="49">
+        <v>18.3</v>
+      </c>
+      <c r="C135" s="49">
+        <v>5.8</v>
+      </c>
+      <c r="D135" s="52">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="E135" s="52">
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="47">
+        <v>2018</v>
+      </c>
+      <c r="B136" s="49">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="C136" s="49">
+        <v>5.9</v>
+      </c>
+      <c r="D136" s="52">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="E136" s="52">
+        <v>0.17599999999999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="47">
+        <v>2019</v>
+      </c>
+      <c r="B137" s="49">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="C137" s="49">
+        <v>6</v>
+      </c>
+      <c r="D137" s="52">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="E137" s="52">
+        <v>0.17899999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A7033F-364E-4376-9035-B6EA58466DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC02F08-EC53-4D85-B5F1-9106265ECF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="5" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
@@ -729,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -817,7 +817,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -826,27 +846,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1177,21 +1176,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.75">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8" t="s">
@@ -5421,7 +5420,7 @@
       <c r="J122" s="4"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="46" t="s">
+      <c r="A124" s="42" t="s">
         <v>25</v>
       </c>
     </row>
@@ -5429,11 +5428,11 @@
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
-      <c r="D126" s="40" t="s">
+      <c r="D126" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="40"/>
-      <c r="F126" s="40"/>
+      <c r="E126" s="46"/>
+      <c r="F126" s="46"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="8" t="s">
@@ -5661,21 +5660,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.75">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8" t="s">
@@ -9914,7 +9913,7 @@
       <c r="J122" s="4"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="46" t="s">
+      <c r="A124" s="42" t="s">
         <v>25</v>
       </c>
     </row>
@@ -9922,11 +9921,11 @@
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
-      <c r="D126" s="40" t="s">
+      <c r="D126" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="40"/>
-      <c r="F126" s="40"/>
+      <c r="E126" s="46"/>
+      <c r="F126" s="46"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="8" t="s">
@@ -10154,21 +10153,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.75">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8" t="s">
@@ -14428,7 +14427,7 @@
       <c r="J122" s="4"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="46" t="s">
+      <c r="A124" s="42" t="s">
         <v>25</v>
       </c>
     </row>
@@ -14436,11 +14435,11 @@
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
-      <c r="D126" s="40" t="s">
+      <c r="D126" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="40"/>
-      <c r="F126" s="40"/>
+      <c r="E126" s="46"/>
+      <c r="F126" s="46"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="8" t="s">
@@ -14667,21 +14666,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.399999999999999" x14ac:dyDescent="0.75">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8" t="s">
@@ -18940,7 +18939,7 @@
       <c r="J122" s="4"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="46" t="s">
+      <c r="A124" s="42" t="s">
         <v>25</v>
       </c>
     </row>
@@ -18948,11 +18947,11 @@
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
-      <c r="D126" s="40" t="s">
+      <c r="D126" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="E126" s="40"/>
-      <c r="F126" s="40"/>
+      <c r="E126" s="46"/>
+      <c r="F126" s="46"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="8" t="s">
@@ -19193,7 +19192,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.399999999999999" x14ac:dyDescent="0.75">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>121</v>
       </c>
     </row>
@@ -19203,16 +19202,16 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="45" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="S5" s="44" t="s">
+      <c r="S5" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
       <c r="W5" s="8"/>
       <c r="X5" s="8"/>
     </row>
@@ -19360,19 +19359,19 @@
         <v>2320.2072732914394</v>
       </c>
       <c r="V8" s="14">
-        <f ca="1">SUM(C8:R8) - S8</f>
-        <v>176641.3199955624</v>
+        <f ca="1">SUM(C8:R8) - SUM(S8:U8)</f>
+        <v>171833.54683073488</v>
       </c>
       <c r="W8" s="25">
         <v>148530</v>
       </c>
       <c r="X8" s="16">
         <f t="shared" ref="X8:X13" ca="1" si="0">100 * (V8-W8) / V8</f>
-        <v>15.914351181404564</v>
+        <v>13.561698085467622</v>
       </c>
       <c r="Y8" s="14">
         <f t="shared" ref="Y8:Y13" ca="1" si="1">V8-W8</f>
-        <v>28111.3199955624</v>
+        <v>23303.546830734878</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -19439,19 +19438,19 @@
         <v>2831.9073297187219</v>
       </c>
       <c r="V9" s="14">
-        <f t="shared" ref="V9:V16" ca="1" si="2">SUM(C9:R9) - S9</f>
-        <v>214421.42574317649</v>
+        <f t="shared" ref="V9:V16" ca="1" si="2">SUM(C9:R9) - SUM(S9:U9)</f>
+        <v>208594.26368724962</v>
       </c>
       <c r="W9" s="25">
         <v>162039</v>
       </c>
       <c r="X9" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>24.429660217779542</v>
+        <v>22.318573322347468</v>
       </c>
       <c r="Y9" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>52382.425743176485</v>
+        <v>46555.263687249622</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -19519,18 +19518,18 @@
       </c>
       <c r="V10" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>224979.43815776223</v>
+        <v>218909.86178425854</v>
       </c>
       <c r="W10" s="25">
         <v>167650</v>
       </c>
       <c r="X10" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>25.482078996730859</v>
+        <v>23.415967360473001</v>
       </c>
       <c r="Y10" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>57329.438157762226</v>
+        <v>51259.861784258537</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -19883,7 +19882,7 @@
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
-      <c r="R15" s="50">
+      <c r="R15" s="14">
         <f t="shared" si="3"/>
         <v>6707.7018392093914</v>
       </c>
@@ -20533,7 +20532,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20.399999999999999" x14ac:dyDescent="0.75">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>134</v>
       </c>
     </row>
@@ -20543,26 +20542,26 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="45" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52" t="s">
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="I5" s="52"/>
-      <c r="J5" s="44" t="s">
+      <c r="I5" s="48"/>
+      <c r="J5" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="K5" s="40"/>
+      <c r="K5" s="46"/>
     </row>
     <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="22" t="s">
@@ -20589,7 +20588,7 @@
       <c r="H6" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="I6" s="40" t="s">
         <v>71</v>
       </c>
       <c r="J6" s="24" t="s">
@@ -20630,7 +20629,7 @@
         <f t="array" aca="1" ref="F8" ca="1">INDIRECT("USSR!" &amp; ADDRESS(ROW(), COLUMN(), 4))</f>
         <v>12962.051806097428</v>
       </c>
-      <c r="G8" s="49" t="str">
+      <c r="G8" s="44" t="str">
         <f ca="1">"минус  " &amp; TEXT(SUM(USSR!S8:'USSR'!U8),"#,##0")</f>
         <v>минус  7,835</v>
       </c>
@@ -20641,7 +20640,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14">
         <f ca="1">USSR!V8</f>
-        <v>176641.3199955624</v>
+        <v>171833.54683073488</v>
       </c>
       <c r="K8" s="17">
         <f>USSR!W8</f>
@@ -20649,11 +20648,11 @@
       </c>
       <c r="L8" s="14">
         <f ca="1">USSR!X8</f>
-        <v>15.914351181404564</v>
+        <v>13.561698085467622</v>
       </c>
       <c r="M8" s="14">
         <f ca="1">USSR!Y8</f>
-        <v>28111.3199955624</v>
+        <v>23303.546830734878</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -20681,7 +20680,7 @@
         <f t="array" aca="1" ref="F9" ca="1">INDIRECT("USSR!" &amp; ADDRESS(ROW(), COLUMN(), 4))</f>
         <v>15820.711339210739</v>
       </c>
-      <c r="G9" s="49" t="str">
+      <c r="G9" s="44" t="str">
         <f ca="1">"минус  " &amp; TEXT(SUM(USSR!S9:'USSR'!U9),"#,##0")</f>
         <v>минус  9,587</v>
       </c>
@@ -20692,7 +20691,7 @@
       <c r="I9" s="14"/>
       <c r="J9" s="14">
         <f ca="1">USSR!V9</f>
-        <v>214421.42574317649</v>
+        <v>208594.26368724962</v>
       </c>
       <c r="K9" s="17">
         <f>USSR!W9</f>
@@ -20700,11 +20699,11 @@
       </c>
       <c r="L9" s="14">
         <f ca="1">USSR!X9</f>
-        <v>24.429660217779542</v>
+        <v>22.318573322347468</v>
       </c>
       <c r="M9" s="14">
         <f ca="1">USSR!Y9</f>
-        <v>52382.425743176485</v>
+        <v>46555.263687249622</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -20732,7 +20731,7 @@
         <f t="array" aca="1" ref="F10" ca="1">INDIRECT("USSR!" &amp; ADDRESS(ROW(), COLUMN(), 4))</f>
         <v>16500.649945916142</v>
       </c>
-      <c r="G10" s="49" t="str">
+      <c r="G10" s="44" t="str">
         <f ca="1">"минус  " &amp; TEXT(SUM(USSR!S10:'USSR'!U10),"#,##0")</f>
         <v>минус  10,007</v>
       </c>
@@ -20743,7 +20742,7 @@
       <c r="I10" s="14"/>
       <c r="J10" s="14">
         <f ca="1">USSR!V10</f>
-        <v>224979.43815776223</v>
+        <v>218909.86178425854</v>
       </c>
       <c r="K10" s="17">
         <f>USSR!W10</f>
@@ -20751,11 +20750,11 @@
       </c>
       <c r="L10" s="14">
         <f ca="1">USSR!X10</f>
-        <v>25.482078996730859</v>
+        <v>23.415967360473001</v>
       </c>
       <c r="M10" s="14">
         <f ca="1">USSR!Y10</f>
-        <v>57329.438157762226</v>
+        <v>51259.861784258537</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -20989,7 +20988,7 @@
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
-      <c r="I15" s="50">
+      <c r="I15" s="14">
         <f>USSR!R15</f>
         <v>6707.7018392093914</v>
       </c>
@@ -20997,7 +20996,7 @@
         <f ca="1">USSR!V15</f>
         <v>1984163.1718853214</v>
       </c>
-      <c r="K15" s="50">
+      <c r="K15" s="14">
         <f>USSR!W15</f>
         <v>198061</v>
       </c>
@@ -21062,7 +21061,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="H25" s="48"/>
+      <c r="H25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -21086,7 +21085,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.75">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="41" t="s">
         <v>100</v>
       </c>
     </row>
@@ -21112,20 +21111,20 @@
     </row>
     <row r="10" spans="1:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="11" spans="1:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41" t="s">
+      <c r="C11" s="49"/>
+      <c r="D11" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="41"/>
+      <c r="E11" s="49"/>
     </row>
     <row r="12" spans="1:5" ht="29.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="43"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="37" t="s">
         <v>103</v>
       </c>

--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DB2ECB-0FC4-47B5-BF2E-1FFBDD7D5BD5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39D5953-17E5-491F-9C4D-77E79510D153}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="170">
   <si>
     <t>год</t>
   </si>
@@ -576,6 +576,30 @@
 рождаемость 
 и смертность</t>
   </si>
+  <si>
+    <t>р</t>
+  </si>
+  <si>
+    <t>с</t>
+  </si>
+  <si>
+    <t>фактическая
+рождаемость и
+смертность (АДХ)</t>
+  </si>
+  <si>
+    <t>фактическая
+vs ожидаемая</t>
+  </si>
+  <si>
+    <t>среднее за 1929-1939</t>
+  </si>
+  <si>
+    <t>среднее за 1946-1958</t>
+  </si>
+  <si>
+    <t>ожидаемые</t>
+  </si>
 </sst>
 </file>
 
@@ -790,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -944,20 +968,24 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -974,10 +1002,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1292,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F5700B7-B2D0-432D-B154-E5245457325E}">
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:X148"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="17.140625" customWidth="1"/>
@@ -1307,38 +1350,49 @@
     <col min="15" max="15" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="37" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="72" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B3" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="69"/>
-      <c r="F3" s="69" t="s">
-        <v>132</v>
-      </c>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-    </row>
-    <row r="4" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="73" t="s">
+      <c r="C3" s="72"/>
+      <c r="D3" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+    </row>
+    <row r="4" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73" t="s">
+      <c r="E4" s="71"/>
+      <c r="F4" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-    </row>
-    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="Q4" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="81"/>
+      <c r="S4" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="T4" s="83"/>
+    </row>
+    <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
@@ -1381,8 +1435,20 @@
       <c r="O5" s="23" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q5" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="R5" s="82" t="s">
+        <v>164</v>
+      </c>
+      <c r="S5" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="T5" s="82" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1399,7 +1465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1917</v>
       </c>
@@ -1436,7 +1502,7 @@
         <v>-0.74484065934066768</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>A7+1</f>
         <v>1918</v>
@@ -1475,7 +1541,7 @@
         <v>-0.40053639971879551</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" ref="A9:A72" si="5">A8+1</f>
         <v>1919</v>
@@ -1514,7 +1580,7 @@
         <v>3.3518199226763068</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="5"/>
         <v>1920</v>
@@ -1553,7 +1619,7 @@
         <v>2.6757280349096129</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="5"/>
         <v>1921</v>
@@ -1592,7 +1658,7 @@
         <v>2.3475619836147046</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="5"/>
         <v>1922</v>
@@ -1628,7 +1694,7 @@
         <v>1.7607299999999988</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="5"/>
         <v>1923</v>
@@ -1664,7 +1730,7 @@
         <v>1.7861400000000018</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="5"/>
         <v>1924</v>
@@ -1700,7 +1766,7 @@
         <v>1.8211800000000087</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="5"/>
         <v>1925</v>
@@ -1736,7 +1802,7 @@
         <v>1.8512700000000046</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="5"/>
         <v>1926</v>
@@ -1772,7 +1838,7 @@
         <v>1.8830999999999887</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="5"/>
         <v>1927</v>
@@ -1810,7 +1876,7 @@
       <c r="M17" s="4">
         <v>93604</v>
       </c>
-      <c r="N17" s="80">
+      <c r="N17" s="70">
         <f>100*O17/F17</f>
         <v>12.460528599348768</v>
       </c>
@@ -1818,8 +1884,22 @@
         <f>F17-M17</f>
         <v>13323.764701242704</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q17" s="84">
+        <v>49.6</v>
+      </c>
+      <c r="R17" s="84">
+        <v>28.6</v>
+      </c>
+      <c r="S17" s="49">
+        <f>Q17/D17</f>
+        <v>1.0152180364946324</v>
+      </c>
+      <c r="T17" s="49">
+        <f>R17/E17</f>
+        <v>0.96112808207899392</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="5"/>
         <v>1928</v>
@@ -1857,7 +1937,7 @@
       <c r="M18" s="4">
         <v>95587</v>
       </c>
-      <c r="N18" s="80">
+      <c r="N18" s="70">
         <f t="shared" ref="N18:N31" si="7">100*O18/F18</f>
         <v>12.281413056681945</v>
       </c>
@@ -1865,8 +1945,22 @@
         <f t="shared" ref="O18:O31" si="8">F18-M18</f>
         <v>13383.063621483496</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q18" s="84">
+        <v>48.9</v>
+      </c>
+      <c r="R18" s="84">
+        <v>26.8</v>
+      </c>
+      <c r="S18" s="49">
+        <f t="shared" ref="S18:S30" si="9">Q18/D18</f>
+        <v>1.0029226272881095</v>
+      </c>
+      <c r="T18" s="49">
+        <f t="shared" ref="T18:T30" si="10">R18/E18</f>
+        <v>0.91344744609637551</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="5"/>
         <v>1929</v>
@@ -1904,7 +1998,7 @@
       <c r="M19" s="4">
         <v>97721</v>
       </c>
-      <c r="N19" s="80">
+      <c r="N19" s="70">
         <f t="shared" si="7"/>
         <v>12.031262779255171</v>
       </c>
@@ -1912,8 +2006,22 @@
         <f t="shared" si="8"/>
         <v>13365.055213891814</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q19" s="84">
+        <v>47</v>
+      </c>
+      <c r="R19" s="84">
+        <v>28.6</v>
+      </c>
+      <c r="S19" s="49">
+        <f t="shared" si="9"/>
+        <v>0.96689913390524385</v>
+      </c>
+      <c r="T19" s="49">
+        <f t="shared" si="10"/>
+        <v>0.9888631876661792</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="5"/>
         <v>1930</v>
@@ -1951,7 +2059,7 @@
       <c r="M20" s="4">
         <v>99566</v>
       </c>
-      <c r="N20" s="80">
+      <c r="N20" s="70">
         <f t="shared" si="7"/>
         <v>12.100850022630462</v>
       </c>
@@ -1959,8 +2067,22 @@
         <f t="shared" si="8"/>
         <v>13706.995274282177</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q20" s="84">
+        <v>43.9</v>
+      </c>
+      <c r="R20" s="84">
+        <v>27.3</v>
+      </c>
+      <c r="S20" s="49">
+        <f t="shared" si="9"/>
+        <v>0.90496804782519069</v>
+      </c>
+      <c r="T20" s="49">
+        <f t="shared" si="10"/>
+        <v>0.95881317893982654</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="5"/>
         <v>1931</v>
@@ -1998,7 +2120,7 @@
       <c r="M21" s="4">
         <v>101272</v>
       </c>
-      <c r="N21" s="80">
+      <c r="N21" s="70">
         <f t="shared" si="7"/>
         <v>12.351003308968776</v>
       </c>
@@ -2006,8 +2128,22 @@
         <f t="shared" si="8"/>
         <v>14270.680262491544</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q21" s="84">
+        <v>43.3</v>
+      </c>
+      <c r="R21" s="84">
+        <v>30.3</v>
+      </c>
+      <c r="S21" s="49">
+        <f t="shared" si="9"/>
+        <v>0.89259946402803547</v>
+      </c>
+      <c r="T21" s="49">
+        <f t="shared" si="10"/>
+        <v>1.0800059881520134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="5"/>
         <v>1932</v>
@@ -2045,7 +2181,7 @@
       <c r="M22" s="4">
         <v>102625</v>
       </c>
-      <c r="N22" s="80">
+      <c r="N22" s="70">
         <f t="shared" si="7"/>
         <v>12.960368301590124</v>
       </c>
@@ -2053,8 +2189,22 @@
         <f t="shared" si="8"/>
         <v>15281.059570188707</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q22" s="84">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="R22" s="84">
+        <v>29.8</v>
+      </c>
+      <c r="S22" s="49">
+        <f t="shared" si="9"/>
+        <v>0.81179897130817369</v>
+      </c>
+      <c r="T22" s="49">
+        <f t="shared" si="10"/>
+        <v>1.0757229544117275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="5"/>
         <v>1933</v>
@@ -2092,7 +2242,7 @@
       <c r="M23" s="4">
         <v>103648</v>
       </c>
-      <c r="N23" s="80">
+      <c r="N23" s="70">
         <f t="shared" si="7"/>
         <v>13.876239534652884</v>
       </c>
@@ -2100,8 +2250,22 @@
         <f t="shared" si="8"/>
         <v>16699.740786009876</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q23" s="84">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="R23" s="84">
+        <v>51</v>
+      </c>
+      <c r="S23" s="49">
+        <f t="shared" si="9"/>
+        <v>0.66925666925666927</v>
+      </c>
+      <c r="T23" s="49">
+        <f t="shared" si="10"/>
+        <v>1.8495751417100952</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="5"/>
         <v>1934</v>
@@ -2139,7 +2303,7 @@
       <c r="M24" s="4">
         <v>101763</v>
       </c>
-      <c r="N24" s="80">
+      <c r="N24" s="70">
         <f t="shared" si="7"/>
         <v>17.156451044346753</v>
       </c>
@@ -2147,8 +2311,22 @@
         <f t="shared" si="8"/>
         <v>21074.567056035317</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q24" s="84">
+        <v>28.7</v>
+      </c>
+      <c r="R24" s="84">
+        <v>26.1</v>
+      </c>
+      <c r="S24" s="49">
+        <f t="shared" si="9"/>
+        <v>0.5964999792160286</v>
+      </c>
+      <c r="T24" s="49">
+        <f t="shared" si="10"/>
+        <v>0.95544549018746505</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="5"/>
         <v>1935</v>
@@ -2186,7 +2364,7 @@
       <c r="M25" s="4">
         <v>102080</v>
       </c>
-      <c r="N25" s="80">
+      <c r="N25" s="70">
         <f t="shared" si="7"/>
         <v>18.591432506400697</v>
       </c>
@@ -2194,8 +2372,22 @@
         <f t="shared" si="8"/>
         <v>23312.207654342987</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q25" s="84">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="R25" s="84">
+        <v>23.6</v>
+      </c>
+      <c r="S25" s="49">
+        <f t="shared" si="9"/>
+        <v>0.72627097420485853</v>
+      </c>
+      <c r="T25" s="49">
+        <f t="shared" si="10"/>
+        <v>0.87420034745759567</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="5"/>
         <v>1936</v>
@@ -2233,7 +2425,7 @@
       <c r="M26" s="4">
         <v>103288</v>
       </c>
-      <c r="N26" s="80">
+      <c r="N26" s="70">
         <f t="shared" si="7"/>
         <v>19.315957361442283</v>
       </c>
@@ -2241,8 +2433,22 @@
         <f t="shared" si="8"/>
         <v>24727.400099251085</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q26" s="84">
+        <v>37.5</v>
+      </c>
+      <c r="R26" s="84">
+        <v>26.2</v>
+      </c>
+      <c r="S26" s="49">
+        <f t="shared" si="9"/>
+        <v>0.79244326106250795</v>
+      </c>
+      <c r="T26" s="49">
+        <f t="shared" si="10"/>
+        <v>0.98455895892284739</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="5"/>
         <v>1937</v>
@@ -2280,7 +2486,7 @@
       <c r="M27" s="4">
         <v>104520</v>
       </c>
-      <c r="N27" s="80">
+      <c r="N27" s="70">
         <f t="shared" si="7"/>
         <v>20.010248883390286</v>
       </c>
@@ -2288,8 +2494,22 @@
         <f t="shared" si="8"/>
         <v>26146.739852246683</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q27" s="84">
+        <v>41.5</v>
+      </c>
+      <c r="R27" s="84">
+        <v>26.2</v>
+      </c>
+      <c r="S27" s="49">
+        <f t="shared" si="9"/>
+        <v>0.87240774025373402</v>
+      </c>
+      <c r="T27" s="49">
+        <f t="shared" si="10"/>
+        <v>0.99779874932401036</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="5"/>
         <v>1938</v>
@@ -2327,7 +2547,7 @@
       <c r="M28" s="4">
         <v>106195</v>
       </c>
-      <c r="N28" s="80">
+      <c r="N28" s="70">
         <f t="shared" si="7"/>
         <v>20.424256224877411</v>
       </c>
@@ -2335,8 +2555,22 @@
         <f t="shared" si="8"/>
         <v>27256.470211955806</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q28" s="84">
+        <v>40.9</v>
+      </c>
+      <c r="R28" s="84">
+        <v>25.6</v>
+      </c>
+      <c r="S28" s="49">
+        <f t="shared" si="9"/>
+        <v>0.85534433360520312</v>
+      </c>
+      <c r="T28" s="49">
+        <f t="shared" si="10"/>
+        <v>0.98946375702480616</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="5"/>
         <v>1939</v>
@@ -2374,7 +2608,7 @@
       <c r="M29" s="4">
         <v>107893</v>
       </c>
-      <c r="N29" s="80">
+      <c r="N29" s="70">
         <f t="shared" si="7"/>
         <v>20.887950049799155</v>
       </c>
@@ -2382,8 +2616,22 @@
         <f t="shared" si="8"/>
         <v>28486.982654875057</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q29" s="84">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="R29" s="84">
+        <v>23.9</v>
+      </c>
+      <c r="S29" s="49">
+        <f t="shared" si="9"/>
+        <v>0.82976305886522606</v>
+      </c>
+      <c r="T29" s="49">
+        <f t="shared" si="10"/>
+        <v>0.93185017096916301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="5"/>
         <v>1940</v>
@@ -2421,7 +2669,7 @@
       <c r="M30" s="4">
         <v>109678</v>
       </c>
-      <c r="N30" s="80">
+      <c r="N30" s="70">
         <f t="shared" si="7"/>
         <v>21.334727040295608</v>
       </c>
@@ -2429,8 +2677,22 @@
         <f t="shared" si="8"/>
         <v>29745.656555773487</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q30" s="84">
+        <v>34.6</v>
+      </c>
+      <c r="R30" s="84">
+        <v>23.2</v>
+      </c>
+      <c r="S30" s="49">
+        <f t="shared" si="9"/>
+        <v>0.72434186423823732</v>
+      </c>
+      <c r="T30" s="49">
+        <f t="shared" si="10"/>
+        <v>0.91025369398212441</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="5"/>
         <v>1941</v>
@@ -2468,7 +2730,7 @@
       <c r="M31" s="4">
         <v>110988</v>
       </c>
-      <c r="N31" s="80">
+      <c r="N31" s="70">
         <f t="shared" si="7"/>
         <v>22.130094031553732</v>
       </c>
@@ -2476,8 +2738,12 @@
         <f t="shared" si="8"/>
         <v>31542.029566201789</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q31" s="85"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="86"/>
+      <c r="T31" s="86"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="5"/>
         <v>1942</v>
@@ -2516,9 +2782,13 @@
         <v>2.1481777383496192</v>
       </c>
       <c r="M32" s="4"/>
-      <c r="N32" s="80"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N32" s="70"/>
+      <c r="Q32" s="85"/>
+      <c r="R32" s="85"/>
+      <c r="S32" s="86"/>
+      <c r="T32" s="86"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="5"/>
         <v>1943</v>
@@ -2557,9 +2827,24 @@
         <v>2.1422468099558021</v>
       </c>
       <c r="M33" s="4"/>
-      <c r="N33" s="80"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N33" s="70"/>
+      <c r="Q33" s="85"/>
+      <c r="R33" s="85"/>
+      <c r="S33" s="87">
+        <f>AVERAGE(S19:S30)</f>
+        <v>0.80354945814742573</v>
+      </c>
+      <c r="T33" s="87">
+        <f>AVERAGE(T19:T30)</f>
+        <v>1.0497126348956545</v>
+      </c>
+      <c r="V33" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="W33" s="88"/>
+      <c r="X33" s="88"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="5"/>
         <v>1944</v>
@@ -2598,9 +2883,13 @@
         <v>2.1780151245122958</v>
       </c>
       <c r="M34" s="4"/>
-      <c r="N34" s="80"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N34" s="70"/>
+      <c r="Q34" s="85"/>
+      <c r="R34" s="85"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="86"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="5"/>
         <v>1945</v>
@@ -2636,9 +2925,13 @@
         <v>2.2761300000000073</v>
       </c>
       <c r="M35" s="4"/>
-      <c r="N35" s="80"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N35" s="70"/>
+      <c r="Q35" s="85"/>
+      <c r="R35" s="85"/>
+      <c r="S35" s="86"/>
+      <c r="T35" s="86"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="5"/>
         <v>1946</v>
@@ -2676,16 +2969,30 @@
       <c r="M36" s="4">
         <v>97548</v>
       </c>
-      <c r="N36" s="80">
-        <f t="shared" ref="N36:N99" si="9">100*O36/F36</f>
+      <c r="N36" s="70">
+        <f t="shared" ref="N36:N99" si="11">100*O36/F36</f>
         <v>38.595304259902612</v>
       </c>
       <c r="O36" s="4">
-        <f t="shared" ref="O36:O99" si="10">F36-M36</f>
+        <f t="shared" ref="O36:O99" si="12">F36-M36</f>
         <v>61312.814835535391</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q36" s="84">
+        <v>26</v>
+      </c>
+      <c r="R36" s="84">
+        <v>12.3</v>
+      </c>
+      <c r="S36" s="49">
+        <f t="shared" ref="S36:S48" si="13">Q36/D36</f>
+        <v>0.56236887072004837</v>
+      </c>
+      <c r="T36" s="49">
+        <f t="shared" ref="T36:T48" si="14">R36/E36</f>
+        <v>0.52706680893185409</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="5"/>
         <v>1947</v>
@@ -2723,16 +3030,30 @@
       <c r="M37" s="4">
         <v>98509</v>
       </c>
-      <c r="N37" s="80">
-        <f t="shared" si="9"/>
+      <c r="N37" s="70">
+        <f t="shared" si="11"/>
         <v>39.378382930630131</v>
       </c>
       <c r="O37" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>63989.139710254269</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q37" s="84">
+        <v>27.5</v>
+      </c>
+      <c r="R37" s="84">
+        <v>17</v>
+      </c>
+      <c r="S37" s="49">
+        <f t="shared" si="13"/>
+        <v>0.59801459155603398</v>
+      </c>
+      <c r="T37" s="49">
+        <f t="shared" si="14"/>
+        <v>0.7438132241240506</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="5"/>
         <v>1948</v>
@@ -2770,16 +3091,30 @@
       <c r="M38" s="4">
         <v>99159</v>
       </c>
-      <c r="N38" s="80">
-        <f t="shared" si="9"/>
+      <c r="N38" s="70">
+        <f t="shared" si="11"/>
         <v>40.35791760971496</v>
       </c>
       <c r="O38" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>67097.770431194367</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q38" s="84">
+        <v>25.2</v>
+      </c>
+      <c r="R38" s="84">
+        <v>13.1</v>
+      </c>
+      <c r="S38" s="49">
+        <f t="shared" si="13"/>
+        <v>0.55275885894778398</v>
+      </c>
+      <c r="T38" s="49">
+        <f t="shared" si="14"/>
+        <v>0.58467004079300899</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="5"/>
         <v>1949</v>
@@ -2817,16 +3152,30 @@
       <c r="M39" s="4">
         <v>100252</v>
       </c>
-      <c r="N39" s="80">
-        <f t="shared" si="9"/>
+      <c r="N39" s="70">
+        <f t="shared" si="11"/>
         <v>41.066790619902754</v>
       </c>
       <c r="O39" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>69859.217519840051</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q39" s="84">
+        <v>30.5</v>
+      </c>
+      <c r="R39" s="84">
+        <v>11.7</v>
+      </c>
+      <c r="S39" s="49">
+        <f t="shared" si="13"/>
+        <v>0.66040902053763784</v>
+      </c>
+      <c r="T39" s="49">
+        <f t="shared" si="14"/>
+        <v>0.52368675475346438</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="5"/>
         <v>1950</v>
@@ -2864,16 +3213,30 @@
       <c r="M40" s="4">
         <v>102067</v>
       </c>
-      <c r="N40" s="80">
-        <f t="shared" si="9"/>
+      <c r="N40" s="70">
+        <f t="shared" si="11"/>
         <v>41.397047318762247</v>
       </c>
       <c r="O40" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>72099.992156826309</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q40" s="84">
+        <v>27.8</v>
+      </c>
+      <c r="R40" s="84">
+        <v>11.5</v>
+      </c>
+      <c r="S40" s="49">
+        <f t="shared" si="13"/>
+        <v>0.59619550065409943</v>
+      </c>
+      <c r="T40" s="49">
+        <f t="shared" si="14"/>
+        <v>0.51399634392165805</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="5"/>
         <v>1951</v>
@@ -2911,16 +3274,30 @@
       <c r="M41" s="4">
         <v>103599</v>
       </c>
-      <c r="N41" s="80">
-        <f t="shared" si="9"/>
+      <c r="N41" s="70">
+        <f t="shared" si="11"/>
         <v>41.926033224085145</v>
       </c>
       <c r="O41" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>74792.464801687776</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q41" s="84">
+        <v>28.1</v>
+      </c>
+      <c r="R41" s="84">
+        <v>11.6</v>
+      </c>
+      <c r="S41" s="49">
+        <f t="shared" si="13"/>
+        <v>0.59881515577718114</v>
+      </c>
+      <c r="T41" s="49">
+        <f t="shared" si="14"/>
+        <v>0.52070708430965906</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="5"/>
         <v>1952</v>
@@ -2958,16 +3335,30 @@
       <c r="M42" s="4">
         <v>105278</v>
       </c>
-      <c r="N42" s="80">
-        <f t="shared" si="9"/>
+      <c r="N42" s="70">
+        <f t="shared" si="11"/>
         <v>42.404493303369634</v>
       </c>
       <c r="O42" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>77510.564660998643</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q42" s="84">
+        <v>27.6</v>
+      </c>
+      <c r="R42" s="84">
+        <v>10.7</v>
+      </c>
+      <c r="S42" s="49">
+        <f t="shared" si="13"/>
+        <v>0.58507424719386947</v>
+      </c>
+      <c r="T42" s="49">
+        <f t="shared" si="14"/>
+        <v>0.48449612403100778</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="5"/>
         <v>1953</v>
@@ -3005,16 +3396,30 @@
       <c r="M43" s="4">
         <v>107049</v>
       </c>
-      <c r="N43" s="80">
-        <f t="shared" si="9"/>
+      <c r="N43" s="70">
+        <f t="shared" si="11"/>
         <v>42.868957889097636</v>
       </c>
       <c r="O43" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>80325.492123209056</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q43" s="84">
+        <v>26.2</v>
+      </c>
+      <c r="R43" s="84">
+        <v>10.4</v>
+      </c>
+      <c r="S43" s="49">
+        <f t="shared" si="13"/>
+        <v>0.5530751612256315</v>
+      </c>
+      <c r="T43" s="49">
+        <f t="shared" si="14"/>
+        <v>0.47715396014846823</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="5"/>
         <v>1954</v>
@@ -3052,16 +3457,30 @@
       <c r="M44" s="4">
         <v>108607</v>
       </c>
-      <c r="N44" s="80">
-        <f t="shared" si="9"/>
+      <c r="N44" s="70">
+        <f t="shared" si="11"/>
         <v>43.482926053349196</v>
       </c>
       <c r="O44" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>83559.707183955412</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q44" s="84">
+        <v>27.8</v>
+      </c>
+      <c r="R44" s="84">
+        <v>10.3</v>
+      </c>
+      <c r="S44" s="49">
+        <f t="shared" si="13"/>
+        <v>0.58562686299912581</v>
+      </c>
+      <c r="T44" s="49">
+        <f t="shared" si="14"/>
+        <v>0.47962970723961462</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="5"/>
         <v>1955</v>
@@ -3099,16 +3518,30 @@
       <c r="M45" s="4">
         <v>110678</v>
       </c>
-      <c r="N45" s="80">
-        <f t="shared" si="9"/>
+      <c r="N45" s="70">
+        <f t="shared" si="11"/>
         <v>43.864492167097474</v>
       </c>
       <c r="O45" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>86484.196037226648</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q45" s="84">
+        <v>26.4</v>
+      </c>
+      <c r="R45" s="84">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="S45" s="49">
+        <f t="shared" si="13"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="T45" s="49">
+        <f t="shared" si="14"/>
+        <v>0.44299637028780475</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="5"/>
         <v>1956</v>
@@ -3146,16 +3579,30 @@
       <c r="M46" s="4">
         <v>112465</v>
       </c>
-      <c r="N46" s="80">
-        <f t="shared" si="9"/>
+      <c r="N46" s="70">
+        <f t="shared" si="11"/>
         <v>44.432157726762689</v>
       </c>
       <c r="O46" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>89927.238746627729</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q46" s="84">
+        <v>24.9</v>
+      </c>
+      <c r="R46" s="84">
+        <v>8.4</v>
+      </c>
+      <c r="S46" s="49">
+        <f t="shared" si="13"/>
+        <v>0.52235753170332599</v>
+      </c>
+      <c r="T46" s="49">
+        <f t="shared" si="14"/>
+        <v>0.41869158878504675</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="5"/>
         <v>1957</v>
@@ -3193,16 +3640,30 @@
       <c r="M47" s="4">
         <v>114189</v>
       </c>
-      <c r="N47" s="80">
-        <f t="shared" si="9"/>
+      <c r="N47" s="70">
+        <f t="shared" si="11"/>
         <v>45.096025526303521</v>
       </c>
       <c r="O47" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>93790.478889467136</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q47" s="84">
+        <v>25</v>
+      </c>
+      <c r="R47" s="84">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="S47" s="49">
+        <f t="shared" si="13"/>
+        <v>0.52336839901606746</v>
+      </c>
+      <c r="T47" s="49">
+        <f t="shared" si="14"/>
+        <v>0.46543854360048453</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="5"/>
         <v>1958</v>
@@ -3240,16 +3701,30 @@
       <c r="M48" s="4">
         <v>115881</v>
       </c>
-      <c r="N48" s="80">
-        <f t="shared" si="9"/>
+      <c r="N48" s="70">
+        <f t="shared" si="11"/>
         <v>45.845417469063001</v>
       </c>
       <c r="O48" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>98100.891437904473</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q48" s="84">
+        <v>24.5</v>
+      </c>
+      <c r="R48" s="84">
+        <v>8</v>
+      </c>
+      <c r="S48" s="49">
+        <f t="shared" si="13"/>
+        <v>0.51025721128813917</v>
+      </c>
+      <c r="T48" s="49">
+        <f t="shared" si="14"/>
+        <v>0.44743480036018496</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="5"/>
         <v>1959</v>
@@ -3287,16 +3762,16 @@
       <c r="M49" s="4">
         <v>117616</v>
       </c>
-      <c r="N49" s="80">
-        <f t="shared" si="9"/>
+      <c r="N49" s="70">
+        <f t="shared" si="11"/>
         <v>46.642544134430864</v>
       </c>
       <c r="O49" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>102814.29993095316</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="5"/>
         <v>1960</v>
@@ -3334,16 +3809,29 @@
       <c r="M50" s="4">
         <v>119046</v>
       </c>
-      <c r="N50" s="80">
-        <f t="shared" si="9"/>
+      <c r="N50" s="70">
+        <f t="shared" si="11"/>
         <v>47.618513835288638</v>
       </c>
       <c r="O50" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>108221.32041482156</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S50" s="89">
+        <f>AVERAGE(S36:S48)</f>
+        <v>0.56952899747496155</v>
+      </c>
+      <c r="T50" s="89">
+        <f>AVERAGE(T36:T48)</f>
+        <v>0.50998318086817729</v>
+      </c>
+      <c r="V50" s="88" t="s">
+        <v>168</v>
+      </c>
+      <c r="W50" s="88"/>
+      <c r="X50" s="88"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="5"/>
         <v>1961</v>
@@ -3381,16 +3869,16 @@
       <c r="M51" s="4">
         <v>120766</v>
       </c>
-      <c r="N51" s="80">
-        <f t="shared" si="9"/>
+      <c r="N51" s="70">
+        <f t="shared" si="11"/>
         <v>48.458277982530177</v>
       </c>
       <c r="O51" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>113541.26656565128</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="5"/>
         <v>1962</v>
@@ -3428,16 +3916,16 @@
       <c r="M52" s="4">
         <v>122407</v>
       </c>
-      <c r="N52" s="80">
-        <f t="shared" si="9"/>
+      <c r="N52" s="70">
+        <f t="shared" si="11"/>
         <v>49.349648462974308</v>
       </c>
       <c r="O52" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>119263.5832940168</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="5"/>
         <v>1963</v>
@@ -3475,16 +3963,16 @@
       <c r="M53" s="4">
         <v>123848</v>
       </c>
-      <c r="N53" s="80">
-        <f t="shared" si="9"/>
+      <c r="N53" s="70">
+        <f t="shared" si="11"/>
         <v>50.32811994348851</v>
       </c>
       <c r="O53" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>125484.21746207037</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="5"/>
         <v>1964</v>
@@ -3522,16 +4010,16 @@
       <c r="M54" s="4">
         <v>125179</v>
       </c>
-      <c r="N54" s="80">
-        <f t="shared" si="9"/>
+      <c r="N54" s="70">
+        <f t="shared" si="11"/>
         <v>51.353002210553043</v>
       </c>
       <c r="O54" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>132142.12090821605</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="5"/>
         <v>1965</v>
@@ -3569,16 +4057,16 @@
       <c r="M55" s="4">
         <v>126309</v>
       </c>
-      <c r="N55" s="80">
-        <f t="shared" si="9"/>
+      <c r="N55" s="70">
+        <f t="shared" si="11"/>
         <v>52.487877066074084</v>
       </c>
       <c r="O55" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>139536.83512644807</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="5"/>
         <v>1966</v>
@@ -3616,16 +4104,16 @@
       <c r="M56" s="4">
         <v>127189</v>
       </c>
-      <c r="N56" s="80">
-        <f t="shared" si="9"/>
+      <c r="N56" s="70">
+        <f t="shared" si="11"/>
         <v>53.730368032860341</v>
       </c>
       <c r="O56" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>147697.56077992724</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="5"/>
         <v>1967</v>
@@ -3663,16 +4151,16 @@
       <c r="M57" s="4">
         <v>128026</v>
       </c>
-      <c r="N57" s="80">
-        <f t="shared" si="9"/>
+      <c r="N57" s="70">
+        <f t="shared" si="11"/>
         <v>55.004974705972039</v>
       </c>
       <c r="O57" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>156507.67714184272</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58">
         <f t="shared" si="5"/>
         <v>1968</v>
@@ -3710,16 +4198,16 @@
       <c r="M58" s="4">
         <v>128696</v>
       </c>
-      <c r="N58" s="80">
-        <f t="shared" si="9"/>
+      <c r="N58" s="70">
+        <f t="shared" si="11"/>
         <v>56.350874595024692</v>
       </c>
       <c r="O58" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>166146.10463774996</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59">
         <f t="shared" si="5"/>
         <v>1969</v>
@@ -3757,16 +4245,16 @@
       <c r="M59" s="4">
         <v>129379</v>
       </c>
-      <c r="N59" s="80">
-        <f t="shared" si="9"/>
+      <c r="N59" s="70">
+        <f t="shared" si="11"/>
         <v>57.67662793195688</v>
       </c>
       <c r="O59" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>176312.61595157848</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60">
         <f t="shared" si="5"/>
         <v>1970</v>
@@ -3804,16 +4292,16 @@
       <c r="M60" s="4">
         <v>129941</v>
       </c>
-      <c r="N60" s="80">
-        <f t="shared" si="9"/>
+      <c r="N60" s="70">
+        <f t="shared" si="11"/>
         <v>59.03092940674852</v>
       </c>
       <c r="O60" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>187227.53255002614</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61">
         <f t="shared" si="5"/>
         <v>1971</v>
@@ -3851,16 +4339,16 @@
       <c r="M61" s="4">
         <v>130563</v>
       </c>
-      <c r="N61" s="80">
-        <f t="shared" si="9"/>
+      <c r="N61" s="70">
+        <f t="shared" si="11"/>
         <v>60.328647888313057</v>
       </c>
       <c r="O61" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>198548.54536005063</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62">
         <f t="shared" si="5"/>
         <v>1972</v>
@@ -3898,16 +4386,16 @@
       <c r="M62" s="4">
         <v>131304</v>
       </c>
-      <c r="N62" s="80">
-        <f t="shared" si="9"/>
+      <c r="N62" s="70">
+        <f t="shared" si="11"/>
         <v>61.560599399865204</v>
       </c>
       <c r="O62" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>210283.01215424138</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63">
         <f t="shared" si="5"/>
         <v>1973</v>
@@ -3945,16 +4433,16 @@
       <c r="M63" s="4">
         <v>132069</v>
       </c>
-      <c r="N63" s="80">
-        <f t="shared" si="9"/>
+      <c r="N63" s="70">
+        <f t="shared" si="11"/>
         <v>62.75019656491223</v>
       </c>
       <c r="O63" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>222480.52193276933</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64">
         <f t="shared" si="5"/>
         <v>1974</v>
@@ -3992,12 +4480,12 @@
       <c r="M64" s="4">
         <v>132799</v>
       </c>
-      <c r="N64" s="80">
-        <f t="shared" si="9"/>
+      <c r="N64" s="70">
+        <f t="shared" si="11"/>
         <v>63.928109394423799</v>
       </c>
       <c r="O64" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>235351.9279679152</v>
       </c>
     </row>
@@ -4039,12 +4527,12 @@
       <c r="M65" s="4">
         <v>133634</v>
       </c>
-      <c r="N65" s="80">
-        <f t="shared" si="9"/>
+      <c r="N65" s="70">
+        <f t="shared" si="11"/>
         <v>65.048169047578895</v>
       </c>
       <c r="O65" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>248703.6239771588</v>
       </c>
     </row>
@@ -4086,12 +4574,12 @@
       <c r="M66" s="4">
         <v>134549</v>
       </c>
-      <c r="N66" s="80">
-        <f t="shared" si="9"/>
+      <c r="N66" s="70">
+        <f t="shared" si="11"/>
         <v>66.118725555066305</v>
       </c>
       <c r="O66" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>262570.06415645254</v>
       </c>
     </row>
@@ -4133,12 +4621,12 @@
       <c r="M67" s="4">
         <v>135504</v>
       </c>
-      <c r="N67" s="80">
-        <f t="shared" si="9"/>
+      <c r="N67" s="70">
+        <f t="shared" si="11"/>
         <v>67.157447793225813</v>
       </c>
       <c r="O67" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>277082.69285772071</v>
       </c>
     </row>
@@ -4180,12 +4668,12 @@
       <c r="M68" s="4">
         <v>136455</v>
       </c>
-      <c r="N68" s="80">
-        <f t="shared" si="9"/>
+      <c r="N68" s="70">
+        <f t="shared" si="11"/>
         <v>68.161139628853476</v>
       </c>
       <c r="O68" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>292125.03838498023</v>
       </c>
     </row>
@@ -4227,12 +4715,12 @@
       <c r="M69" s="4">
         <v>137410</v>
       </c>
-      <c r="N69" s="80">
-        <f t="shared" si="9"/>
+      <c r="N69" s="70">
+        <f t="shared" si="11"/>
         <v>69.13459818854372</v>
       </c>
       <c r="O69" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>307781.02922871296</v>
       </c>
     </row>
@@ -4274,12 +4762,12 @@
       <c r="M70" s="4">
         <v>138127</v>
       </c>
-      <c r="N70" s="80">
-        <f t="shared" si="9"/>
+      <c r="N70" s="70">
+        <f t="shared" si="11"/>
         <v>70.114114636549346</v>
       </c>
       <c r="O70" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>324054.38870640338</v>
       </c>
     </row>
@@ -4321,12 +4809,12 @@
       <c r="M71" s="4">
         <v>138839</v>
       </c>
-      <c r="N71" s="80">
-        <f t="shared" si="9"/>
+      <c r="N71" s="70">
+        <f t="shared" si="11"/>
         <v>71.052840976641747</v>
       </c>
       <c r="O71" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>340790.10587518109</v>
       </c>
     </row>
@@ -4342,11 +4830,11 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="D72" s="3">
-        <f t="shared" ref="D72:D121" si="11">B72*$D$6</f>
+        <f t="shared" ref="D72:D121" si="15">B72*$D$6</f>
         <v>47.0745</v>
       </c>
       <c r="E72" s="3">
-        <f t="shared" ref="E72:E121" si="12">C72*$E$6</f>
+        <f t="shared" ref="E72:E121" si="16">C72*$E$6</f>
         <v>9.1163999999999987</v>
       </c>
       <c r="F72" s="4">
@@ -4354,32 +4842,32 @@
         <v>497829.15988963132</v>
       </c>
       <c r="G72" s="4">
-        <f t="shared" ref="G72:G121" si="13">F72*D72/1000</f>
+        <f t="shared" ref="G72:G121" si="17">F72*D72/1000</f>
         <v>23435.05878722445</v>
       </c>
       <c r="H72" s="4">
-        <f t="shared" ref="H72:H121" si="14">E72*F72/1000</f>
+        <f t="shared" ref="H72:H121" si="18">E72*F72/1000</f>
         <v>4538.4097532178339</v>
       </c>
       <c r="J72" s="6">
-        <f t="shared" ref="J72:J129" si="15">100 *(F73-F72) / F72</f>
+        <f t="shared" ref="J72:J129" si="19">100 *(F73-F72) / F72</f>
         <v>3.7958100000000048</v>
       </c>
       <c r="M72" s="4">
         <v>139604</v>
       </c>
-      <c r="N72" s="80">
-        <f t="shared" si="9"/>
+      <c r="N72" s="70">
+        <f t="shared" si="11"/>
         <v>71.957448207543692</v>
       </c>
       <c r="O72" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>358225.15988963132</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
-        <f t="shared" ref="A73:A122" si="16">A72+1</f>
+        <f t="shared" ref="A73:A122" si="20">A72+1</f>
         <v>1983</v>
       </c>
       <c r="B73" s="2">
@@ -4389,44 +4877,44 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="D73" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>46.8765</v>
       </c>
       <c r="E73" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>8.7954000000000008</v>
       </c>
       <c r="F73" s="4">
-        <f t="shared" ref="F73:F121" si="17">F72+G72-H72+I72</f>
+        <f t="shared" ref="F73:F121" si="21">F72+G72-H72+I72</f>
         <v>516725.80892363796</v>
       </c>
       <c r="G73" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>24222.297382008914</v>
       </c>
       <c r="H73" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4544.8101798069656</v>
       </c>
       <c r="J73" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.8081099999999815</v>
       </c>
       <c r="M73" s="4">
         <v>140530</v>
       </c>
-      <c r="N73" s="80">
-        <f t="shared" si="9"/>
+      <c r="N73" s="70">
+        <f t="shared" si="11"/>
         <v>72.803758284740979</v>
       </c>
       <c r="O73" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>376195.80892363796</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1984</v>
       </c>
       <c r="B74" s="2">
@@ -4436,44 +4924,44 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="D74" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>46.529999999999994</v>
       </c>
       <c r="E74" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>8.2176000000000009</v>
       </c>
       <c r="F74" s="4">
+        <f t="shared" si="21"/>
+        <v>536403.29612583981</v>
+      </c>
+      <c r="G74" s="4">
         <f t="shared" si="17"/>
-        <v>536403.29612583981</v>
-      </c>
-      <c r="G74" s="4">
-        <f t="shared" si="13"/>
         <v>24958.845368735325</v>
       </c>
       <c r="H74" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4407.9477262437022</v>
       </c>
       <c r="J74" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.8312399999999989</v>
       </c>
       <c r="M74" s="4">
         <v>141583</v>
       </c>
-      <c r="N74" s="80">
-        <f t="shared" si="9"/>
+      <c r="N74" s="70">
+        <f t="shared" si="11"/>
         <v>73.605121179795148</v>
       </c>
       <c r="O74" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>394820.29612583981</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1985</v>
       </c>
       <c r="B75" s="2">
@@ -4483,44 +4971,44 @@
         <v>0.24299999999999999</v>
       </c>
       <c r="D75" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>45.886500000000005</v>
       </c>
       <c r="E75" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>7.8003</v>
       </c>
       <c r="F75" s="4">
+        <f t="shared" si="21"/>
+        <v>556954.19376833143</v>
+      </c>
+      <c r="G75" s="4">
         <f t="shared" si="17"/>
-        <v>556954.19376833143</v>
-      </c>
-      <c r="G75" s="4">
-        <f t="shared" si="13"/>
         <v>25556.678612350541</v>
       </c>
       <c r="H75" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4344.4097976511157</v>
       </c>
       <c r="J75" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.808619999999991</v>
       </c>
       <c r="M75" s="4">
         <v>142539</v>
       </c>
-      <c r="N75" s="80">
-        <f t="shared" si="9"/>
+      <c r="N75" s="70">
+        <f t="shared" si="11"/>
         <v>74.407410592317035</v>
       </c>
       <c r="O75" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>414415.19376833143</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1986</v>
       </c>
       <c r="B76" s="2">
@@ -4530,44 +5018,44 @@
         <v>0.23200000000000001</v>
       </c>
       <c r="D76" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>44.9955</v>
       </c>
       <c r="E76" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>7.4472000000000005</v>
       </c>
       <c r="F76" s="4">
+        <f t="shared" si="21"/>
+        <v>578166.46258303081</v>
+      </c>
+      <c r="G76" s="4">
         <f t="shared" si="17"/>
-        <v>578166.46258303081</v>
-      </c>
-      <c r="G76" s="4">
-        <f t="shared" si="13"/>
         <v>26014.88906715476</v>
       </c>
       <c r="H76" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4305.7212801483465</v>
       </c>
       <c r="J76" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.7548299999999899</v>
       </c>
       <c r="M76" s="4">
         <v>143528</v>
       </c>
-      <c r="N76" s="80">
-        <f t="shared" si="9"/>
+      <c r="N76" s="70">
+        <f t="shared" si="11"/>
         <v>75.175315538232582</v>
       </c>
       <c r="O76" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>434638.46258303081</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1987</v>
       </c>
       <c r="B77" s="2">
@@ -4577,44 +5065,44 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="D77" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>43.906500000000001</v>
       </c>
       <c r="E77" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>7.2225000000000001</v>
       </c>
       <c r="F77" s="4">
+        <f t="shared" si="21"/>
+        <v>599875.63037003716</v>
+      </c>
+      <c r="G77" s="4">
         <f t="shared" si="17"/>
-        <v>599875.63037003716</v>
-      </c>
-      <c r="G77" s="4">
-        <f t="shared" si="13"/>
         <v>26338.439364842037</v>
       </c>
       <c r="H77" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4332.6017403475935</v>
       </c>
       <c r="J77" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.6684000000000014</v>
       </c>
       <c r="M77" s="4">
         <v>144784</v>
       </c>
-      <c r="N77" s="80">
-        <f t="shared" si="9"/>
+      <c r="N77" s="70">
+        <f t="shared" si="11"/>
         <v>75.864330426177006</v>
       </c>
       <c r="O77" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>455091.63037003716</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1988</v>
       </c>
       <c r="B78" s="2">
@@ -4624,44 +5112,44 @@
         <v>0.215</v>
       </c>
       <c r="D78" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>42.966000000000001</v>
       </c>
       <c r="E78" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>6.9015000000000004</v>
       </c>
       <c r="F78" s="4">
+        <f t="shared" si="21"/>
+        <v>621881.46799453162</v>
+      </c>
+      <c r="G78" s="4">
         <f t="shared" si="17"/>
-        <v>621881.46799453162</v>
-      </c>
-      <c r="G78" s="4">
-        <f t="shared" si="13"/>
         <v>26719.759153853047</v>
       </c>
       <c r="H78" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4291.9149513642606</v>
       </c>
       <c r="J78" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.6064499999999988</v>
       </c>
       <c r="M78" s="4">
         <v>145988</v>
       </c>
-      <c r="N78" s="80">
-        <f t="shared" si="9"/>
+      <c r="N78" s="70">
+        <f t="shared" si="11"/>
         <v>76.52478687445246</v>
       </c>
       <c r="O78" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>475893.46799453162</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1989</v>
       </c>
       <c r="B79" s="2">
@@ -4671,44 +5159,44 @@
         <v>0.20799999999999999</v>
       </c>
       <c r="D79" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>41.481000000000002</v>
       </c>
       <c r="E79" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>6.6768000000000001</v>
       </c>
       <c r="F79" s="4">
+        <f t="shared" si="21"/>
+        <v>644309.31219702039</v>
+      </c>
+      <c r="G79" s="4">
         <f t="shared" si="17"/>
-        <v>644309.31219702039</v>
-      </c>
-      <c r="G79" s="4">
-        <f t="shared" si="13"/>
         <v>26726.594579244604</v>
       </c>
       <c r="H79" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4301.9244156770656</v>
       </c>
       <c r="J79" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.4804199999999983</v>
       </c>
       <c r="M79" s="4">
         <v>147022</v>
       </c>
-      <c r="N79" s="80">
-        <f t="shared" si="9"/>
+      <c r="N79" s="70">
+        <f t="shared" si="11"/>
         <v>77.181456605264344</v>
       </c>
       <c r="O79" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>497287.31219702039</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1990</v>
       </c>
       <c r="B80" s="2">
@@ -4718,44 +5206,44 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="D80" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>40.095000000000006</v>
       </c>
       <c r="E80" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>6.5163000000000011</v>
       </c>
       <c r="F80" s="4">
+        <f t="shared" si="21"/>
+        <v>666733.98236058792</v>
+      </c>
+      <c r="G80" s="4">
         <f t="shared" si="17"/>
-        <v>666733.98236058792</v>
-      </c>
-      <c r="G80" s="4">
-        <f t="shared" si="13"/>
         <v>26732.699022747776</v>
       </c>
       <c r="H80" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4344.6386492563006</v>
       </c>
       <c r="J80" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.3578700000000028</v>
       </c>
       <c r="M80" s="4">
         <v>147662</v>
       </c>
-      <c r="N80" s="80">
-        <f t="shared" si="9"/>
+      <c r="N80" s="70">
+        <f t="shared" si="11"/>
         <v>77.852936267445216</v>
       </c>
       <c r="O80" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>519071.98236058792</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1991</v>
       </c>
       <c r="B81" s="2">
@@ -4765,44 +5253,44 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="D81" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>38.659500000000001</v>
       </c>
       <c r="E81" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>6.2595000000000001</v>
       </c>
       <c r="F81" s="4">
+        <f t="shared" si="21"/>
+        <v>689122.04273407941</v>
+      </c>
+      <c r="G81" s="4">
         <f t="shared" si="17"/>
-        <v>689122.04273407941</v>
-      </c>
-      <c r="G81" s="4">
-        <f t="shared" si="13"/>
         <v>26641.113611078144</v>
       </c>
       <c r="H81" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4313.55942649397</v>
       </c>
       <c r="J81" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.2400000000000011</v>
       </c>
       <c r="M81" s="4">
         <v>148164</v>
       </c>
-      <c r="N81" s="80">
-        <f t="shared" si="9"/>
+      <c r="N81" s="70">
+        <f t="shared" si="11"/>
         <v>78.499599372534661</v>
       </c>
       <c r="O81" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>540958.04273407941</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1992</v>
       </c>
       <c r="B82" s="2">
@@ -4812,44 +5300,44 @@
         <v>0.185</v>
       </c>
       <c r="D82" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>38.0655</v>
       </c>
       <c r="E82" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.9385000000000003</v>
       </c>
       <c r="F82" s="4">
+        <f t="shared" si="21"/>
+        <v>711449.59691866359</v>
+      </c>
+      <c r="G82" s="4">
         <f t="shared" si="17"/>
-        <v>711449.59691866359</v>
-      </c>
-      <c r="G82" s="4">
-        <f t="shared" si="13"/>
         <v>27081.684631507389</v>
       </c>
       <c r="H82" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4224.9434313014835</v>
       </c>
       <c r="J82" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.212699999999995</v>
       </c>
       <c r="M82" s="4">
         <v>148326</v>
       </c>
-      <c r="N82" s="80">
-        <f t="shared" si="9"/>
+      <c r="N82" s="70">
+        <f t="shared" si="11"/>
         <v>79.151580007577493</v>
       </c>
       <c r="O82" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>563123.59691866359</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1993</v>
       </c>
       <c r="B83" s="2">
@@ -4859,44 +5347,44 @@
         <v>0.18</v>
       </c>
       <c r="D83" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>37.669499999999999</v>
       </c>
       <c r="E83" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.7780000000000005</v>
       </c>
       <c r="F83" s="4">
+        <f t="shared" si="21"/>
+        <v>734306.33811886946</v>
+      </c>
+      <c r="G83" s="4">
         <f t="shared" si="17"/>
-        <v>734306.33811886946</v>
-      </c>
-      <c r="G83" s="4">
-        <f t="shared" si="13"/>
         <v>27660.95260376875</v>
       </c>
       <c r="H83" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4242.822021650828</v>
       </c>
       <c r="J83" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.1891500000000019</v>
       </c>
       <c r="M83" s="4">
         <v>148295</v>
       </c>
-      <c r="N83" s="80">
-        <f t="shared" si="9"/>
+      <c r="N83" s="70">
+        <f t="shared" si="11"/>
         <v>79.804750101994344</v>
       </c>
       <c r="O83" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>586011.33811886946</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1994</v>
       </c>
       <c r="B84" s="2">
@@ -4906,44 +5394,44 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="D84" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>37.521000000000001</v>
       </c>
       <c r="E84" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.6495999999999995</v>
       </c>
       <c r="F84" s="4">
+        <f t="shared" si="21"/>
+        <v>757724.4687009874</v>
+      </c>
+      <c r="G84" s="4">
         <f t="shared" si="17"/>
-        <v>757724.4687009874</v>
-      </c>
-      <c r="G84" s="4">
-        <f t="shared" si="13"/>
         <v>28430.579790129748</v>
       </c>
       <c r="H84" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4280.8401583730974</v>
       </c>
       <c r="J84" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.1871400000000034</v>
       </c>
       <c r="M84" s="4">
         <v>147997</v>
       </c>
-      <c r="N84" s="80">
-        <f t="shared" si="9"/>
+      <c r="N84" s="70">
+        <f t="shared" si="11"/>
         <v>80.468230060760717</v>
       </c>
       <c r="O84" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>609727.4687009874</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1995</v>
       </c>
       <c r="B85" s="2">
@@ -4953,44 +5441,44 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="D85" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>37.421999999999997</v>
       </c>
       <c r="E85" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.4891000000000005</v>
       </c>
       <c r="F85" s="4">
+        <f t="shared" si="21"/>
+        <v>781874.20833274408</v>
+      </c>
+      <c r="G85" s="4">
         <f t="shared" si="17"/>
-        <v>781874.20833274408</v>
-      </c>
-      <c r="G85" s="4">
-        <f t="shared" si="13"/>
         <v>29259.296624227944</v>
       </c>
       <c r="H85" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4291.7857169592662</v>
       </c>
       <c r="J85" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.1932899999999917</v>
       </c>
       <c r="M85" s="4">
         <v>147938</v>
       </c>
-      <c r="N85" s="80">
-        <f t="shared" si="9"/>
+      <c r="N85" s="70">
+        <f t="shared" si="11"/>
         <v>81.079053583892915</v>
       </c>
       <c r="O85" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>633936.20833274408</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1996</v>
       </c>
       <c r="B86" s="2">
@@ -5000,44 +5488,44 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="D86" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>37.669499999999999</v>
       </c>
       <c r="E86" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.3286000000000007</v>
       </c>
       <c r="F86" s="4">
+        <f t="shared" si="21"/>
+        <v>806841.7192400127</v>
+      </c>
+      <c r="G86" s="4">
         <f t="shared" si="17"/>
-        <v>806841.7192400127</v>
-      </c>
-      <c r="G86" s="4">
-        <f t="shared" si="13"/>
         <v>30393.324142911657</v>
       </c>
       <c r="H86" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4299.3367851423327</v>
       </c>
       <c r="J86" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.2340900000000086</v>
       </c>
       <c r="M86" s="4">
         <v>147609</v>
       </c>
-      <c r="N86" s="80">
-        <f t="shared" si="9"/>
+      <c r="N86" s="70">
+        <f t="shared" si="11"/>
         <v>81.705333712907517</v>
       </c>
       <c r="O86" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>659232.7192400127</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1997</v>
       </c>
       <c r="B87" s="2">
@@ -5047,44 +5535,44 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="D87" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>37.372500000000002</v>
       </c>
       <c r="E87" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.2323000000000004</v>
       </c>
       <c r="F87" s="4">
+        <f t="shared" si="21"/>
+        <v>832935.70659778209</v>
+      </c>
+      <c r="G87" s="4">
         <f t="shared" si="17"/>
-        <v>832935.70659778209</v>
-      </c>
-      <c r="G87" s="4">
-        <f t="shared" si="13"/>
         <v>31128.889694825612</v>
       </c>
       <c r="H87" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4358.1694976315757</v>
       </c>
       <c r="J87" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.2140199999999983</v>
       </c>
       <c r="M87" s="4">
         <v>147137</v>
       </c>
-      <c r="N87" s="80">
-        <f t="shared" si="9"/>
+      <c r="N87" s="70">
+        <f t="shared" si="11"/>
         <v>82.335131171048317</v>
       </c>
       <c r="O87" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>685798.70659778209</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1998</v>
       </c>
       <c r="B88" s="2">
@@ -5094,44 +5582,44 @@
         <v>0.16</v>
       </c>
       <c r="D88" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>36.778500000000001</v>
       </c>
       <c r="E88" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.1360000000000001</v>
       </c>
       <c r="F88" s="4">
+        <f t="shared" si="21"/>
+        <v>859706.42679497611</v>
+      </c>
+      <c r="G88" s="4">
         <f t="shared" si="17"/>
-        <v>859706.42679497611</v>
-      </c>
-      <c r="G88" s="4">
-        <f t="shared" si="13"/>
         <v>31618.71281787903</v>
       </c>
       <c r="H88" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4415.4522080189981</v>
       </c>
       <c r="J88" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.164250000000004</v>
       </c>
       <c r="M88" s="4">
         <v>147802.1</v>
       </c>
-      <c r="N88" s="80">
-        <f t="shared" si="9"/>
+      <c r="N88" s="70">
+        <f t="shared" si="11"/>
         <v>82.807840514696068</v>
       </c>
       <c r="O88" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>711904.32679497614</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1999</v>
       </c>
       <c r="B89" s="2">
@@ -5141,44 +5629,44 @@
         <v>0.159</v>
       </c>
       <c r="D89" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>35.936999999999998</v>
       </c>
       <c r="E89" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.1039000000000003</v>
       </c>
       <c r="F89" s="4">
+        <f t="shared" si="21"/>
+        <v>886909.68740483618</v>
+      </c>
+      <c r="G89" s="4">
         <f t="shared" si="17"/>
-        <v>886909.68740483618</v>
-      </c>
-      <c r="G89" s="4">
-        <f t="shared" si="13"/>
         <v>31872.873436267597</v>
       </c>
       <c r="H89" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4526.6983535455438</v>
       </c>
       <c r="J89" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3.0833100000000049</v>
       </c>
       <c r="M89" s="4">
         <v>147539.4</v>
       </c>
-      <c r="N89" s="80">
-        <f t="shared" si="9"/>
+      <c r="N89" s="70">
+        <f t="shared" si="11"/>
         <v>83.36477748577633</v>
       </c>
       <c r="O89" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>739370.28740483616</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2000</v>
       </c>
       <c r="B90" s="2">
@@ -5188,44 +5676,44 @@
         <v>0.16</v>
       </c>
       <c r="D90" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>34.897500000000001</v>
       </c>
       <c r="E90" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.1360000000000001</v>
       </c>
       <c r="F90" s="4">
+        <f t="shared" si="21"/>
+        <v>914255.86248755828</v>
+      </c>
+      <c r="G90" s="4">
         <f t="shared" si="17"/>
-        <v>914255.86248755828</v>
-      </c>
-      <c r="G90" s="4">
-        <f t="shared" si="13"/>
         <v>31905.243961159566</v>
       </c>
       <c r="H90" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4695.6181097360995</v>
       </c>
       <c r="J90" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.9761500000000014</v>
       </c>
       <c r="M90" s="4">
         <v>146890.1</v>
       </c>
-      <c r="N90" s="80">
-        <f t="shared" si="9"/>
+      <c r="N90" s="70">
+        <f t="shared" si="11"/>
         <v>83.933370730559687</v>
       </c>
       <c r="O90" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>767365.7624875583</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2001</v>
       </c>
       <c r="B91" s="2">
@@ -5235,44 +5723,44 @@
         <v>0.161</v>
       </c>
       <c r="D91" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>33.412500000000001</v>
       </c>
       <c r="E91" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.1681000000000008</v>
       </c>
       <c r="F91" s="4">
+        <f t="shared" si="21"/>
+        <v>941465.48833898176</v>
+      </c>
+      <c r="G91" s="4">
         <f t="shared" si="17"/>
-        <v>941465.48833898176</v>
-      </c>
-      <c r="G91" s="4">
-        <f t="shared" si="13"/>
         <v>31456.715629126229</v>
       </c>
       <c r="H91" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>4865.5877902846923</v>
       </c>
       <c r="J91" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.8244399999999987</v>
       </c>
       <c r="M91" s="4">
         <v>146303.6</v>
       </c>
-      <c r="N91" s="80">
-        <f t="shared" si="9"/>
+      <c r="N91" s="70">
+        <f t="shared" si="11"/>
         <v>84.460014539872091</v>
       </c>
       <c r="O91" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>795161.88833898178</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2002</v>
       </c>
       <c r="B92" s="2">
@@ -5282,44 +5770,44 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="D92" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>32.076000000000001</v>
       </c>
       <c r="E92" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.2323000000000004</v>
       </c>
       <c r="F92" s="4">
+        <f t="shared" si="21"/>
+        <v>968056.61617782328</v>
+      </c>
+      <c r="G92" s="4">
         <f t="shared" si="17"/>
-        <v>968056.61617782328</v>
-      </c>
-      <c r="G92" s="4">
-        <f t="shared" si="13"/>
         <v>31051.384020519861</v>
       </c>
       <c r="H92" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5065.162632827225</v>
       </c>
       <c r="J92" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.6843700000000097</v>
       </c>
       <c r="M92" s="4">
         <v>145649.29999999999</v>
       </c>
-      <c r="N92" s="80">
-        <f t="shared" si="9"/>
+      <c r="N92" s="70">
+        <f t="shared" si="11"/>
         <v>84.954464690808393</v>
       </c>
       <c r="O92" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>822407.31617782335</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2003</v>
       </c>
       <c r="B93" s="2">
@@ -5329,44 +5817,44 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="D93" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>30.591000000000001</v>
       </c>
       <c r="E93" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.2323000000000004</v>
       </c>
       <c r="F93" s="4">
+        <f t="shared" si="21"/>
+        <v>994042.83756551601</v>
+      </c>
+      <c r="G93" s="4">
         <f t="shared" si="17"/>
-        <v>994042.83756551601</v>
-      </c>
-      <c r="G93" s="4">
-        <f t="shared" si="13"/>
         <v>30408.764443966702</v>
       </c>
       <c r="H93" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5201.1303389940495</v>
       </c>
       <c r="J93" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.5358699999999939</v>
       </c>
       <c r="M93" s="4">
         <v>144963.6</v>
       </c>
-      <c r="N93" s="80">
-        <f t="shared" si="9"/>
+      <c r="N93" s="70">
+        <f t="shared" si="11"/>
         <v>85.416765302084315</v>
       </c>
       <c r="O93" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>849079.23756551603</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2004</v>
       </c>
       <c r="B94" s="2">
@@ -5376,44 +5864,44 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="D94" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>29.402999999999999</v>
       </c>
       <c r="E94" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.2002000000000006</v>
       </c>
       <c r="F94" s="4">
+        <f t="shared" si="21"/>
+        <v>1019250.4716704886</v>
+      </c>
+      <c r="G94" s="4">
         <f t="shared" si="17"/>
-        <v>1019250.4716704886</v>
-      </c>
-      <c r="G94" s="4">
-        <f t="shared" si="13"/>
         <v>29969.021618527375</v>
       </c>
       <c r="H94" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5300.3063027808748</v>
       </c>
       <c r="J94" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.4202799999999991</v>
       </c>
       <c r="M94" s="4">
         <v>144333.6</v>
       </c>
-      <c r="N94" s="80">
-        <f t="shared" si="9"/>
+      <c r="N94" s="70">
+        <f t="shared" si="11"/>
         <v>85.839241284485638</v>
       </c>
       <c r="O94" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>874916.87167048862</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2005</v>
       </c>
       <c r="B95" s="2">
@@ -5423,44 +5911,44 @@
         <v>0.161</v>
       </c>
       <c r="D95" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>28.165499999999998</v>
       </c>
       <c r="E95" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.1681000000000008</v>
       </c>
       <c r="F95" s="4">
+        <f t="shared" si="21"/>
+        <v>1043919.1869862351</v>
+      </c>
+      <c r="G95" s="4">
         <f t="shared" si="17"/>
-        <v>1043919.1869862351</v>
-      </c>
-      <c r="G95" s="4">
-        <f t="shared" si="13"/>
         <v>29402.505861060803</v>
       </c>
       <c r="H95" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5395.0787502635621</v>
       </c>
       <c r="J95" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.2997399999999906</v>
       </c>
       <c r="M95" s="4">
         <v>143801</v>
       </c>
-      <c r="N95" s="80">
-        <f t="shared" si="9"/>
+      <c r="N95" s="70">
+        <f t="shared" si="11"/>
         <v>86.224891563191846</v>
       </c>
       <c r="O95" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>900118.18698623509</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2006</v>
       </c>
       <c r="B96" s="2">
@@ -5470,44 +5958,44 @@
         <v>0.158</v>
       </c>
       <c r="D96" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>27.571500000000004</v>
       </c>
       <c r="E96" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.0718000000000005</v>
       </c>
       <c r="F96" s="4">
+        <f t="shared" si="21"/>
+        <v>1067926.6140970322</v>
+      </c>
+      <c r="G96" s="4">
         <f t="shared" si="17"/>
-        <v>1067926.6140970322</v>
-      </c>
-      <c r="G96" s="4">
-        <f t="shared" si="13"/>
         <v>29444.33864057633</v>
       </c>
       <c r="H96" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5416.3102013773287</v>
       </c>
       <c r="J96" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.2499699999999865</v>
       </c>
       <c r="M96" s="4">
         <v>143236.6</v>
       </c>
-      <c r="N96" s="80">
-        <f t="shared" si="9"/>
+      <c r="N96" s="70">
+        <f t="shared" si="11"/>
         <v>86.587411708892432</v>
       </c>
       <c r="O96" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>924690.01409703225</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2007</v>
       </c>
       <c r="B97" s="2">
@@ -5517,44 +6005,44 @@
         <v>0.156</v>
       </c>
       <c r="D97" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>27.076500000000003</v>
       </c>
       <c r="E97" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.0076000000000001</v>
       </c>
       <c r="F97" s="4">
+        <f t="shared" si="21"/>
+        <v>1091954.6425362311</v>
+      </c>
+      <c r="G97" s="4">
         <f t="shared" si="17"/>
-        <v>1091954.6425362311</v>
-      </c>
-      <c r="G97" s="4">
-        <f t="shared" si="13"/>
         <v>29566.309878632263</v>
       </c>
       <c r="H97" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5468.072067964431</v>
       </c>
       <c r="J97" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.2068900000000005</v>
       </c>
       <c r="M97" s="4">
         <v>142862.70000000001</v>
       </c>
-      <c r="N97" s="80">
-        <f t="shared" si="9"/>
+      <c r="N97" s="70">
+        <f t="shared" si="11"/>
         <v>86.916791738878501</v>
       </c>
       <c r="O97" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>949091.94253623113</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2008</v>
       </c>
       <c r="B98" s="2">
@@ -5564,44 +6052,44 @@
         <v>0.155</v>
       </c>
       <c r="D98" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>26.977500000000003</v>
       </c>
       <c r="E98" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.9755000000000003</v>
       </c>
       <c r="F98" s="4">
+        <f t="shared" si="21"/>
+        <v>1116052.8803468989</v>
+      </c>
+      <c r="G98" s="4">
         <f t="shared" si="17"/>
-        <v>1116052.8803468989</v>
-      </c>
-      <c r="G98" s="4">
-        <f t="shared" si="13"/>
         <v>30108.316579558468</v>
       </c>
       <c r="H98" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5552.9211061659962</v>
       </c>
       <c r="J98" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.2001999999999979</v>
       </c>
       <c r="M98" s="4">
         <v>142747.5</v>
       </c>
-      <c r="N98" s="80">
-        <f t="shared" si="9"/>
+      <c r="N98" s="70">
+        <f t="shared" si="11"/>
         <v>87.209611433856935</v>
       </c>
       <c r="O98" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>973305.38034689892</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2009</v>
       </c>
       <c r="B99" s="2">
@@ -5611,44 +6099,44 @@
         <v>0.154</v>
       </c>
       <c r="D99" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>26.433</v>
       </c>
       <c r="E99" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.9434000000000005</v>
       </c>
       <c r="F99" s="4">
+        <f t="shared" si="21"/>
+        <v>1140608.2758202914</v>
+      </c>
+      <c r="G99" s="4">
         <f t="shared" si="17"/>
-        <v>1140608.2758202914</v>
-      </c>
-      <c r="G99" s="4">
-        <f t="shared" si="13"/>
         <v>30149.698554757764</v>
       </c>
       <c r="H99" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5638.4829506900296</v>
       </c>
       <c r="J99" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.1489600000000042</v>
       </c>
       <c r="M99" s="4">
         <v>142737.20000000001</v>
       </c>
-      <c r="N99" s="80">
-        <f t="shared" si="9"/>
+      <c r="N99" s="70">
+        <f t="shared" si="11"/>
         <v>87.485870212773293</v>
       </c>
       <c r="O99" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>997871.07582029141</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2010</v>
       </c>
       <c r="B100" s="2">
@@ -5658,44 +6146,44 @@
         <v>0.153</v>
       </c>
       <c r="D100" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>25.938000000000002</v>
       </c>
       <c r="E100" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.9112999999999998</v>
       </c>
       <c r="F100" s="4">
+        <f t="shared" si="21"/>
+        <v>1165119.4914243591</v>
+      </c>
+      <c r="G100" s="4">
         <f t="shared" si="17"/>
-        <v>1165119.4914243591</v>
-      </c>
-      <c r="G100" s="4">
-        <f t="shared" si="13"/>
         <v>30220.869368565029</v>
       </c>
       <c r="H100" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5722.2513582324545</v>
       </c>
       <c r="J100" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.1026700000000003</v>
       </c>
       <c r="M100" s="4">
         <v>142833.5</v>
       </c>
-      <c r="N100" s="80">
-        <f t="shared" ref="N100:N110" si="18">100*O100/F100</f>
+      <c r="N100" s="70">
+        <f t="shared" ref="N100:N110" si="22">100*O100/F100</f>
         <v>87.740871125125025</v>
       </c>
       <c r="O100" s="4">
-        <f t="shared" ref="O100:O110" si="19">F100-M100</f>
+        <f t="shared" ref="O100:O110" si="23">F100-M100</f>
         <v>1022285.9914243591</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2011</v>
       </c>
       <c r="B101" s="2">
@@ -5705,44 +6193,44 @@
         <v>0.152</v>
       </c>
       <c r="D101" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>25.3935</v>
       </c>
       <c r="E101" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.8792</v>
       </c>
       <c r="F101" s="4">
+        <f t="shared" si="21"/>
+        <v>1189618.1094346917</v>
+      </c>
+      <c r="G101" s="4">
         <f t="shared" si="17"/>
-        <v>1189618.1094346917</v>
-      </c>
-      <c r="G101" s="4">
-        <f t="shared" si="13"/>
         <v>30208.567461929844</v>
       </c>
       <c r="H101" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5804.3846795537484</v>
       </c>
       <c r="J101" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.0514299999999879</v>
       </c>
       <c r="M101" s="4">
         <v>142865.4</v>
       </c>
-      <c r="N101" s="80">
-        <f t="shared" si="18"/>
+      <c r="N101" s="70">
+        <f t="shared" si="22"/>
         <v>87.990650203880136</v>
       </c>
       <c r="O101" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1046752.7094346917</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2012</v>
       </c>
       <c r="B102" s="2">
@@ -5752,44 +6240,44 @@
         <v>0.152</v>
       </c>
       <c r="D102" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>24.948</v>
       </c>
       <c r="E102" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.8792</v>
       </c>
       <c r="F102" s="4">
+        <f t="shared" si="21"/>
+        <v>1214022.2922170677</v>
+      </c>
+      <c r="G102" s="4">
         <f t="shared" si="17"/>
-        <v>1214022.2922170677</v>
-      </c>
-      <c r="G102" s="4">
-        <f t="shared" si="13"/>
         <v>30287.428146231407</v>
       </c>
       <c r="H102" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5923.4575681855167</v>
       </c>
       <c r="J102" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2.0068800000000135</v>
       </c>
       <c r="M102" s="4">
         <v>143056.4</v>
       </c>
-      <c r="N102" s="80">
-        <f t="shared" si="18"/>
+      <c r="N102" s="70">
+        <f t="shared" si="22"/>
         <v>88.216328405407779</v>
       </c>
       <c r="O102" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1070965.8922170678</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2013</v>
       </c>
       <c r="B103" s="2">
@@ -5799,44 +6287,44 @@
         <v>0.152</v>
       </c>
       <c r="D103" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>24.452999999999999</v>
       </c>
       <c r="E103" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.8792</v>
       </c>
       <c r="F103" s="4">
+        <f t="shared" si="21"/>
+        <v>1238386.2627951137</v>
+      </c>
+      <c r="G103" s="4">
         <f t="shared" si="17"/>
-        <v>1238386.2627951137</v>
-      </c>
-      <c r="G103" s="4">
-        <f t="shared" si="13"/>
         <v>30282.259284128915</v>
       </c>
       <c r="H103" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6042.3342534299181</v>
       </c>
       <c r="J103" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.9573800000000001</v>
       </c>
       <c r="M103" s="4">
         <v>143347.1</v>
       </c>
-      <c r="N103" s="80">
-        <f t="shared" si="18"/>
+      <c r="N103" s="70">
+        <f t="shared" si="22"/>
         <v>88.424685874950129</v>
       </c>
       <c r="O103" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1095039.1627951136</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2014</v>
       </c>
       <c r="B104" s="2">
@@ -5846,44 +6334,44 @@
         <v>0.153</v>
       </c>
       <c r="D104" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>24.0075</v>
       </c>
       <c r="E104" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.9112999999999998</v>
       </c>
       <c r="F104" s="4">
+        <f t="shared" si="21"/>
+        <v>1262626.1878258127</v>
+      </c>
+      <c r="G104" s="4">
         <f t="shared" si="17"/>
-        <v>1262626.1878258127</v>
-      </c>
-      <c r="G104" s="4">
-        <f t="shared" si="13"/>
         <v>30312.498204228199</v>
       </c>
       <c r="H104" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6201.1359962689139</v>
       </c>
       <c r="J104" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.9096200000000096</v>
       </c>
       <c r="M104" s="4">
         <v>143666.9</v>
       </c>
-      <c r="N104" s="80">
-        <f t="shared" si="18"/>
+      <c r="N104" s="70">
+        <f t="shared" si="22"/>
         <v>88.621580845920192</v>
       </c>
       <c r="O104" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1118959.2878258128</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2015</v>
       </c>
       <c r="B105" s="2">
@@ -5893,44 +6381,44 @@
         <v>0.154</v>
       </c>
       <c r="D105" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>23.611499999999999</v>
       </c>
       <c r="E105" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.9434000000000005</v>
       </c>
       <c r="F105" s="4">
+        <f t="shared" si="21"/>
+        <v>1286737.5500337721</v>
+      </c>
+      <c r="G105" s="4">
         <f t="shared" si="17"/>
-        <v>1286737.5500337721</v>
-      </c>
-      <c r="G105" s="4">
-        <f t="shared" si="13"/>
         <v>30381.803662622409</v>
       </c>
       <c r="H105" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6360.8584048369503</v>
       </c>
       <c r="J105" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.8668100000000027</v>
       </c>
       <c r="M105" s="4">
         <v>146267.29999999999</v>
       </c>
-      <c r="N105" s="80">
-        <f t="shared" si="18"/>
+      <c r="N105" s="70">
+        <f t="shared" si="22"/>
         <v>88.632701361970746</v>
       </c>
       <c r="O105" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1140470.2500337721</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2016</v>
       </c>
       <c r="B106" s="2">
@@ -5940,44 +6428,44 @@
         <v>0.155</v>
       </c>
       <c r="D106" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>23.215499999999999</v>
       </c>
       <c r="E106" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.9755000000000003</v>
       </c>
       <c r="F106" s="4">
+        <f t="shared" si="21"/>
+        <v>1310758.4952915576</v>
+      </c>
+      <c r="G106" s="4">
         <f t="shared" si="17"/>
-        <v>1310758.4952915576</v>
-      </c>
-      <c r="G106" s="4">
-        <f t="shared" si="13"/>
         <v>30429.913847441156</v>
       </c>
       <c r="H106" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6521.6788933231446</v>
       </c>
       <c r="J106" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.8240000000000014</v>
       </c>
       <c r="M106" s="4">
         <v>146544.70000000001</v>
       </c>
-      <c r="N106" s="80">
-        <f t="shared" si="18"/>
+      <c r="N106" s="70">
+        <f t="shared" si="22"/>
         <v>88.819855028488419</v>
       </c>
       <c r="O106" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1164213.7952915577</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2017</v>
       </c>
       <c r="B107" s="2">
@@ -5987,44 +6475,44 @@
         <v>0.156</v>
       </c>
       <c r="D107" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>22.819500000000001</v>
       </c>
       <c r="E107" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.0076000000000001</v>
       </c>
       <c r="F107" s="4">
+        <f t="shared" si="21"/>
+        <v>1334666.7302456757</v>
+      </c>
+      <c r="G107" s="4">
         <f t="shared" si="17"/>
-        <v>1334666.7302456757</v>
-      </c>
-      <c r="G107" s="4">
-        <f t="shared" si="13"/>
         <v>30456.427450841195</v>
       </c>
       <c r="H107" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6683.477118378245</v>
       </c>
       <c r="J107" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.7811900000000052</v>
       </c>
       <c r="M107" s="4">
         <v>146804.4</v>
       </c>
-      <c r="N107" s="80">
-        <f t="shared" si="18"/>
+      <c r="N107" s="70">
+        <f t="shared" si="22"/>
         <v>89.00066985464025</v>
       </c>
       <c r="O107" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1187862.3302456758</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2018</v>
       </c>
       <c r="B108" s="2">
@@ -6034,44 +6522,44 @@
         <v>0.158</v>
       </c>
       <c r="D108" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>22.423500000000001</v>
       </c>
       <c r="E108" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.0718000000000005</v>
       </c>
       <c r="F108" s="4">
+        <f t="shared" si="21"/>
+        <v>1358439.6805781387</v>
+      </c>
+      <c r="G108" s="4">
         <f t="shared" si="17"/>
-        <v>1358439.6805781387</v>
-      </c>
-      <c r="G108" s="4">
-        <f t="shared" si="13"/>
         <v>30460.972177443891</v>
       </c>
       <c r="H108" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6889.7343719562041</v>
       </c>
       <c r="J108" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.7351699999999926</v>
       </c>
       <c r="M108" s="4">
         <v>146880.4</v>
       </c>
-      <c r="N108" s="80">
-        <f t="shared" si="18"/>
+      <c r="N108" s="70">
+        <f t="shared" si="22"/>
         <v>89.187565550390204</v>
       </c>
       <c r="O108" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1211559.2805781388</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2019</v>
       </c>
       <c r="B109" s="2">
@@ -6081,44 +6569,44 @@
         <v>0.16</v>
       </c>
       <c r="D109" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>22.077000000000002</v>
       </c>
       <c r="E109" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.1360000000000001</v>
       </c>
       <c r="F109" s="4">
+        <f t="shared" si="21"/>
+        <v>1382010.9183836263</v>
+      </c>
+      <c r="G109" s="4">
         <f t="shared" si="17"/>
-        <v>1382010.9183836263</v>
-      </c>
-      <c r="G109" s="4">
-        <f t="shared" si="13"/>
         <v>30510.655045155319</v>
       </c>
       <c r="H109" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7098.0080768183052</v>
       </c>
       <c r="J109" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.6941000000000166</v>
       </c>
       <c r="M109" s="4">
         <v>146780.70000000001</v>
       </c>
-      <c r="N109" s="80">
-        <f t="shared" si="18"/>
+      <c r="N109" s="70">
+        <f t="shared" si="22"/>
         <v>89.379193894381686</v>
       </c>
       <c r="O109" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1235230.2183836263</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2020</v>
       </c>
       <c r="B110" s="2">
@@ -6128,44 +6616,44 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="D110" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>21.681000000000001</v>
       </c>
       <c r="E110" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.2002000000000006</v>
       </c>
       <c r="F110" s="4">
+        <f t="shared" si="21"/>
+        <v>1405423.5653519635</v>
+      </c>
+      <c r="G110" s="4">
         <f t="shared" si="17"/>
-        <v>1405423.5653519635</v>
-      </c>
-      <c r="G110" s="4">
-        <f t="shared" si="13"/>
         <v>30470.988320395922</v>
       </c>
       <c r="H110" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7308.4836245432816</v>
       </c>
       <c r="J110" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.6480799999999916</v>
       </c>
       <c r="M110" s="4">
         <v>146748.6</v>
       </c>
-      <c r="N110" s="80">
-        <f t="shared" si="18"/>
+      <c r="N110" s="70">
+        <f t="shared" si="22"/>
         <v>89.558407613348251</v>
       </c>
       <c r="O110" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1258674.9653519634</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2021</v>
       </c>
       <c r="B111" s="2">
@@ -6175,44 +6663,44 @@
         <v>0.16400000000000001</v>
       </c>
       <c r="D111" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>21.334499999999998</v>
       </c>
       <c r="E111" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.2644000000000002</v>
       </c>
       <c r="F111" s="4">
+        <f t="shared" si="21"/>
+        <v>1428586.070047816</v>
+      </c>
+      <c r="G111" s="4">
         <f t="shared" si="17"/>
-        <v>1428586.070047816</v>
-      </c>
-      <c r="G111" s="4">
-        <f t="shared" si="13"/>
         <v>30478.169511435128</v>
       </c>
       <c r="H111" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7520.6485071597226</v>
       </c>
       <c r="J111" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.6070100000000007</v>
       </c>
       <c r="M111" s="4">
         <v>147455.70000000001</v>
       </c>
-      <c r="N111" s="80">
-        <f t="shared" ref="N111:N114" si="20">100*O111/F111</f>
+      <c r="N111" s="70">
+        <f t="shared" ref="N111:N114" si="24">100*O111/F111</f>
         <v>89.678206788404111</v>
       </c>
       <c r="O111" s="4">
-        <f t="shared" ref="O111:O114" si="21">F111-M111</f>
+        <f t="shared" ref="O111:O114" si="25">F111-M111</f>
         <v>1281130.3700478161</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2022</v>
       </c>
       <c r="B112" s="2">
@@ -6222,44 +6710,44 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="D112" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>21.037499999999998</v>
       </c>
       <c r="E112" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.3286000000000007</v>
       </c>
       <c r="F112" s="4">
+        <f t="shared" si="21"/>
+        <v>1451543.5910520914</v>
+      </c>
+      <c r="G112" s="4">
         <f t="shared" si="17"/>
-        <v>1451543.5910520914</v>
-      </c>
-      <c r="G112" s="4">
-        <f t="shared" si="13"/>
         <v>30536.848296758373</v>
       </c>
       <c r="H112" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7734.6951792801756</v>
       </c>
       <c r="J112" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.570890000000011</v>
       </c>
       <c r="M112" s="4">
         <v>146980.1</v>
       </c>
-      <c r="N112" s="80">
-        <f t="shared" si="20"/>
+      <c r="N112" s="70">
+        <f t="shared" si="24"/>
         <v>89.874220732601799</v>
       </c>
       <c r="O112" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>1304563.4910520914</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2023</v>
       </c>
       <c r="B113" s="2">
@@ -6269,44 +6757,44 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="D113" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20.740500000000001</v>
       </c>
       <c r="E113" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.3928000000000003</v>
       </c>
       <c r="F113" s="4">
+        <f t="shared" si="21"/>
+        <v>1474345.7441695698</v>
+      </c>
+      <c r="G113" s="4">
         <f t="shared" si="17"/>
-        <v>1474345.7441695698</v>
-      </c>
-      <c r="G113" s="4">
-        <f t="shared" si="13"/>
         <v>30578.667906948966</v>
       </c>
       <c r="H113" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7950.8517291576563</v>
       </c>
       <c r="J113" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.5347700000000097</v>
       </c>
       <c r="M113" s="4">
         <v>146447.4</v>
       </c>
-      <c r="N113" s="80">
-        <f t="shared" si="20"/>
+      <c r="N113" s="70">
+        <f t="shared" si="24"/>
         <v>90.06695677868376</v>
       </c>
       <c r="O113" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>1327898.3441695699</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2024</v>
       </c>
       <c r="B114" s="2">
@@ -6316,44 +6804,44 @@
         <v>0.17</v>
       </c>
       <c r="D114" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20.4435</v>
       </c>
       <c r="E114" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.4570000000000007</v>
       </c>
       <c r="F114" s="4">
+        <f t="shared" si="21"/>
+        <v>1496973.5603473613</v>
+      </c>
+      <c r="G114" s="4">
         <f t="shared" si="17"/>
-        <v>1496973.5603473613</v>
-      </c>
-      <c r="G114" s="4">
-        <f t="shared" si="13"/>
         <v>30603.378980961283</v>
       </c>
       <c r="H114" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8168.9847188155509</v>
       </c>
       <c r="J114" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.4986500000000007</v>
       </c>
       <c r="M114" s="4">
         <v>146150.79999999999</v>
       </c>
-      <c r="N114" s="80">
-        <f t="shared" si="20"/>
+      <c r="N114" s="70">
+        <f t="shared" si="24"/>
         <v>90.236915075100811</v>
       </c>
       <c r="O114" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>1350822.7603473612</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2025</v>
       </c>
       <c r="B115" s="2">
@@ -6363,33 +6851,33 @@
         <v>0.17</v>
       </c>
       <c r="D115" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20.1465</v>
       </c>
       <c r="E115" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.4570000000000007</v>
       </c>
       <c r="F115" s="4">
+        <f t="shared" si="21"/>
+        <v>1519407.954609507</v>
+      </c>
+      <c r="G115" s="4">
         <f t="shared" si="17"/>
-        <v>1519407.954609507</v>
-      </c>
-      <c r="G115" s="4">
-        <f t="shared" si="13"/>
         <v>30610.752357540434</v>
       </c>
       <c r="H115" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8291.4092083040814</v>
       </c>
       <c r="J115" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.4689500000000033</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2026</v>
       </c>
       <c r="B116" s="2">
@@ -6399,33 +6887,33 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="D116" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>19.849500000000003</v>
       </c>
       <c r="E116" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.4891000000000005</v>
       </c>
       <c r="F116" s="4">
+        <f t="shared" si="21"/>
+        <v>1541727.2977587434</v>
+      </c>
+      <c r="G116" s="4">
         <f t="shared" si="17"/>
-        <v>1541727.2977587434</v>
-      </c>
-      <c r="G116" s="4">
-        <f t="shared" si="13"/>
         <v>30602.515996862181</v>
       </c>
       <c r="H116" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8462.6953101275194</v>
       </c>
       <c r="J116" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.4360400000000058</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2027</v>
       </c>
       <c r="B117" s="2">
@@ -6435,33 +6923,33 @@
         <v>0.17299999999999999</v>
       </c>
       <c r="D117" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>19.602</v>
       </c>
       <c r="E117" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.5533000000000001</v>
       </c>
       <c r="F117" s="4">
+        <f t="shared" si="21"/>
+        <v>1563867.1184454781</v>
+      </c>
+      <c r="G117" s="4">
         <f t="shared" si="17"/>
-        <v>1563867.1184454781</v>
-      </c>
-      <c r="G117" s="4">
-        <f t="shared" si="13"/>
         <v>30654.923255768263</v>
       </c>
       <c r="H117" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8684.6232688632736</v>
       </c>
       <c r="J117" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.4048700000000125</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2028</v>
       </c>
       <c r="B118" s="2">
@@ -6471,33 +6959,33 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="D118" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>19.255500000000001</v>
       </c>
       <c r="E118" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.5853999999999999</v>
       </c>
       <c r="F118" s="4">
+        <f t="shared" si="21"/>
+        <v>1585837.4184323833</v>
+      </c>
+      <c r="G118" s="4">
         <f t="shared" si="17"/>
-        <v>1585837.4184323833</v>
-      </c>
-      <c r="G118" s="4">
-        <f t="shared" si="13"/>
         <v>30536.092410624762</v>
       </c>
       <c r="H118" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8857.5363169122338</v>
       </c>
       <c r="J118" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.3670100000000029</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2029</v>
       </c>
       <c r="B119" s="2">
@@ -6507,33 +6995,33 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="D119" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>18.958500000000001</v>
       </c>
       <c r="E119" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.6495999999999995</v>
       </c>
       <c r="F119" s="4">
+        <f t="shared" si="21"/>
+        <v>1607515.9745260959</v>
+      </c>
+      <c r="G119" s="4">
         <f t="shared" si="17"/>
-        <v>1607515.9745260959</v>
-      </c>
-      <c r="G119" s="4">
-        <f t="shared" si="13"/>
         <v>30476.091603052988</v>
       </c>
       <c r="H119" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>9081.8222496826311</v>
       </c>
       <c r="J119" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.3308900000000035</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2030</v>
       </c>
       <c r="B120" s="2">
@@ -6543,33 +7031,33 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="D120" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>18.5625</v>
       </c>
       <c r="E120" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.7458999999999998</v>
       </c>
       <c r="F120" s="4">
+        <f t="shared" si="21"/>
+        <v>1628910.2438794663</v>
+      </c>
+      <c r="G120" s="4">
         <f t="shared" si="17"/>
-        <v>1628910.2438794663</v>
-      </c>
-      <c r="G120" s="4">
-        <f t="shared" si="13"/>
         <v>30236.646402012593</v>
       </c>
       <c r="H120" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>9359.5553703070254</v>
       </c>
       <c r="J120" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.2816599999999956</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2031</v>
       </c>
       <c r="B121" s="2">
@@ -6579,33 +7067,33 @@
         <v>0.18</v>
       </c>
       <c r="D121" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>18.216000000000001</v>
       </c>
       <c r="E121" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5.7780000000000005</v>
       </c>
       <c r="F121" s="4">
+        <f t="shared" si="21"/>
+        <v>1649787.3349111718</v>
+      </c>
+      <c r="G121" s="4">
         <f t="shared" si="17"/>
-        <v>1649787.3349111718</v>
-      </c>
-      <c r="G121" s="4">
-        <f t="shared" si="13"/>
         <v>30052.526092741908</v>
       </c>
       <c r="H121" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>9532.4712211167516</v>
       </c>
       <c r="J121" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.2437999999999927</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>2032</v>
       </c>
       <c r="B122" s="1">
@@ -6615,27 +7103,27 @@
         <v>0.18099999999999999</v>
       </c>
       <c r="D122" s="3">
-        <f t="shared" ref="D122:D129" si="22">B122*$D$6</f>
+        <f t="shared" ref="D122:D129" si="26">B122*$D$6</f>
         <v>17.82</v>
       </c>
       <c r="E122" s="3">
-        <f t="shared" ref="E122:E129" si="23">C122*$E$6</f>
+        <f t="shared" ref="E122:E129" si="27">C122*$E$6</f>
         <v>5.8101000000000003</v>
       </c>
       <c r="F122" s="4">
-        <f t="shared" ref="F122:F130" si="24">F121+G121-H121+I121</f>
+        <f t="shared" ref="F122:F130" si="28">F121+G121-H121+I121</f>
         <v>1670307.3897827968</v>
       </c>
       <c r="G122" s="4">
-        <f t="shared" ref="G122:G129" si="25">F122*D122/1000</f>
+        <f t="shared" ref="G122:G129" si="29">F122*D122/1000</f>
         <v>29764.877685929441</v>
       </c>
       <c r="H122" s="4">
-        <f t="shared" ref="H122:H129" si="26">E122*F122/1000</f>
+        <f t="shared" ref="H122:H129" si="30">E122*F122/1000</f>
         <v>9704.6529653770285</v>
       </c>
       <c r="J122" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.2009899999999951</v>
       </c>
     </row>
@@ -6651,33 +7139,33 @@
         <v>0.182</v>
       </c>
       <c r="D123" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>17.473499999999998</v>
       </c>
       <c r="E123" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>5.8422000000000001</v>
       </c>
       <c r="F123" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1690367.6145033492</v>
       </c>
       <c r="G123" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>29536.63851202427</v>
       </c>
       <c r="H123" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>9875.4656774514679</v>
       </c>
       <c r="J123" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.1631299999999887</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
-        <f t="shared" ref="A124:A129" si="27">A123+1</f>
+        <f t="shared" ref="A124:A129" si="31">A123+1</f>
         <v>2034</v>
       </c>
       <c r="B124" s="1">
@@ -6687,33 +7175,33 @@
         <v>0.183</v>
       </c>
       <c r="D124" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>17.126999999999999</v>
       </c>
       <c r="E124" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>5.8742999999999999</v>
       </c>
       <c r="F124" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1710028.7873379218</v>
       </c>
       <c r="G124" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>29287.663040736585</v>
       </c>
       <c r="H124" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>10045.222105459154</v>
       </c>
       <c r="J124" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.1252700000000107</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2035</v>
       </c>
       <c r="B125" s="1">
@@ -6723,33 +7211,33 @@
         <v>0.184</v>
       </c>
       <c r="D125" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>16.7805</v>
       </c>
       <c r="E125" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>5.9064000000000005</v>
       </c>
       <c r="F125" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1729271.2282731994</v>
       </c>
       <c r="G125" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>29018.035846038423</v>
       </c>
       <c r="H125" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>10213.767582672825</v>
       </c>
       <c r="J125" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.0874100000000007</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2036</v>
       </c>
       <c r="B126" s="1">
@@ -6759,33 +7247,33 @@
         <v>0.186</v>
       </c>
       <c r="D126" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>16.434000000000001</v>
       </c>
       <c r="E126" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>5.9706000000000001</v>
       </c>
       <c r="F126" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1748075.496536565</v>
       </c>
       <c r="G126" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>28727.872710081912</v>
       </c>
       <c r="H126" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>10437.059559621215</v>
       </c>
       <c r="J126" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.0463400000000078</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2037</v>
       </c>
       <c r="B127" s="1">
@@ -6795,33 +7283,33 @@
         <v>0.187</v>
       </c>
       <c r="D127" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>16.087500000000002</v>
       </c>
       <c r="E127" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>6.0026999999999999</v>
       </c>
       <c r="F127" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1766366.3096870258</v>
       </c>
       <c r="G127" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>28416.418007090033</v>
       </c>
       <c r="H127" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>10602.96704715831</v>
       </c>
       <c r="J127" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1.0084799999999929</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2038</v>
       </c>
       <c r="B128" s="1">
@@ -6831,33 +7319,33 @@
         <v>0.189</v>
       </c>
       <c r="D128" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>15.741</v>
       </c>
       <c r="E128" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>6.0669000000000004</v>
       </c>
       <c r="F128" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1784179.7606469574</v>
       </c>
       <c r="G128" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>28084.773612343753</v>
       </c>
       <c r="H128" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>10824.440189869028</v>
       </c>
       <c r="J128" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.96740999999999056</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2039</v>
       </c>
       <c r="B129" s="57">
@@ -6867,27 +7355,27 @@
         <v>0.19</v>
       </c>
       <c r="D129" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>15.394500000000001</v>
       </c>
       <c r="E129" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>6.0990000000000002</v>
       </c>
       <c r="F129" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1801440.094069432</v>
       </c>
       <c r="G129" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>27732.269528151872</v>
       </c>
       <c r="H129" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>10986.983133729465</v>
       </c>
       <c r="J129" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.92955000000000021</v>
       </c>
     </row>
@@ -6898,7 +7386,7 @@
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="F130" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>1818185.3804638544</v>
       </c>
       <c r="G130" s="4"/>
@@ -6935,11 +7423,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="69" t="s">
+      <c r="D137" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="69"/>
-      <c r="F137" s="69"/>
+      <c r="E137" s="72"/>
+      <c r="F137" s="72"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -6999,11 +7487,11 @@
         <v>130666.73985224668</v>
       </c>
       <c r="E140" s="4">
-        <f t="shared" ref="E140:E145" ca="1" si="28">OFFSET(INDIRECT(MID(_xlfn.FORMULATEXT(D140),2,255)),1,0)</f>
+        <f t="shared" ref="E140:E145" ca="1" si="32">OFFSET(INDIRECT(MID(_xlfn.FORMULATEXT(D140),2,255)),1,0)</f>
         <v>133451.47021195581</v>
       </c>
       <c r="F140" s="4">
-        <f t="shared" ref="F140:F145" ca="1" si="29">D140*(E140/D140)^((C140-1)/365)</f>
+        <f t="shared" ref="F140:F145" ca="1" si="33">D140*(E140/D140)^((C140-1)/365)</f>
         <v>130704.49149186898</v>
       </c>
     </row>
@@ -7022,11 +7510,11 @@
         <v>136379.98265487506</v>
       </c>
       <c r="E141" s="4">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" ca="1" si="32"/>
         <v>139423.65655577349</v>
       </c>
       <c r="F141" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="33"/>
         <v>136512.00079842543</v>
       </c>
     </row>
@@ -7045,11 +7533,11 @@
         <v>220430.29993095316</v>
       </c>
       <c r="E142" s="4">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" ca="1" si="32"/>
         <v>227267.32041482156</v>
       </c>
       <c r="F142" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="33"/>
         <v>220688.70840674659</v>
       </c>
     </row>
@@ -7068,11 +7556,11 @@
         <v>317168.53255002614</v>
       </c>
       <c r="E143" s="4">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" ca="1" si="32"/>
         <v>329111.54536005063</v>
       </c>
       <c r="F143" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="33"/>
         <v>317618.5255269864</v>
       </c>
     </row>
@@ -7091,11 +7579,11 @@
         <v>445191.02922871296</v>
       </c>
       <c r="E144" s="4">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" ca="1" si="32"/>
         <v>462181.38870640338</v>
       </c>
       <c r="F144" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="33"/>
         <v>445922.55198754626</v>
       </c>
     </row>
@@ -7114,11 +7602,11 @@
         <v>644309.31219702039</v>
       </c>
       <c r="E145" s="4">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" ca="1" si="32"/>
         <v>666733.98236058792</v>
       </c>
       <c r="F145" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" ca="1" si="33"/>
         <v>644973.97216546303</v>
       </c>
     </row>
@@ -7159,11 +7647,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="D3:J3"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="D137:F137"/>
-    <mergeCell ref="F3:I3"/>
     <mergeCell ref="B3:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7192,16 +7682,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69" t="s">
+      <c r="E4" s="72"/>
+      <c r="F4" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -11769,11 +12259,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="69" t="s">
+      <c r="D137" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="69"/>
-      <c r="F137" s="69"/>
+      <c r="E137" s="72"/>
+      <c r="F137" s="72"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -12024,16 +12514,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69" t="s">
+      <c r="E4" s="72"/>
+      <c r="F4" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -16610,11 +17100,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="69" t="s">
+      <c r="D137" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="69"/>
-      <c r="F137" s="69"/>
+      <c r="E137" s="72"/>
+      <c r="F137" s="72"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -16864,16 +17354,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69" t="s">
+      <c r="E4" s="72"/>
+      <c r="F4" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -21446,11 +21936,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="69" t="s">
+      <c r="D137" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="69"/>
-      <c r="F137" s="69"/>
+      <c r="E137" s="72"/>
+      <c r="F137" s="72"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -21744,15 +22234,15 @@
       <c r="P5" s="63"/>
       <c r="Q5" s="63"/>
       <c r="R5" s="63"/>
-      <c r="S5" s="70" t="s">
+      <c r="S5" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="T5" s="71"/>
-      <c r="U5" s="71"/>
-      <c r="V5" s="70" t="s">
+      <c r="T5" s="75"/>
+      <c r="U5" s="75"/>
+      <c r="V5" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="W5" s="71"/>
+      <c r="W5" s="75"/>
       <c r="X5" s="64"/>
       <c r="Y5" s="63"/>
     </row>
@@ -23135,21 +23625,21 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73" t="s">
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="I5" s="73"/>
-      <c r="J5" s="72" t="s">
+      <c r="I5" s="71"/>
+      <c r="J5" s="73" t="s">
         <v>134</v>
       </c>
-      <c r="K5" s="69"/>
+      <c r="K5" s="72"/>
     </row>
     <row r="6" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
@@ -23773,20 +24263,20 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74" t="s">
+      <c r="C11" s="76"/>
+      <c r="D11" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="74"/>
+      <c r="E11" s="76"/>
     </row>
     <row r="12" spans="1:20" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="76"/>
+      <c r="A12" s="78"/>
       <c r="B12" s="34" t="s">
         <v>99</v>
       </c>
@@ -23808,10 +24298,10 @@
       <c r="J12" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="K12" s="77" t="s">
+      <c r="K12" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="L12" s="78"/>
+      <c r="L12" s="80"/>
       <c r="M12" s="51" t="s">
         <v>154</v>
       </c>
@@ -23824,10 +24314,10 @@
       <c r="Q12" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="R12" s="77" t="s">
+      <c r="R12" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="S12" s="78"/>
+      <c r="S12" s="80"/>
       <c r="T12" s="51" t="s">
         <v>154</v>
       </c>
@@ -31091,10 +31581,10 @@
       <c r="T144" s="15"/>
     </row>
     <row r="145" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="79" t="s">
+      <c r="A145" s="69" t="s">
         <v>150</v>
       </c>
-      <c r="B145" s="79"/>
+      <c r="B145" s="69"/>
       <c r="D145" s="67">
         <v>0.311</v>
       </c>

--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFD1067-FBE1-4D47-A0AD-BBEA4606A11B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE464E4-26E0-4468-BB93-27F427E76385}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="8" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="184">
   <si>
     <t>год</t>
   </si>
@@ -629,6 +629,21 @@
   <si>
     <t>Ожидаемые и фактические значения рождаемости и смертности для РСФСР-1991</t>
   </si>
+  <si>
+    <t>Фактические значения рождаемости и смертности в Мексике и в РСФСР-1991, синхронно по годам</t>
+  </si>
+  <si>
+    <t>RU-смертность</t>
+  </si>
+  <si>
+    <t>RU-рождаемость</t>
+  </si>
+  <si>
+    <t>MX-рождаемость</t>
+  </si>
+  <si>
+    <t>MX-смертность</t>
+  </si>
 </sst>
 </file>
 
@@ -875,7 +890,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1044,6 +1059,26 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1051,13 +1086,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1080,17 +1109,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -3929,7 +3953,2862 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Графики!$B$106</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MX-рождаемость</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$A$107:$A$203</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>1927</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1928</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1929</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1930</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1931</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1933</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1934</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1937</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1938</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1939</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1940</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1941</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1943</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1945</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1946</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1947</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1948</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1949</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1950</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1951</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1952</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1954</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$B$107:$B$203</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>44.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>49.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>42.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>42.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>44.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>43.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>44.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>43.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44.2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>43.7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46.1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>45.2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45.2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>45.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>43.8</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46.4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46.4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46.8</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>47.3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>44.8</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>47.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>45.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>45.4</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46.3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>45.7</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>45.7</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>44.8</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>44.5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>44.1</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43.4</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>42.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>43.2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>45.8</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>44.9</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>40.4</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>39.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>36.4</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>36.9</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>36.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>36.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>33.9</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>36.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>27.9</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>27.1</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>26.8</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>26.3</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>25.9</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>25.4</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>24.8</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>24.3</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>23.9</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>23.4</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>22.6</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>22.2</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>21.1</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>20.8</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>20.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>20.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>19.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>18.7</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>17.8</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>16.8</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>16.3</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>16.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>15.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EFC3-470E-9766-DF4365DF915B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Графики!$C$106</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MX-смертность</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$A$107:$A$203</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>1927</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1928</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1929</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1930</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1931</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1933</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1934</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1937</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1938</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1939</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1940</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1941</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1943</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1945</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1946</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1947</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1948</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1949</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1950</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1951</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1952</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1954</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$C$107:$C$203</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>26.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26.1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24.4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22.9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22.1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>22.4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>16.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>17.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>16.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>17.3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15.9</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13.1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>13.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>13.2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>10.8</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>10.199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7.2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>7.2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EFC3-470E-9766-DF4365DF915B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Графики!$D$106</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RU-рождаемость</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$A$107:$A$203</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>1927</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1928</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1929</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1930</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1931</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1933</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1934</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1937</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1938</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1939</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1940</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1941</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1943</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1945</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1946</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1947</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1948</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1949</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1950</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1951</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1952</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1954</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$D$107:$D$203</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>49.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>32.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>40.9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>34.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>15.1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>27.8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>28.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.6</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26.2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27.8</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>26.4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>24.9</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>23.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>23.2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>20.2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>18.8</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>16.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>15.7</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>15.3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>14.4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>14.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>14.2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>14.6</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>15.1</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15.3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>15.1</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>15.6</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>15.7</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>15.9</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>15.8</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>15.9</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.8</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>15.9</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>16.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17.2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17.2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>14.6</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>13.4</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>9.6</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>9.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>8.9</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>8.6</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>8.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>8.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>8.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>10.199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>10.199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>10.3</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>12.3</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>12.6</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>13.3</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>13.2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>13.3</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13.3</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>10.1</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>8.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>8.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EFC3-470E-9766-DF4365DF915B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Графики!$E$106</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RU-смертность</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$A$107:$A$203</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>1927</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1928</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1929</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1930</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1931</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1932</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1933</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1934</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1937</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1938</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1939</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1940</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1941</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1943</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1945</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1946</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1947</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1948</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1949</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1950</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1951</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1952</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1954</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$E$107:$E$203</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>28.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>26.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26.2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>23.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>51.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>67.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>51.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>13.1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11.7</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>11.6</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>10.3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7.2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>10.199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>10.3</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>10.8</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>11.6</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>11.4</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>12.2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>15.7</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>14.2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>13.7</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>13.6</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>14.7</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>15.3</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>15.6</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>16.2</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>16.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>15.9</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>16.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>15.1</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>14.6</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>14.1</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>14.2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>13.3</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>13.1</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>12.4</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>12.3</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>14.6</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>17.3</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>13.8</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EFC3-470E-9766-DF4365DF915B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="905418920"/>
+        <c:axId val="905419904"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="905418920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2025"/>
+          <c:min val="1925"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="905419904"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="905419904"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="70"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="905418920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4485,6 +7364,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -4518,6 +7913,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEB56A8B-3C8F-4AF1-A4DB-0D1AEE324A44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4874,41 +8305,41 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="83" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="82" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
     </row>
     <row r="4" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="79" t="s">
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79" t="s">
+      <c r="E4" s="86"/>
+      <c r="F4" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="Q4" s="76" t="s">
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="Q4" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="R4" s="76"/>
-      <c r="S4" s="77" t="s">
+      <c r="R4" s="84"/>
+      <c r="S4" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="T4" s="77"/>
+      <c r="T4" s="85"/>
     </row>
     <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -7277,17 +10708,17 @@
         <f t="shared" si="14"/>
         <v>98100.891437904473</v>
       </c>
-      <c r="Q48" s="88">
+      <c r="Q48" s="77">
         <v>24.5</v>
       </c>
-      <c r="R48" s="88">
+      <c r="R48" s="77">
         <v>8</v>
       </c>
-      <c r="S48" s="89">
+      <c r="S48" s="78">
         <f t="shared" si="15"/>
         <v>0.51025721128813917</v>
       </c>
-      <c r="T48" s="89">
+      <c r="T48" s="78">
         <f t="shared" si="16"/>
         <v>0.44743480036018496</v>
       </c>
@@ -7338,10 +10769,10 @@
         <f t="shared" si="14"/>
         <v>102814.29993095316</v>
       </c>
-      <c r="Q49" s="90">
+      <c r="Q49" s="79">
         <v>23.7</v>
       </c>
-      <c r="R49" s="90">
+      <c r="R49" s="79">
         <v>7.8</v>
       </c>
       <c r="S49" s="49">
@@ -7399,10 +10830,10 @@
         <f t="shared" si="14"/>
         <v>108221.32041482156</v>
       </c>
-      <c r="Q50" s="90">
+      <c r="Q50" s="79">
         <v>23.2</v>
       </c>
-      <c r="R50" s="90">
+      <c r="R50" s="79">
         <v>7.4</v>
       </c>
       <c r="S50" s="49">
@@ -7465,10 +10896,10 @@
         <f t="shared" si="14"/>
         <v>113541.26656565128</v>
       </c>
-      <c r="Q51" s="90">
+      <c r="Q51" s="79">
         <v>21.9</v>
       </c>
-      <c r="R51" s="90">
+      <c r="R51" s="79">
         <v>7.4</v>
       </c>
       <c r="S51" s="49">
@@ -7532,10 +10963,10 @@
         <f t="shared" si="14"/>
         <v>119263.5832940168</v>
       </c>
-      <c r="Q52" s="90">
+      <c r="Q52" s="79">
         <v>20.2</v>
       </c>
-      <c r="R52" s="90">
+      <c r="R52" s="79">
         <v>7.7</v>
       </c>
       <c r="S52" s="49">
@@ -7593,10 +11024,10 @@
         <f t="shared" si="14"/>
         <v>125484.21746207037</v>
       </c>
-      <c r="Q53" s="90">
+      <c r="Q53" s="79">
         <v>18.8</v>
       </c>
-      <c r="R53" s="90">
+      <c r="R53" s="79">
         <v>7.5</v>
       </c>
       <c r="S53" s="49">
@@ -7654,10 +11085,10 @@
         <f t="shared" si="14"/>
         <v>132142.12090821605</v>
       </c>
-      <c r="Q54" s="90">
+      <c r="Q54" s="79">
         <v>16.899999999999999</v>
       </c>
-      <c r="R54" s="90">
+      <c r="R54" s="79">
         <v>7.2</v>
       </c>
       <c r="S54" s="49">
@@ -7715,10 +11146,10 @@
         <f t="shared" si="14"/>
         <v>139536.83512644807</v>
       </c>
-      <c r="Q55" s="90">
+      <c r="Q55" s="79">
         <v>15.7</v>
       </c>
-      <c r="R55" s="90">
+      <c r="R55" s="79">
         <v>7.6</v>
       </c>
       <c r="S55" s="49">
@@ -7776,10 +11207,10 @@
         <f t="shared" si="14"/>
         <v>147697.56077992724</v>
       </c>
-      <c r="Q56" s="90">
+      <c r="Q56" s="79">
         <v>15.3</v>
       </c>
-      <c r="R56" s="90">
+      <c r="R56" s="79">
         <v>7.6</v>
       </c>
       <c r="S56" s="49">
@@ -7837,10 +11268,10 @@
         <f t="shared" si="14"/>
         <v>156507.67714184272</v>
       </c>
-      <c r="Q57" s="90">
+      <c r="Q57" s="79">
         <v>14.4</v>
       </c>
-      <c r="R57" s="90">
+      <c r="R57" s="79">
         <v>7.9</v>
       </c>
       <c r="S57" s="49">
@@ -7898,10 +11329,10 @@
         <f t="shared" si="14"/>
         <v>166146.10463774996</v>
       </c>
-      <c r="Q58" s="90">
+      <c r="Q58" s="79">
         <v>14.1</v>
       </c>
-      <c r="R58" s="90">
+      <c r="R58" s="79">
         <v>8.1</v>
       </c>
       <c r="S58" s="49">
@@ -7959,10 +11390,10 @@
         <f t="shared" si="14"/>
         <v>176312.61595157848</v>
       </c>
-      <c r="Q59" s="90">
+      <c r="Q59" s="79">
         <v>14.2</v>
       </c>
-      <c r="R59" s="90">
+      <c r="R59" s="79">
         <v>8.5</v>
       </c>
       <c r="S59" s="49">
@@ -8020,10 +11451,10 @@
         <f t="shared" si="14"/>
         <v>187227.53255002614</v>
       </c>
-      <c r="Q60" s="90">
+      <c r="Q60" s="79">
         <v>14.6</v>
       </c>
-      <c r="R60" s="90">
+      <c r="R60" s="79">
         <v>8.6999999999999993</v>
       </c>
       <c r="S60" s="49">
@@ -8081,10 +11512,10 @@
         <f t="shared" si="14"/>
         <v>198548.54536005063</v>
       </c>
-      <c r="Q61" s="90">
+      <c r="Q61" s="79">
         <v>15.1</v>
       </c>
-      <c r="R61" s="90">
+      <c r="R61" s="79">
         <v>8.6999999999999993</v>
       </c>
       <c r="S61" s="49">
@@ -8142,10 +11573,10 @@
         <f t="shared" si="14"/>
         <v>210283.01215424138</v>
       </c>
-      <c r="Q62" s="90">
+      <c r="Q62" s="79">
         <v>15.3</v>
       </c>
-      <c r="R62" s="90">
+      <c r="R62" s="79">
         <v>9</v>
       </c>
       <c r="S62" s="49">
@@ -8203,10 +11634,10 @@
         <f t="shared" si="14"/>
         <v>222480.52193276933</v>
       </c>
-      <c r="Q63" s="90">
+      <c r="Q63" s="79">
         <v>15.1</v>
       </c>
-      <c r="R63" s="90">
+      <c r="R63" s="79">
         <v>9.1999999999999993</v>
       </c>
       <c r="S63" s="49">
@@ -8264,10 +11695,10 @@
         <f t="shared" si="14"/>
         <v>235351.9279679152</v>
       </c>
-      <c r="Q64" s="90">
+      <c r="Q64" s="79">
         <v>15.6</v>
       </c>
-      <c r="R64" s="90">
+      <c r="R64" s="79">
         <v>9.1999999999999993</v>
       </c>
       <c r="S64" s="49">
@@ -8325,10 +11756,10 @@
         <f t="shared" si="14"/>
         <v>248703.6239771588</v>
       </c>
-      <c r="Q65" s="90">
+      <c r="Q65" s="79">
         <v>15.7</v>
       </c>
-      <c r="R65" s="90">
+      <c r="R65" s="79">
         <v>9.8000000000000007</v>
       </c>
       <c r="S65" s="49">
@@ -8386,10 +11817,10 @@
         <f t="shared" si="14"/>
         <v>262570.06415645254</v>
       </c>
-      <c r="Q66" s="90">
+      <c r="Q66" s="79">
         <v>15.9</v>
       </c>
-      <c r="R66" s="90">
+      <c r="R66" s="79">
         <v>10</v>
       </c>
       <c r="S66" s="49">
@@ -8447,10 +11878,10 @@
         <f t="shared" si="14"/>
         <v>277082.69285772071</v>
       </c>
-      <c r="Q67" s="90">
+      <c r="Q67" s="79">
         <v>15.8</v>
       </c>
-      <c r="R67" s="90">
+      <c r="R67" s="79">
         <v>10.199999999999999</v>
       </c>
       <c r="S67" s="49">
@@ -8508,10 +11939,10 @@
         <f t="shared" si="14"/>
         <v>292125.03838498023</v>
       </c>
-      <c r="Q68" s="90">
+      <c r="Q68" s="79">
         <v>15.9</v>
       </c>
-      <c r="R68" s="90">
+      <c r="R68" s="79">
         <v>10.3</v>
       </c>
       <c r="S68" s="49">
@@ -8569,10 +12000,10 @@
         <f t="shared" si="14"/>
         <v>307781.02922871296</v>
       </c>
-      <c r="Q69" s="90">
+      <c r="Q69" s="79">
         <v>15.8</v>
       </c>
-      <c r="R69" s="90">
+      <c r="R69" s="79">
         <v>10.8</v>
       </c>
       <c r="S69" s="49">
@@ -8630,10 +12061,10 @@
         <f t="shared" si="14"/>
         <v>324054.38870640338</v>
       </c>
-      <c r="Q70" s="90">
+      <c r="Q70" s="79">
         <v>15.9</v>
       </c>
-      <c r="R70" s="90">
+      <c r="R70" s="79">
         <v>11</v>
       </c>
       <c r="S70" s="49">
@@ -8691,10 +12122,10 @@
         <f t="shared" si="14"/>
         <v>340790.10587518109</v>
       </c>
-      <c r="Q71" s="90">
+      <c r="Q71" s="79">
         <v>16</v>
       </c>
-      <c r="R71" s="90">
+      <c r="R71" s="79">
         <v>10.9</v>
       </c>
       <c r="S71" s="49">
@@ -8752,10 +12183,10 @@
         <f t="shared" si="14"/>
         <v>358225.15988963132</v>
       </c>
-      <c r="Q72" s="90">
+      <c r="Q72" s="79">
         <v>16.600000000000001</v>
       </c>
-      <c r="R72" s="90">
+      <c r="R72" s="79">
         <v>10.7</v>
       </c>
       <c r="S72" s="49">
@@ -8813,10 +12244,10 @@
         <f t="shared" si="14"/>
         <v>376195.80892363796</v>
       </c>
-      <c r="Q73" s="90">
+      <c r="Q73" s="79">
         <v>17.5</v>
       </c>
-      <c r="R73" s="90">
+      <c r="R73" s="79">
         <v>11</v>
       </c>
       <c r="S73" s="49">
@@ -8874,10 +12305,10 @@
         <f t="shared" si="14"/>
         <v>394820.29612583981</v>
       </c>
-      <c r="Q74" s="90">
+      <c r="Q74" s="79">
         <v>16.899999999999999</v>
       </c>
-      <c r="R74" s="90">
+      <c r="R74" s="79">
         <v>11.6</v>
       </c>
       <c r="S74" s="49">
@@ -8935,10 +12366,10 @@
         <f t="shared" si="14"/>
         <v>414415.19376833143</v>
       </c>
-      <c r="Q75" s="90">
+      <c r="Q75" s="79">
         <v>16.600000000000001</v>
       </c>
-      <c r="R75" s="90">
+      <c r="R75" s="79">
         <v>11.3</v>
       </c>
       <c r="S75" s="49">
@@ -8996,10 +12427,10 @@
         <f t="shared" si="14"/>
         <v>434638.46258303081</v>
       </c>
-      <c r="Q76" s="90">
+      <c r="Q76" s="79">
         <v>17.2</v>
       </c>
-      <c r="R76" s="90">
+      <c r="R76" s="79">
         <v>10.4</v>
       </c>
       <c r="S76" s="49">
@@ -9057,10 +12488,10 @@
         <f t="shared" si="14"/>
         <v>455091.63037003716</v>
       </c>
-      <c r="Q77" s="90">
+      <c r="Q77" s="79">
         <v>17.2</v>
       </c>
-      <c r="R77" s="90">
+      <c r="R77" s="79">
         <v>10.5</v>
       </c>
       <c r="S77" s="49">
@@ -9118,10 +12549,10 @@
         <f t="shared" si="14"/>
         <v>475893.46799453162</v>
       </c>
-      <c r="Q78" s="90">
+      <c r="Q78" s="79">
         <v>16</v>
       </c>
-      <c r="R78" s="90">
+      <c r="R78" s="79">
         <v>10.7</v>
       </c>
       <c r="S78" s="49">
@@ -9179,10 +12610,10 @@
         <f t="shared" si="14"/>
         <v>497287.31219702039</v>
       </c>
-      <c r="Q79" s="90">
+      <c r="Q79" s="79">
         <v>14.6</v>
       </c>
-      <c r="R79" s="90">
+      <c r="R79" s="79">
         <v>10.7</v>
       </c>
       <c r="S79" s="49">
@@ -9240,10 +12671,10 @@
         <f t="shared" si="14"/>
         <v>519071.98236058792</v>
       </c>
-      <c r="Q80" s="90">
+      <c r="Q80" s="79">
         <v>13.4</v>
       </c>
-      <c r="R80" s="90">
+      <c r="R80" s="79">
         <v>11.2</v>
       </c>
       <c r="S80" s="49">
@@ -9301,10 +12732,10 @@
         <f t="shared" si="14"/>
         <v>540958.04273407941</v>
       </c>
-      <c r="Q81" s="91">
+      <c r="Q81" s="80">
         <v>12.1</v>
       </c>
-      <c r="R81" s="91">
+      <c r="R81" s="80">
         <v>11.4</v>
       </c>
       <c r="S81" s="49">
@@ -9362,10 +12793,10 @@
         <f t="shared" si="14"/>
         <v>563123.59691866359</v>
       </c>
-      <c r="Q82" s="91">
+      <c r="Q82" s="80">
         <v>10.7</v>
       </c>
-      <c r="R82" s="91">
+      <c r="R82" s="80">
         <v>12.2</v>
       </c>
       <c r="S82" s="49">
@@ -9423,10 +12854,10 @@
         <f t="shared" si="14"/>
         <v>586011.33811886946</v>
       </c>
-      <c r="Q83" s="91">
+      <c r="Q83" s="80">
         <v>9.4</v>
       </c>
-      <c r="R83" s="91">
+      <c r="R83" s="80">
         <v>14.5</v>
       </c>
       <c r="S83" s="49">
@@ -9484,10 +12915,10 @@
         <f t="shared" si="14"/>
         <v>609727.4687009874</v>
       </c>
-      <c r="Q84" s="91">
+      <c r="Q84" s="80">
         <v>9.6</v>
       </c>
-      <c r="R84" s="91">
+      <c r="R84" s="80">
         <v>15.7</v>
       </c>
       <c r="S84" s="49">
@@ -9545,10 +12976,10 @@
         <f t="shared" si="14"/>
         <v>633936.20833274408</v>
       </c>
-      <c r="Q85" s="91">
+      <c r="Q85" s="80">
         <v>9.3000000000000007</v>
       </c>
-      <c r="R85" s="91">
+      <c r="R85" s="80">
         <v>15</v>
       </c>
       <c r="S85" s="49">
@@ -9606,10 +13037,10 @@
         <f t="shared" si="14"/>
         <v>659232.7192400127</v>
       </c>
-      <c r="Q86" s="91">
+      <c r="Q86" s="80">
         <v>8.9</v>
       </c>
-      <c r="R86" s="91">
+      <c r="R86" s="80">
         <v>14.2</v>
       </c>
       <c r="S86" s="49">
@@ -9667,10 +13098,10 @@
         <f t="shared" si="14"/>
         <v>685798.70659778209</v>
       </c>
-      <c r="Q87" s="91">
+      <c r="Q87" s="80">
         <v>8.6</v>
       </c>
-      <c r="R87" s="91">
+      <c r="R87" s="80">
         <v>13.7</v>
       </c>
       <c r="S87" s="49">
@@ -9728,10 +13159,10 @@
         <f t="shared" si="14"/>
         <v>711904.32679497614</v>
       </c>
-      <c r="Q88" s="91">
+      <c r="Q88" s="80">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R88" s="91">
+      <c r="R88" s="80">
         <v>13.6</v>
       </c>
       <c r="S88" s="49">
@@ -9789,10 +13220,10 @@
         <f t="shared" si="14"/>
         <v>739370.28740483616</v>
       </c>
-      <c r="Q89" s="91">
+      <c r="Q89" s="80">
         <v>8.3000000000000007</v>
       </c>
-      <c r="R89" s="91">
+      <c r="R89" s="80">
         <v>14.7</v>
       </c>
       <c r="S89" s="49">
@@ -9850,10 +13281,10 @@
         <f t="shared" si="14"/>
         <v>767365.7624875583</v>
       </c>
-      <c r="Q90" s="91">
+      <c r="Q90" s="80">
         <v>8.6999999999999993</v>
       </c>
-      <c r="R90" s="91">
+      <c r="R90" s="80">
         <v>15.3</v>
       </c>
       <c r="S90" s="49">
@@ -9911,10 +13342,10 @@
         <f t="shared" si="14"/>
         <v>795161.88833898178</v>
       </c>
-      <c r="Q91" s="91">
+      <c r="Q91" s="80">
         <v>9</v>
       </c>
-      <c r="R91" s="91">
+      <c r="R91" s="80">
         <v>15.6</v>
       </c>
       <c r="S91" s="49">
@@ -9972,10 +13403,10 @@
         <f t="shared" si="14"/>
         <v>822407.31617782335</v>
       </c>
-      <c r="Q92" s="91">
+      <c r="Q92" s="80">
         <v>9.6999999999999993</v>
       </c>
-      <c r="R92" s="91">
+      <c r="R92" s="80">
         <v>16.2</v>
       </c>
       <c r="S92" s="49">
@@ -10033,10 +13464,10 @@
         <f t="shared" si="14"/>
         <v>849079.23756551603</v>
       </c>
-      <c r="Q93" s="91">
+      <c r="Q93" s="80">
         <v>10.199999999999999</v>
       </c>
-      <c r="R93" s="91">
+      <c r="R93" s="80">
         <v>16.399999999999999</v>
       </c>
       <c r="S93" s="49">
@@ -10094,10 +13525,10 @@
         <f t="shared" si="14"/>
         <v>874916.87167048862</v>
       </c>
-      <c r="Q94" s="91">
+      <c r="Q94" s="80">
         <v>10.4</v>
       </c>
-      <c r="R94" s="91">
+      <c r="R94" s="80">
         <v>15.9</v>
       </c>
       <c r="S94" s="49">
@@ -10155,10 +13586,10 @@
         <f t="shared" si="14"/>
         <v>900118.18698623509</v>
       </c>
-      <c r="Q95" s="91">
+      <c r="Q95" s="80">
         <v>10.199999999999999</v>
       </c>
-      <c r="R95" s="91">
+      <c r="R95" s="80">
         <v>16.100000000000001</v>
       </c>
       <c r="S95" s="49">
@@ -10216,10 +13647,10 @@
         <f t="shared" si="14"/>
         <v>924690.01409703225</v>
       </c>
-      <c r="Q96" s="91">
+      <c r="Q96" s="80">
         <v>10.3</v>
       </c>
-      <c r="R96" s="91">
+      <c r="R96" s="80">
         <v>15.1</v>
       </c>
       <c r="S96" s="49">
@@ -10277,10 +13708,10 @@
         <f t="shared" si="14"/>
         <v>949091.94253623113</v>
       </c>
-      <c r="Q97" s="91">
+      <c r="Q97" s="80">
         <v>11.3</v>
       </c>
-      <c r="R97" s="91">
+      <c r="R97" s="80">
         <v>14.6</v>
       </c>
       <c r="S97" s="49">
@@ -10338,10 +13769,10 @@
         <f t="shared" si="14"/>
         <v>973305.38034689892</v>
       </c>
-      <c r="Q98" s="91">
+      <c r="Q98" s="80">
         <v>12</v>
       </c>
-      <c r="R98" s="91">
+      <c r="R98" s="80">
         <v>14.5</v>
       </c>
       <c r="S98" s="49">
@@ -10399,10 +13830,10 @@
         <f t="shared" si="14"/>
         <v>997871.07582029141</v>
       </c>
-      <c r="Q99" s="91">
+      <c r="Q99" s="80">
         <v>12.3</v>
       </c>
-      <c r="R99" s="91">
+      <c r="R99" s="80">
         <v>14.1</v>
       </c>
       <c r="S99" s="49">
@@ -10460,10 +13891,10 @@
         <f t="shared" ref="O100:O110" si="27">F100-M100</f>
         <v>1022285.9914243591</v>
       </c>
-      <c r="Q100" s="91">
+      <c r="Q100" s="80">
         <v>12.5</v>
       </c>
-      <c r="R100" s="91">
+      <c r="R100" s="80">
         <v>14.2</v>
       </c>
       <c r="S100" s="49">
@@ -10521,10 +13952,10 @@
         <f t="shared" si="27"/>
         <v>1046752.7094346917</v>
       </c>
-      <c r="Q101" s="91">
+      <c r="Q101" s="80">
         <v>12.6</v>
       </c>
-      <c r="R101" s="91">
+      <c r="R101" s="80">
         <v>13.5</v>
       </c>
       <c r="S101" s="49">
@@ -10582,10 +14013,10 @@
         <f t="shared" si="27"/>
         <v>1070965.8922170678</v>
       </c>
-      <c r="Q102" s="91">
+      <c r="Q102" s="80">
         <v>13.3</v>
       </c>
-      <c r="R102" s="91">
+      <c r="R102" s="80">
         <v>13.3</v>
       </c>
       <c r="S102" s="49">
@@ -10643,10 +14074,10 @@
         <f t="shared" si="27"/>
         <v>1095039.1627951136</v>
       </c>
-      <c r="Q103" s="91">
+      <c r="Q103" s="80">
         <v>13.2</v>
       </c>
-      <c r="R103" s="91">
+      <c r="R103" s="80">
         <v>13</v>
       </c>
       <c r="S103" s="49">
@@ -10704,10 +14135,10 @@
         <f t="shared" si="27"/>
         <v>1118959.2878258128</v>
       </c>
-      <c r="Q104" s="91">
+      <c r="Q104" s="80">
         <v>13.3</v>
       </c>
-      <c r="R104" s="91">
+      <c r="R104" s="80">
         <v>13.1</v>
       </c>
       <c r="S104" s="49">
@@ -10765,10 +14196,10 @@
         <f t="shared" si="27"/>
         <v>1140470.2500337721</v>
       </c>
-      <c r="Q105" s="91">
+      <c r="Q105" s="80">
         <v>13.3</v>
       </c>
-      <c r="R105" s="91">
+      <c r="R105" s="80">
         <v>13</v>
       </c>
       <c r="S105" s="49">
@@ -10826,10 +14257,10 @@
         <f t="shared" si="27"/>
         <v>1164213.7952915577</v>
       </c>
-      <c r="Q106" s="91">
+      <c r="Q106" s="80">
         <v>12.9</v>
       </c>
-      <c r="R106" s="91">
+      <c r="R106" s="80">
         <v>12.9</v>
       </c>
       <c r="S106" s="49">
@@ -10887,10 +14318,10 @@
         <f t="shared" si="27"/>
         <v>1187862.3302456758</v>
       </c>
-      <c r="Q107" s="91">
+      <c r="Q107" s="80">
         <v>11.5</v>
       </c>
-      <c r="R107" s="91">
+      <c r="R107" s="80">
         <v>12.4</v>
       </c>
       <c r="S107" s="49">
@@ -10948,10 +14379,10 @@
         <f t="shared" si="27"/>
         <v>1211559.2805781388</v>
       </c>
-      <c r="Q108" s="91">
+      <c r="Q108" s="80">
         <v>10.9</v>
       </c>
-      <c r="R108" s="91">
+      <c r="R108" s="80">
         <v>12.5</v>
       </c>
       <c r="S108" s="49">
@@ -11009,10 +14440,10 @@
         <f t="shared" si="27"/>
         <v>1235230.2183836263</v>
       </c>
-      <c r="Q109" s="91">
+      <c r="Q109" s="80">
         <v>10.1</v>
       </c>
-      <c r="R109" s="91">
+      <c r="R109" s="80">
         <v>12.3</v>
       </c>
       <c r="S109" s="49">
@@ -11070,10 +14501,10 @@
         <f t="shared" si="27"/>
         <v>1258674.9653519634</v>
       </c>
-      <c r="Q110" s="91">
+      <c r="Q110" s="80">
         <v>9.8000000000000007</v>
       </c>
-      <c r="R110" s="91">
+      <c r="R110" s="80">
         <v>14.6</v>
       </c>
       <c r="S110" s="49">
@@ -11131,10 +14562,10 @@
         <f t="shared" ref="O111:O114" si="29">F111-M111</f>
         <v>1281130.3700478161</v>
       </c>
-      <c r="Q111" s="91">
+      <c r="Q111" s="80">
         <v>9.4</v>
       </c>
-      <c r="R111" s="91">
+      <c r="R111" s="80">
         <v>17.3</v>
       </c>
       <c r="S111" s="49">
@@ -11192,10 +14623,10 @@
         <f t="shared" si="29"/>
         <v>1304563.4910520914</v>
       </c>
-      <c r="Q112" s="91">
+      <c r="Q112" s="80">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R112" s="91">
+      <c r="R112" s="80">
         <v>13.8</v>
       </c>
       <c r="S112" s="49">
@@ -11253,10 +14684,10 @@
         <f t="shared" si="29"/>
         <v>1327898.3441695699</v>
       </c>
-      <c r="Q113" s="91">
+      <c r="Q113" s="80">
         <v>8.6</v>
       </c>
-      <c r="R113" s="91">
+      <c r="R113" s="80">
         <v>13</v>
       </c>
       <c r="S113" s="49">
@@ -11899,11 +15330,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="78" t="s">
+      <c r="D137" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="78"/>
-      <c r="F137" s="78"/>
+      <c r="E137" s="82"/>
+      <c r="F137" s="82"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -12158,16 +15589,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="78" t="s">
+      <c r="D4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -16735,11 +20166,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="78" t="s">
+      <c r="D137" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="78"/>
-      <c r="F137" s="78"/>
+      <c r="E137" s="82"/>
+      <c r="F137" s="82"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -16990,16 +20421,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="78" t="s">
+      <c r="D4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -21576,11 +25007,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="78" t="s">
+      <c r="D137" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="78"/>
-      <c r="F137" s="78"/>
+      <c r="E137" s="82"/>
+      <c r="F137" s="82"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -21830,16 +25261,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="78" t="s">
+      <c r="D4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -26412,11 +29843,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="78" t="s">
+      <c r="D137" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="78"/>
-      <c r="F137" s="78"/>
+      <c r="E137" s="82"/>
+      <c r="F137" s="82"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -26710,15 +30141,15 @@
       <c r="P5" s="63"/>
       <c r="Q5" s="63"/>
       <c r="R5" s="63"/>
-      <c r="S5" s="81" t="s">
+      <c r="S5" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="81" t="s">
+      <c r="T5" s="88"/>
+      <c r="U5" s="88"/>
+      <c r="V5" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="W5" s="82"/>
+      <c r="W5" s="88"/>
       <c r="X5" s="64"/>
       <c r="Y5" s="63"/>
     </row>
@@ -28101,21 +31532,21 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="86" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79" t="s">
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86" t="s">
         <v>137</v>
       </c>
-      <c r="I5" s="79"/>
-      <c r="J5" s="80" t="s">
+      <c r="I5" s="86"/>
+      <c r="J5" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="K5" s="78"/>
+      <c r="K5" s="82"/>
     </row>
     <row r="6" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
@@ -28739,20 +32170,20 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83" t="s">
+      <c r="C11" s="89"/>
+      <c r="D11" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="83"/>
+      <c r="E11" s="89"/>
     </row>
     <row r="12" spans="1:20" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="85"/>
+      <c r="A12" s="91"/>
       <c r="B12" s="34" t="s">
         <v>98</v>
       </c>
@@ -28774,10 +32205,10 @@
       <c r="J12" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="86" t="s">
+      <c r="K12" s="92" t="s">
         <v>152</v>
       </c>
-      <c r="L12" s="87"/>
+      <c r="L12" s="93"/>
       <c r="M12" s="51" t="s">
         <v>153</v>
       </c>
@@ -28790,10 +32221,10 @@
       <c r="Q12" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="R12" s="86" t="s">
+      <c r="R12" s="92" t="s">
         <v>152</v>
       </c>
-      <c r="S12" s="87"/>
+      <c r="S12" s="93"/>
       <c r="T12" s="51" t="s">
         <v>153</v>
       </c>
@@ -36323,7 +39754,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5D43E-3BF9-467F-A132-8F9ED68CFF3D}">
-  <dimension ref="A2:E101"/>
+  <dimension ref="A2:E203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -37252,7 +40683,7 @@
       <c r="D57" s="3">
         <v>15.8</v>
       </c>
-      <c r="E57" s="92">
+      <c r="E57" s="81">
         <v>10.8</v>
       </c>
     </row>
@@ -38004,9 +41435,1681 @@
         <v>13</v>
       </c>
     </row>
+    <row r="104" spans="1:5" ht="21" x14ac:dyDescent="0.35">
+      <c r="A104" s="37" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B106" s="76" t="s">
+        <v>182</v>
+      </c>
+      <c r="C106" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="D106" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="E106" s="76" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="11">
+        <v>1927</v>
+      </c>
+      <c r="B107" s="94">
+        <v>44.3</v>
+      </c>
+      <c r="C107" s="94">
+        <v>26.7</v>
+      </c>
+      <c r="D107" s="3">
+        <v>49.6</v>
+      </c>
+      <c r="E107" s="3">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="11">
+        <v>1928</v>
+      </c>
+      <c r="B108" s="94">
+        <v>44.3</v>
+      </c>
+      <c r="C108" s="94">
+        <v>26.7</v>
+      </c>
+      <c r="D108" s="3">
+        <v>48.9</v>
+      </c>
+      <c r="E108" s="3">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="11">
+        <v>1929</v>
+      </c>
+      <c r="B109" s="94">
+        <v>44.3</v>
+      </c>
+      <c r="C109" s="94">
+        <v>26.7</v>
+      </c>
+      <c r="D109" s="3">
+        <v>47</v>
+      </c>
+      <c r="E109" s="3">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="11">
+        <v>1930</v>
+      </c>
+      <c r="B110" s="94">
+        <v>49.4</v>
+      </c>
+      <c r="C110" s="94">
+        <v>26.6</v>
+      </c>
+      <c r="D110" s="3">
+        <v>43.9</v>
+      </c>
+      <c r="E110" s="3">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="11">
+        <v>1931</v>
+      </c>
+      <c r="B111" s="94">
+        <v>43.8</v>
+      </c>
+      <c r="C111" s="94">
+        <v>25.9</v>
+      </c>
+      <c r="D111" s="3">
+        <v>43.3</v>
+      </c>
+      <c r="E111" s="3">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="11">
+        <v>1932</v>
+      </c>
+      <c r="B112" s="94">
+        <v>43.3</v>
+      </c>
+      <c r="C112" s="94">
+        <v>26.1</v>
+      </c>
+      <c r="D112" s="3">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E112" s="3">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="11">
+        <v>1933</v>
+      </c>
+      <c r="B113" s="94">
+        <v>42.2</v>
+      </c>
+      <c r="C113" s="94">
+        <v>25.7</v>
+      </c>
+      <c r="D113" s="3">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="E113" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="11">
+        <v>1934</v>
+      </c>
+      <c r="B114" s="94">
+        <v>44.3</v>
+      </c>
+      <c r="C114" s="94">
+        <v>23.8</v>
+      </c>
+      <c r="D114" s="3">
+        <v>28.7</v>
+      </c>
+      <c r="E114" s="3">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="11">
+        <v>1935</v>
+      </c>
+      <c r="B115" s="94">
+        <v>42.3</v>
+      </c>
+      <c r="C115" s="94">
+        <v>22.6</v>
+      </c>
+      <c r="D115" s="3">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E115" s="3">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="11">
+        <v>1936</v>
+      </c>
+      <c r="B116" s="94">
+        <v>43</v>
+      </c>
+      <c r="C116" s="94">
+        <v>23.5</v>
+      </c>
+      <c r="D116" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="E116" s="3">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="11">
+        <v>1937</v>
+      </c>
+      <c r="B117" s="94">
+        <v>44.1</v>
+      </c>
+      <c r="C117" s="94">
+        <v>24.4</v>
+      </c>
+      <c r="D117" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="E117" s="3">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="11">
+        <v>1938</v>
+      </c>
+      <c r="B118" s="94">
+        <v>43.5</v>
+      </c>
+      <c r="C118" s="94">
+        <v>22.9</v>
+      </c>
+      <c r="D118" s="3">
+        <v>40.9</v>
+      </c>
+      <c r="E118" s="3">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="11">
+        <v>1939</v>
+      </c>
+      <c r="B119" s="94">
+        <v>44.6</v>
+      </c>
+      <c r="C119" s="94">
+        <v>23</v>
+      </c>
+      <c r="D119" s="3">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="E119" s="3">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="11">
+        <v>1940</v>
+      </c>
+      <c r="B120" s="94">
+        <v>44.3</v>
+      </c>
+      <c r="C120" s="94">
+        <v>23.2</v>
+      </c>
+      <c r="D120" s="3">
+        <v>34.6</v>
+      </c>
+      <c r="E120" s="3">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="11">
+        <v>1941</v>
+      </c>
+      <c r="B121" s="94">
+        <v>43.5</v>
+      </c>
+      <c r="C121" s="94">
+        <v>22.1</v>
+      </c>
+      <c r="D121" s="3">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="E121" s="3">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="11">
+        <v>1942</v>
+      </c>
+      <c r="B122" s="94">
+        <v>45.5</v>
+      </c>
+      <c r="C122" s="94">
+        <v>22.8</v>
+      </c>
+      <c r="D122" s="3">
+        <v>21.3</v>
+      </c>
+      <c r="E122" s="3">
+        <v>67.900000000000006</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="11">
+        <v>1943</v>
+      </c>
+      <c r="B123" s="94">
+        <v>45.5</v>
+      </c>
+      <c r="C123" s="94">
+        <v>22.4</v>
+      </c>
+      <c r="D123" s="3">
+        <v>12.9</v>
+      </c>
+      <c r="E123" s="3">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="11">
+        <v>1944</v>
+      </c>
+      <c r="B124" s="94">
+        <v>44.2</v>
+      </c>
+      <c r="C124" s="94">
+        <v>20.6</v>
+      </c>
+      <c r="D124" s="3">
+        <v>13.7</v>
+      </c>
+      <c r="E124" s="3">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="11">
+        <v>1945</v>
+      </c>
+      <c r="B125" s="94">
+        <v>44.9</v>
+      </c>
+      <c r="C125" s="94">
+        <v>19.5</v>
+      </c>
+      <c r="D125" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="E125" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="11">
+        <v>1946</v>
+      </c>
+      <c r="B126" s="94">
+        <v>43.7</v>
+      </c>
+      <c r="C126" s="94">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D126" s="3">
+        <v>26</v>
+      </c>
+      <c r="E126" s="3">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="11">
+        <v>1947</v>
+      </c>
+      <c r="B127" s="94">
+        <v>46.1</v>
+      </c>
+      <c r="C127" s="94">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D127" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="E127" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="11">
+        <v>1948</v>
+      </c>
+      <c r="B128" s="94">
+        <v>45.2</v>
+      </c>
+      <c r="C128" s="94">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D128" s="3">
+        <v>25.2</v>
+      </c>
+      <c r="E128" s="3">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="11">
+        <v>1949</v>
+      </c>
+      <c r="B129" s="94">
+        <v>45.2</v>
+      </c>
+      <c r="C129" s="94">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D129" s="3">
+        <v>30.5</v>
+      </c>
+      <c r="E129" s="3">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="11">
+        <v>1950</v>
+      </c>
+      <c r="B130" s="94">
+        <v>45.5</v>
+      </c>
+      <c r="C130" s="94">
+        <v>16.2</v>
+      </c>
+      <c r="D130" s="3">
+        <v>27.8</v>
+      </c>
+      <c r="E130" s="3">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="11">
+        <v>1951</v>
+      </c>
+      <c r="B131" s="94">
+        <v>44.6</v>
+      </c>
+      <c r="C131" s="94">
+        <v>17.3</v>
+      </c>
+      <c r="D131" s="3">
+        <v>28.1</v>
+      </c>
+      <c r="E131" s="3">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="11">
+        <v>1952</v>
+      </c>
+      <c r="B132" s="94">
+        <v>43.8</v>
+      </c>
+      <c r="C132" s="94">
+        <v>15</v>
+      </c>
+      <c r="D132" s="3">
+        <v>27.6</v>
+      </c>
+      <c r="E132" s="3">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="11">
+        <v>1953</v>
+      </c>
+      <c r="B133" s="94">
+        <v>45</v>
+      </c>
+      <c r="C133" s="94">
+        <v>15.9</v>
+      </c>
+      <c r="D133" s="3">
+        <v>26.2</v>
+      </c>
+      <c r="E133" s="3">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="11">
+        <v>1954</v>
+      </c>
+      <c r="B134" s="94">
+        <v>46.4</v>
+      </c>
+      <c r="C134" s="94">
+        <v>13.1</v>
+      </c>
+      <c r="D134" s="3">
+        <v>27.8</v>
+      </c>
+      <c r="E134" s="3">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="11">
+        <v>1955</v>
+      </c>
+      <c r="B135" s="94">
+        <v>46.4</v>
+      </c>
+      <c r="C135" s="94">
+        <v>13.7</v>
+      </c>
+      <c r="D135" s="3">
+        <v>26.4</v>
+      </c>
+      <c r="E135" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="11">
+        <v>1956</v>
+      </c>
+      <c r="B136" s="94">
+        <v>46.8</v>
+      </c>
+      <c r="C136" s="94">
+        <v>12.1</v>
+      </c>
+      <c r="D136" s="3">
+        <v>24.9</v>
+      </c>
+      <c r="E136" s="3">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="11">
+        <v>1957</v>
+      </c>
+      <c r="B137" s="94">
+        <v>47.3</v>
+      </c>
+      <c r="C137" s="94">
+        <v>13.2</v>
+      </c>
+      <c r="D137" s="3">
+        <v>25</v>
+      </c>
+      <c r="E137" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="11">
+        <v>1958</v>
+      </c>
+      <c r="B138" s="94">
+        <v>44.8</v>
+      </c>
+      <c r="C138" s="94">
+        <v>12.5</v>
+      </c>
+      <c r="D138" s="3">
+        <v>24.5</v>
+      </c>
+      <c r="E138" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="11">
+        <v>1959</v>
+      </c>
+      <c r="B139" s="94">
+        <v>47.7</v>
+      </c>
+      <c r="C139" s="94">
+        <v>11.9</v>
+      </c>
+      <c r="D139" s="3">
+        <v>23.7</v>
+      </c>
+      <c r="E139" s="3">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="11">
+        <v>1960</v>
+      </c>
+      <c r="B140" s="94">
+        <v>46</v>
+      </c>
+      <c r="C140" s="94">
+        <v>11.5</v>
+      </c>
+      <c r="D140" s="3">
+        <v>23.2</v>
+      </c>
+      <c r="E140" s="3">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="11">
+        <v>1961</v>
+      </c>
+      <c r="B141" s="94">
+        <v>45.5</v>
+      </c>
+      <c r="C141" s="94">
+        <v>10.7</v>
+      </c>
+      <c r="D141" s="3">
+        <v>21.9</v>
+      </c>
+      <c r="E141" s="3">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="11">
+        <v>1962</v>
+      </c>
+      <c r="B142" s="94">
+        <v>45.6</v>
+      </c>
+      <c r="C142" s="94">
+        <v>10.8</v>
+      </c>
+      <c r="D142" s="3">
+        <v>20.2</v>
+      </c>
+      <c r="E142" s="3">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="11">
+        <v>1963</v>
+      </c>
+      <c r="B143" s="94">
+        <v>45.4</v>
+      </c>
+      <c r="C143" s="94">
+        <v>10.7</v>
+      </c>
+      <c r="D143" s="3">
+        <v>18.8</v>
+      </c>
+      <c r="E143" s="3">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="11">
+        <v>1964</v>
+      </c>
+      <c r="B144" s="94">
+        <v>46.3</v>
+      </c>
+      <c r="C144" s="94">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D144" s="3">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E144" s="3">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="11">
+        <v>1965</v>
+      </c>
+      <c r="B145" s="94">
+        <v>45.7</v>
+      </c>
+      <c r="C145" s="94">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D145" s="3">
+        <v>15.7</v>
+      </c>
+      <c r="E145" s="3">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="11">
+        <v>1966</v>
+      </c>
+      <c r="B146" s="94">
+        <v>45.7</v>
+      </c>
+      <c r="C146" s="94">
+        <v>9.9</v>
+      </c>
+      <c r="D146" s="3">
+        <v>15.3</v>
+      </c>
+      <c r="E146" s="3">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="11">
+        <v>1967</v>
+      </c>
+      <c r="B147" s="94">
+        <v>44.8</v>
+      </c>
+      <c r="C147" s="94">
+        <v>9.5</v>
+      </c>
+      <c r="D147" s="3">
+        <v>14.4</v>
+      </c>
+      <c r="E147" s="3">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="11">
+        <v>1968</v>
+      </c>
+      <c r="B148" s="94">
+        <v>44.5</v>
+      </c>
+      <c r="C148" s="94">
+        <v>9.9</v>
+      </c>
+      <c r="D148" s="3">
+        <v>14.1</v>
+      </c>
+      <c r="E148" s="3">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="11">
+        <v>1969</v>
+      </c>
+      <c r="B149" s="94">
+        <v>44.1</v>
+      </c>
+      <c r="C149" s="94">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="D149" s="3">
+        <v>14.2</v>
+      </c>
+      <c r="E149" s="3">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="11">
+        <v>1970</v>
+      </c>
+      <c r="B150" s="94">
+        <v>43.4</v>
+      </c>
+      <c r="C150" s="94">
+        <v>9.9</v>
+      </c>
+      <c r="D150" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="E150" s="3">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="11">
+        <v>1971</v>
+      </c>
+      <c r="B151" s="94">
+        <v>42.5</v>
+      </c>
+      <c r="C151" s="94">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D151" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="E151" s="3">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="11">
+        <v>1972</v>
+      </c>
+      <c r="B152" s="94">
+        <v>43.2</v>
+      </c>
+      <c r="C152" s="94">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D152" s="3">
+        <v>15.3</v>
+      </c>
+      <c r="E152" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="11">
+        <v>1973</v>
+      </c>
+      <c r="B153" s="94">
+        <v>45.8</v>
+      </c>
+      <c r="C153" s="94">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D153" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="E153" s="3">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="11">
+        <v>1974</v>
+      </c>
+      <c r="B154" s="94">
+        <v>44.9</v>
+      </c>
+      <c r="C154" s="94">
+        <v>7.5</v>
+      </c>
+      <c r="D154" s="3">
+        <v>15.6</v>
+      </c>
+      <c r="E154" s="3">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="11">
+        <v>1975</v>
+      </c>
+      <c r="B155" s="94">
+        <v>40.4</v>
+      </c>
+      <c r="C155" s="94">
+        <v>7.2</v>
+      </c>
+      <c r="D155" s="3">
+        <v>15.7</v>
+      </c>
+      <c r="E155" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="11">
+        <v>1976</v>
+      </c>
+      <c r="B156" s="94">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="C156" s="94">
+        <v>7.6</v>
+      </c>
+      <c r="D156" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="E156" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="11">
+        <v>1977</v>
+      </c>
+      <c r="B157" s="94">
+        <v>38.5</v>
+      </c>
+      <c r="C157" s="94">
+        <v>7.2</v>
+      </c>
+      <c r="D157" s="3">
+        <v>15.8</v>
+      </c>
+      <c r="E157" s="3">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="11">
+        <v>1978</v>
+      </c>
+      <c r="B158" s="94">
+        <v>36.4</v>
+      </c>
+      <c r="C158" s="94">
+        <v>6.5</v>
+      </c>
+      <c r="D158" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="E158" s="3">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="11">
+        <v>1979</v>
+      </c>
+      <c r="B159" s="94">
+        <v>36.9</v>
+      </c>
+      <c r="C159" s="94">
+        <v>6.4</v>
+      </c>
+      <c r="D159" s="3">
+        <v>15.8</v>
+      </c>
+      <c r="E159" s="81">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="11">
+        <v>1980</v>
+      </c>
+      <c r="B160" s="94">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C160" s="94">
+        <v>6.3</v>
+      </c>
+      <c r="D160" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="E160" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="11">
+        <v>1981</v>
+      </c>
+      <c r="B161" s="94">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="C161" s="94">
+        <v>6.1</v>
+      </c>
+      <c r="D161" s="3">
+        <v>16</v>
+      </c>
+      <c r="E161" s="3">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="11">
+        <v>1982</v>
+      </c>
+      <c r="B162" s="94">
+        <v>33.6</v>
+      </c>
+      <c r="C162" s="94">
+        <v>5.8</v>
+      </c>
+      <c r="D162" s="3">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E162" s="3">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="11">
+        <v>1983</v>
+      </c>
+      <c r="B163" s="94">
+        <v>36</v>
+      </c>
+      <c r="C163" s="94">
+        <v>5.7</v>
+      </c>
+      <c r="D163" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="E163" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="11">
+        <v>1984</v>
+      </c>
+      <c r="B164" s="94">
+        <v>34.1</v>
+      </c>
+      <c r="C164" s="94">
+        <v>5.6</v>
+      </c>
+      <c r="D164" s="3">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E164" s="3">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="11">
+        <v>1985</v>
+      </c>
+      <c r="B165" s="94">
+        <v>35.5</v>
+      </c>
+      <c r="C165" s="94">
+        <v>5.5</v>
+      </c>
+      <c r="D165" s="3">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E165" s="3">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="11">
+        <v>1986</v>
+      </c>
+      <c r="B166" s="94">
+        <v>33.9</v>
+      </c>
+      <c r="C166" s="94">
+        <v>5.3</v>
+      </c>
+      <c r="D166" s="3">
+        <v>17.2</v>
+      </c>
+      <c r="E166" s="3">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="11">
+        <v>1987</v>
+      </c>
+      <c r="B167" s="94">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="C167" s="94">
+        <v>5.3</v>
+      </c>
+      <c r="D167" s="3">
+        <v>17.2</v>
+      </c>
+      <c r="E167" s="3">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="11">
+        <v>1988</v>
+      </c>
+      <c r="B168" s="94">
+        <v>33.5</v>
+      </c>
+      <c r="C168" s="94">
+        <v>5.3</v>
+      </c>
+      <c r="D168" s="3">
+        <v>16</v>
+      </c>
+      <c r="E168" s="3">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="11">
+        <v>1989</v>
+      </c>
+      <c r="B169" s="94">
+        <v>32.9</v>
+      </c>
+      <c r="C169" s="94">
+        <v>5.3</v>
+      </c>
+      <c r="D169" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="E169" s="3">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="11">
+        <v>1990</v>
+      </c>
+      <c r="B170" s="94">
+        <v>27.9</v>
+      </c>
+      <c r="C170" s="94">
+        <v>5.6</v>
+      </c>
+      <c r="D170" s="3">
+        <v>13.4</v>
+      </c>
+      <c r="E170" s="3">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="11">
+        <v>1991</v>
+      </c>
+      <c r="B171" s="94">
+        <v>27.5</v>
+      </c>
+      <c r="C171" s="94">
+        <v>5.5</v>
+      </c>
+      <c r="D171" s="3">
+        <v>12.1</v>
+      </c>
+      <c r="E171" s="3">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="11">
+        <v>1992</v>
+      </c>
+      <c r="B172" s="94">
+        <v>27.1</v>
+      </c>
+      <c r="C172" s="94">
+        <v>5.4</v>
+      </c>
+      <c r="D172" s="3">
+        <v>10.7</v>
+      </c>
+      <c r="E172" s="3">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="11">
+        <v>1993</v>
+      </c>
+      <c r="B173" s="94">
+        <v>26.8</v>
+      </c>
+      <c r="C173" s="94">
+        <v>5.3</v>
+      </c>
+      <c r="D173" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="E173" s="3">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="11">
+        <v>1994</v>
+      </c>
+      <c r="B174" s="94">
+        <v>26.3</v>
+      </c>
+      <c r="C174" s="94">
+        <v>5.3</v>
+      </c>
+      <c r="D174" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="E174" s="3">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="11">
+        <v>1995</v>
+      </c>
+      <c r="B175" s="94">
+        <v>25.9</v>
+      </c>
+      <c r="C175" s="94">
+        <v>5.2</v>
+      </c>
+      <c r="D175" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E175" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="11">
+        <v>1996</v>
+      </c>
+      <c r="B176" s="94">
+        <v>25.4</v>
+      </c>
+      <c r="C176" s="94">
+        <v>5.2</v>
+      </c>
+      <c r="D176" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="E176" s="3">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="11">
+        <v>1997</v>
+      </c>
+      <c r="B177" s="94">
+        <v>24.8</v>
+      </c>
+      <c r="C177" s="94">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D177" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="E177" s="3">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="11">
+        <v>1998</v>
+      </c>
+      <c r="B178" s="94">
+        <v>24.3</v>
+      </c>
+      <c r="C178" s="94">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D178" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E178" s="3">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="11">
+        <v>1999</v>
+      </c>
+      <c r="B179" s="94">
+        <v>23.9</v>
+      </c>
+      <c r="C179" s="94">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D179" s="3">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E179" s="3">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="11">
+        <v>2000</v>
+      </c>
+      <c r="B180" s="94">
+        <v>23.4</v>
+      </c>
+      <c r="C180" s="94">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D180" s="3">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E180" s="3">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="11">
+        <v>2001</v>
+      </c>
+      <c r="B181" s="94">
+        <v>23</v>
+      </c>
+      <c r="C181" s="94">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D181" s="3">
+        <v>9</v>
+      </c>
+      <c r="E181" s="3">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="11">
+        <v>2002</v>
+      </c>
+      <c r="B182" s="94">
+        <v>22.6</v>
+      </c>
+      <c r="C182" s="94">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D182" s="3">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E182" s="3">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="11">
+        <v>2003</v>
+      </c>
+      <c r="B183" s="94">
+        <v>22.2</v>
+      </c>
+      <c r="C183" s="94">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D183" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E183" s="3">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="11">
+        <v>2004</v>
+      </c>
+      <c r="B184" s="94">
+        <v>21.8</v>
+      </c>
+      <c r="C184" s="94">
+        <v>5.2</v>
+      </c>
+      <c r="D184" s="3">
+        <v>10.4</v>
+      </c>
+      <c r="E184" s="3">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="11">
+        <v>2005</v>
+      </c>
+      <c r="B185" s="94">
+        <v>21.5</v>
+      </c>
+      <c r="C185" s="94">
+        <v>5.2</v>
+      </c>
+      <c r="D185" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E185" s="3">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="11">
+        <v>2006</v>
+      </c>
+      <c r="B186" s="94">
+        <v>21.1</v>
+      </c>
+      <c r="C186" s="94">
+        <v>5.3</v>
+      </c>
+      <c r="D186" s="3">
+        <v>10.3</v>
+      </c>
+      <c r="E186" s="3">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="11">
+        <v>2007</v>
+      </c>
+      <c r="B187" s="94">
+        <v>20.8</v>
+      </c>
+      <c r="C187" s="94">
+        <v>5.3</v>
+      </c>
+      <c r="D187" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="E187" s="3">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="11">
+        <v>2008</v>
+      </c>
+      <c r="B188" s="94">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="C188" s="94">
+        <v>5.4</v>
+      </c>
+      <c r="D188" s="3">
+        <v>12</v>
+      </c>
+      <c r="E188" s="3">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="11">
+        <v>2009</v>
+      </c>
+      <c r="B189" s="94">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="C189" s="94">
+        <v>5.5</v>
+      </c>
+      <c r="D189" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="E189" s="3">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="11">
+        <v>2010</v>
+      </c>
+      <c r="B190" s="94">
+        <v>19.7</v>
+      </c>
+      <c r="C190" s="94">
+        <v>5.6</v>
+      </c>
+      <c r="D190" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E190" s="3">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="11">
+        <v>2011</v>
+      </c>
+      <c r="B191" s="94">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="C191" s="94">
+        <v>5.6</v>
+      </c>
+      <c r="D191" s="3">
+        <v>12.6</v>
+      </c>
+      <c r="E191" s="3">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="11">
+        <v>2012</v>
+      </c>
+      <c r="B192" s="94">
+        <v>19.2</v>
+      </c>
+      <c r="C192" s="94">
+        <v>5.7</v>
+      </c>
+      <c r="D192" s="3">
+        <v>13.3</v>
+      </c>
+      <c r="E192" s="3">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="11">
+        <v>2013</v>
+      </c>
+      <c r="B193" s="94">
+        <v>19</v>
+      </c>
+      <c r="C193" s="94">
+        <v>5.7</v>
+      </c>
+      <c r="D193" s="3">
+        <v>13.2</v>
+      </c>
+      <c r="E193" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="11">
+        <v>2014</v>
+      </c>
+      <c r="B194" s="94">
+        <v>18.7</v>
+      </c>
+      <c r="C194" s="94">
+        <v>5.7</v>
+      </c>
+      <c r="D194" s="3">
+        <v>13.3</v>
+      </c>
+      <c r="E194" s="3">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="11">
+        <v>2015</v>
+      </c>
+      <c r="B195" s="95">
+        <v>18.5</v>
+      </c>
+      <c r="C195" s="95">
+        <v>5.8</v>
+      </c>
+      <c r="D195" s="3">
+        <v>13.3</v>
+      </c>
+      <c r="E195" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="11">
+        <v>2016</v>
+      </c>
+      <c r="B196" s="95">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="C196" s="95">
+        <v>5.8</v>
+      </c>
+      <c r="D196" s="3">
+        <v>12.9</v>
+      </c>
+      <c r="E196" s="3">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="11">
+        <v>2017</v>
+      </c>
+      <c r="B197" s="95">
+        <v>17.8</v>
+      </c>
+      <c r="C197" s="95">
+        <v>5.9</v>
+      </c>
+      <c r="D197" s="3">
+        <v>11.5</v>
+      </c>
+      <c r="E197" s="3">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="11">
+        <v>2018</v>
+      </c>
+      <c r="B198" s="95">
+        <v>17.5</v>
+      </c>
+      <c r="C198" s="95">
+        <v>6</v>
+      </c>
+      <c r="D198" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="E198" s="3">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="11">
+        <v>2019</v>
+      </c>
+      <c r="B199" s="95">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="C199" s="95">
+        <v>6</v>
+      </c>
+      <c r="D199" s="3">
+        <v>10.1</v>
+      </c>
+      <c r="E199" s="3">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="11">
+        <v>2020</v>
+      </c>
+      <c r="B200" s="95">
+        <v>16.8</v>
+      </c>
+      <c r="C200" s="95">
+        <v>6.1</v>
+      </c>
+      <c r="D200" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E200" s="3">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="11">
+        <v>2021</v>
+      </c>
+      <c r="B201" s="94">
+        <v>16.3</v>
+      </c>
+      <c r="C201" s="94">
+        <v>9.5</v>
+      </c>
+      <c r="D201" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="E201" s="3">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="11">
+        <v>2022</v>
+      </c>
+      <c r="B202" s="94">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C202" s="94">
+        <v>6.1</v>
+      </c>
+      <c r="D202" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E202" s="3">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="11">
+        <v>2023</v>
+      </c>
+      <c r="B203" s="94">
+        <v>15.8</v>
+      </c>
+      <c r="C203" s="94">
+        <v>6.1</v>
+      </c>
+      <c r="D203" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="E203" s="3">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE464E4-26E0-4468-BB93-27F427E76385}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBC62F3-557F-466E-8DE3-26C9F45408BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="8" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="4" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="9" r:id="rId1"/>
@@ -1073,6 +1073,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1108,12 +1114,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8305,41 +8305,41 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="85" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82" t="s">
+      <c r="C3" s="84"/>
+      <c r="D3" s="84" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="86" t="s">
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86" t="s">
+      <c r="E4" s="88"/>
+      <c r="F4" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="Q4" s="84" t="s">
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="Q4" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="R4" s="84"/>
-      <c r="S4" s="85" t="s">
+      <c r="R4" s="86"/>
+      <c r="S4" s="87" t="s">
         <v>164</v>
       </c>
-      <c r="T4" s="85"/>
+      <c r="T4" s="87"/>
     </row>
     <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -15330,11 +15330,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="82" t="s">
+      <c r="D137" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="82"/>
-      <c r="F137" s="82"/>
+      <c r="E137" s="84"/>
+      <c r="F137" s="84"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -15589,16 +15589,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82" t="s">
+      <c r="E4" s="84"/>
+      <c r="F4" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -20166,11 +20166,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="82" t="s">
+      <c r="D137" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="82"/>
-      <c r="F137" s="82"/>
+      <c r="E137" s="84"/>
+      <c r="F137" s="84"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -20421,16 +20421,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82" t="s">
+      <c r="E4" s="84"/>
+      <c r="F4" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -25007,11 +25007,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="82" t="s">
+      <c r="D137" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="82"/>
-      <c r="F137" s="82"/>
+      <c r="E137" s="84"/>
+      <c r="F137" s="84"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -25261,16 +25261,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82" t="s">
+      <c r="E4" s="84"/>
+      <c r="F4" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -29843,11 +29843,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="82" t="s">
+      <c r="D137" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="82"/>
-      <c r="F137" s="82"/>
+      <c r="E137" s="84"/>
+      <c r="F137" s="84"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -30141,15 +30141,15 @@
       <c r="P5" s="63"/>
       <c r="Q5" s="63"/>
       <c r="R5" s="63"/>
-      <c r="S5" s="87" t="s">
+      <c r="S5" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="88"/>
-      <c r="U5" s="88"/>
-      <c r="V5" s="87" t="s">
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="W5" s="88"/>
+      <c r="W5" s="90"/>
       <c r="X5" s="64"/>
       <c r="Y5" s="63"/>
     </row>
@@ -31532,21 +31532,21 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="88" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86" t="s">
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="I5" s="86"/>
-      <c r="J5" s="83" t="s">
+      <c r="I5" s="88"/>
+      <c r="J5" s="85" t="s">
         <v>133</v>
       </c>
-      <c r="K5" s="82"/>
+      <c r="K5" s="84"/>
     </row>
     <row r="6" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
@@ -32170,20 +32170,20 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="89" t="s">
+      <c r="B11" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="89"/>
-      <c r="D11" s="89" t="s">
+      <c r="C11" s="91"/>
+      <c r="D11" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="89"/>
+      <c r="E11" s="91"/>
     </row>
     <row r="12" spans="1:20" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="91"/>
+      <c r="A12" s="93"/>
       <c r="B12" s="34" t="s">
         <v>98</v>
       </c>
@@ -32205,10 +32205,10 @@
       <c r="J12" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="92" t="s">
+      <c r="K12" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="L12" s="93"/>
+      <c r="L12" s="95"/>
       <c r="M12" s="51" t="s">
         <v>153</v>
       </c>
@@ -32221,10 +32221,10 @@
       <c r="Q12" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="R12" s="92" t="s">
+      <c r="R12" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="S12" s="93"/>
+      <c r="S12" s="95"/>
       <c r="T12" s="51" t="s">
         <v>153</v>
       </c>
@@ -41461,10 +41461,10 @@
       <c r="A107" s="11">
         <v>1927</v>
       </c>
-      <c r="B107" s="94">
+      <c r="B107" s="82">
         <v>44.3</v>
       </c>
-      <c r="C107" s="94">
+      <c r="C107" s="82">
         <v>26.7</v>
       </c>
       <c r="D107" s="3">
@@ -41478,10 +41478,10 @@
       <c r="A108" s="11">
         <v>1928</v>
       </c>
-      <c r="B108" s="94">
+      <c r="B108" s="82">
         <v>44.3</v>
       </c>
-      <c r="C108" s="94">
+      <c r="C108" s="82">
         <v>26.7</v>
       </c>
       <c r="D108" s="3">
@@ -41495,10 +41495,10 @@
       <c r="A109" s="11">
         <v>1929</v>
       </c>
-      <c r="B109" s="94">
+      <c r="B109" s="82">
         <v>44.3</v>
       </c>
-      <c r="C109" s="94">
+      <c r="C109" s="82">
         <v>26.7</v>
       </c>
       <c r="D109" s="3">
@@ -41512,10 +41512,10 @@
       <c r="A110" s="11">
         <v>1930</v>
       </c>
-      <c r="B110" s="94">
+      <c r="B110" s="82">
         <v>49.4</v>
       </c>
-      <c r="C110" s="94">
+      <c r="C110" s="82">
         <v>26.6</v>
       </c>
       <c r="D110" s="3">
@@ -41529,10 +41529,10 @@
       <c r="A111" s="11">
         <v>1931</v>
       </c>
-      <c r="B111" s="94">
+      <c r="B111" s="82">
         <v>43.8</v>
       </c>
-      <c r="C111" s="94">
+      <c r="C111" s="82">
         <v>25.9</v>
       </c>
       <c r="D111" s="3">
@@ -41546,10 +41546,10 @@
       <c r="A112" s="11">
         <v>1932</v>
       </c>
-      <c r="B112" s="94">
+      <c r="B112" s="82">
         <v>43.3</v>
       </c>
-      <c r="C112" s="94">
+      <c r="C112" s="82">
         <v>26.1</v>
       </c>
       <c r="D112" s="3">
@@ -41563,10 +41563,10 @@
       <c r="A113" s="11">
         <v>1933</v>
       </c>
-      <c r="B113" s="94">
+      <c r="B113" s="82">
         <v>42.2</v>
       </c>
-      <c r="C113" s="94">
+      <c r="C113" s="82">
         <v>25.7</v>
       </c>
       <c r="D113" s="3">
@@ -41580,10 +41580,10 @@
       <c r="A114" s="11">
         <v>1934</v>
       </c>
-      <c r="B114" s="94">
+      <c r="B114" s="82">
         <v>44.3</v>
       </c>
-      <c r="C114" s="94">
+      <c r="C114" s="82">
         <v>23.8</v>
       </c>
       <c r="D114" s="3">
@@ -41597,10 +41597,10 @@
       <c r="A115" s="11">
         <v>1935</v>
       </c>
-      <c r="B115" s="94">
+      <c r="B115" s="82">
         <v>42.3</v>
       </c>
-      <c r="C115" s="94">
+      <c r="C115" s="82">
         <v>22.6</v>
       </c>
       <c r="D115" s="3">
@@ -41614,10 +41614,10 @@
       <c r="A116" s="11">
         <v>1936</v>
       </c>
-      <c r="B116" s="94">
+      <c r="B116" s="82">
         <v>43</v>
       </c>
-      <c r="C116" s="94">
+      <c r="C116" s="82">
         <v>23.5</v>
       </c>
       <c r="D116" s="3">
@@ -41631,10 +41631,10 @@
       <c r="A117" s="11">
         <v>1937</v>
       </c>
-      <c r="B117" s="94">
+      <c r="B117" s="82">
         <v>44.1</v>
       </c>
-      <c r="C117" s="94">
+      <c r="C117" s="82">
         <v>24.4</v>
       </c>
       <c r="D117" s="3">
@@ -41648,10 +41648,10 @@
       <c r="A118" s="11">
         <v>1938</v>
       </c>
-      <c r="B118" s="94">
+      <c r="B118" s="82">
         <v>43.5</v>
       </c>
-      <c r="C118" s="94">
+      <c r="C118" s="82">
         <v>22.9</v>
       </c>
       <c r="D118" s="3">
@@ -41665,10 +41665,10 @@
       <c r="A119" s="11">
         <v>1939</v>
       </c>
-      <c r="B119" s="94">
+      <c r="B119" s="82">
         <v>44.6</v>
       </c>
-      <c r="C119" s="94">
+      <c r="C119" s="82">
         <v>23</v>
       </c>
       <c r="D119" s="3">
@@ -41682,10 +41682,10 @@
       <c r="A120" s="11">
         <v>1940</v>
       </c>
-      <c r="B120" s="94">
+      <c r="B120" s="82">
         <v>44.3</v>
       </c>
-      <c r="C120" s="94">
+      <c r="C120" s="82">
         <v>23.2</v>
       </c>
       <c r="D120" s="3">
@@ -41699,10 +41699,10 @@
       <c r="A121" s="11">
         <v>1941</v>
       </c>
-      <c r="B121" s="94">
+      <c r="B121" s="82">
         <v>43.5</v>
       </c>
-      <c r="C121" s="94">
+      <c r="C121" s="82">
         <v>22.1</v>
       </c>
       <c r="D121" s="3">
@@ -41716,10 +41716,10 @@
       <c r="A122" s="11">
         <v>1942</v>
       </c>
-      <c r="B122" s="94">
+      <c r="B122" s="82">
         <v>45.5</v>
       </c>
-      <c r="C122" s="94">
+      <c r="C122" s="82">
         <v>22.8</v>
       </c>
       <c r="D122" s="3">
@@ -41733,10 +41733,10 @@
       <c r="A123" s="11">
         <v>1943</v>
       </c>
-      <c r="B123" s="94">
+      <c r="B123" s="82">
         <v>45.5</v>
       </c>
-      <c r="C123" s="94">
+      <c r="C123" s="82">
         <v>22.4</v>
       </c>
       <c r="D123" s="3">
@@ -41750,10 +41750,10 @@
       <c r="A124" s="11">
         <v>1944</v>
       </c>
-      <c r="B124" s="94">
+      <c r="B124" s="82">
         <v>44.2</v>
       </c>
-      <c r="C124" s="94">
+      <c r="C124" s="82">
         <v>20.6</v>
       </c>
       <c r="D124" s="3">
@@ -41767,10 +41767,10 @@
       <c r="A125" s="11">
         <v>1945</v>
       </c>
-      <c r="B125" s="94">
+      <c r="B125" s="82">
         <v>44.9</v>
       </c>
-      <c r="C125" s="94">
+      <c r="C125" s="82">
         <v>19.5</v>
       </c>
       <c r="D125" s="3">
@@ -41784,10 +41784,10 @@
       <c r="A126" s="11">
         <v>1946</v>
       </c>
-      <c r="B126" s="94">
+      <c r="B126" s="82">
         <v>43.7</v>
       </c>
-      <c r="C126" s="94">
+      <c r="C126" s="82">
         <v>19.399999999999999</v>
       </c>
       <c r="D126" s="3">
@@ -41801,10 +41801,10 @@
       <c r="A127" s="11">
         <v>1947</v>
       </c>
-      <c r="B127" s="94">
+      <c r="B127" s="82">
         <v>46.1</v>
       </c>
-      <c r="C127" s="94">
+      <c r="C127" s="82">
         <v>16.600000000000001</v>
       </c>
       <c r="D127" s="3">
@@ -41818,10 +41818,10 @@
       <c r="A128" s="11">
         <v>1948</v>
       </c>
-      <c r="B128" s="94">
+      <c r="B128" s="82">
         <v>45.2</v>
       </c>
-      <c r="C128" s="94">
+      <c r="C128" s="82">
         <v>16.899999999999999</v>
       </c>
       <c r="D128" s="3">
@@ -41835,10 +41835,10 @@
       <c r="A129" s="11">
         <v>1949</v>
       </c>
-      <c r="B129" s="94">
+      <c r="B129" s="82">
         <v>45.2</v>
       </c>
-      <c r="C129" s="94">
+      <c r="C129" s="82">
         <v>17.899999999999999</v>
       </c>
       <c r="D129" s="3">
@@ -41852,10 +41852,10 @@
       <c r="A130" s="11">
         <v>1950</v>
       </c>
-      <c r="B130" s="94">
+      <c r="B130" s="82">
         <v>45.5</v>
       </c>
-      <c r="C130" s="94">
+      <c r="C130" s="82">
         <v>16.2</v>
       </c>
       <c r="D130" s="3">
@@ -41869,10 +41869,10 @@
       <c r="A131" s="11">
         <v>1951</v>
       </c>
-      <c r="B131" s="94">
+      <c r="B131" s="82">
         <v>44.6</v>
       </c>
-      <c r="C131" s="94">
+      <c r="C131" s="82">
         <v>17.3</v>
       </c>
       <c r="D131" s="3">
@@ -41886,10 +41886,10 @@
       <c r="A132" s="11">
         <v>1952</v>
       </c>
-      <c r="B132" s="94">
+      <c r="B132" s="82">
         <v>43.8</v>
       </c>
-      <c r="C132" s="94">
+      <c r="C132" s="82">
         <v>15</v>
       </c>
       <c r="D132" s="3">
@@ -41903,10 +41903,10 @@
       <c r="A133" s="11">
         <v>1953</v>
       </c>
-      <c r="B133" s="94">
+      <c r="B133" s="82">
         <v>45</v>
       </c>
-      <c r="C133" s="94">
+      <c r="C133" s="82">
         <v>15.9</v>
       </c>
       <c r="D133" s="3">
@@ -41920,10 +41920,10 @@
       <c r="A134" s="11">
         <v>1954</v>
       </c>
-      <c r="B134" s="94">
+      <c r="B134" s="82">
         <v>46.4</v>
       </c>
-      <c r="C134" s="94">
+      <c r="C134" s="82">
         <v>13.1</v>
       </c>
       <c r="D134" s="3">
@@ -41937,10 +41937,10 @@
       <c r="A135" s="11">
         <v>1955</v>
       </c>
-      <c r="B135" s="94">
+      <c r="B135" s="82">
         <v>46.4</v>
       </c>
-      <c r="C135" s="94">
+      <c r="C135" s="82">
         <v>13.7</v>
       </c>
       <c r="D135" s="3">
@@ -41954,10 +41954,10 @@
       <c r="A136" s="11">
         <v>1956</v>
       </c>
-      <c r="B136" s="94">
+      <c r="B136" s="82">
         <v>46.8</v>
       </c>
-      <c r="C136" s="94">
+      <c r="C136" s="82">
         <v>12.1</v>
       </c>
       <c r="D136" s="3">
@@ -41971,10 +41971,10 @@
       <c r="A137" s="11">
         <v>1957</v>
       </c>
-      <c r="B137" s="94">
+      <c r="B137" s="82">
         <v>47.3</v>
       </c>
-      <c r="C137" s="94">
+      <c r="C137" s="82">
         <v>13.2</v>
       </c>
       <c r="D137" s="3">
@@ -41988,10 +41988,10 @@
       <c r="A138" s="11">
         <v>1958</v>
       </c>
-      <c r="B138" s="94">
+      <c r="B138" s="82">
         <v>44.8</v>
       </c>
-      <c r="C138" s="94">
+      <c r="C138" s="82">
         <v>12.5</v>
       </c>
       <c r="D138" s="3">
@@ -42005,10 +42005,10 @@
       <c r="A139" s="11">
         <v>1959</v>
       </c>
-      <c r="B139" s="94">
+      <c r="B139" s="82">
         <v>47.7</v>
       </c>
-      <c r="C139" s="94">
+      <c r="C139" s="82">
         <v>11.9</v>
       </c>
       <c r="D139" s="3">
@@ -42022,10 +42022,10 @@
       <c r="A140" s="11">
         <v>1960</v>
       </c>
-      <c r="B140" s="94">
+      <c r="B140" s="82">
         <v>46</v>
       </c>
-      <c r="C140" s="94">
+      <c r="C140" s="82">
         <v>11.5</v>
       </c>
       <c r="D140" s="3">
@@ -42039,10 +42039,10 @@
       <c r="A141" s="11">
         <v>1961</v>
       </c>
-      <c r="B141" s="94">
+      <c r="B141" s="82">
         <v>45.5</v>
       </c>
-      <c r="C141" s="94">
+      <c r="C141" s="82">
         <v>10.7</v>
       </c>
       <c r="D141" s="3">
@@ -42056,10 +42056,10 @@
       <c r="A142" s="11">
         <v>1962</v>
       </c>
-      <c r="B142" s="94">
+      <c r="B142" s="82">
         <v>45.6</v>
       </c>
-      <c r="C142" s="94">
+      <c r="C142" s="82">
         <v>10.8</v>
       </c>
       <c r="D142" s="3">
@@ -42073,10 +42073,10 @@
       <c r="A143" s="11">
         <v>1963</v>
       </c>
-      <c r="B143" s="94">
+      <c r="B143" s="82">
         <v>45.4</v>
       </c>
-      <c r="C143" s="94">
+      <c r="C143" s="82">
         <v>10.7</v>
       </c>
       <c r="D143" s="3">
@@ -42090,10 +42090,10 @@
       <c r="A144" s="11">
         <v>1964</v>
       </c>
-      <c r="B144" s="94">
+      <c r="B144" s="82">
         <v>46.3</v>
       </c>
-      <c r="C144" s="94">
+      <c r="C144" s="82">
         <v>10.199999999999999</v>
       </c>
       <c r="D144" s="3">
@@ -42107,10 +42107,10 @@
       <c r="A145" s="11">
         <v>1965</v>
       </c>
-      <c r="B145" s="94">
+      <c r="B145" s="82">
         <v>45.7</v>
       </c>
-      <c r="C145" s="94">
+      <c r="C145" s="82">
         <v>9.8000000000000007</v>
       </c>
       <c r="D145" s="3">
@@ -42124,10 +42124,10 @@
       <c r="A146" s="11">
         <v>1966</v>
       </c>
-      <c r="B146" s="94">
+      <c r="B146" s="82">
         <v>45.7</v>
       </c>
-      <c r="C146" s="94">
+      <c r="C146" s="82">
         <v>9.9</v>
       </c>
       <c r="D146" s="3">
@@ -42141,10 +42141,10 @@
       <c r="A147" s="11">
         <v>1967</v>
       </c>
-      <c r="B147" s="94">
+      <c r="B147" s="82">
         <v>44.8</v>
       </c>
-      <c r="C147" s="94">
+      <c r="C147" s="82">
         <v>9.5</v>
       </c>
       <c r="D147" s="3">
@@ -42158,10 +42158,10 @@
       <c r="A148" s="11">
         <v>1968</v>
       </c>
-      <c r="B148" s="94">
+      <c r="B148" s="82">
         <v>44.5</v>
       </c>
-      <c r="C148" s="94">
+      <c r="C148" s="82">
         <v>9.9</v>
       </c>
       <c r="D148" s="3">
@@ -42175,10 +42175,10 @@
       <c r="A149" s="11">
         <v>1969</v>
       </c>
-      <c r="B149" s="94">
+      <c r="B149" s="82">
         <v>44.1</v>
       </c>
-      <c r="C149" s="94">
+      <c r="C149" s="82">
         <v>9.6999999999999993</v>
       </c>
       <c r="D149" s="3">
@@ -42192,10 +42192,10 @@
       <c r="A150" s="11">
         <v>1970</v>
       </c>
-      <c r="B150" s="94">
+      <c r="B150" s="82">
         <v>43.4</v>
       </c>
-      <c r="C150" s="94">
+      <c r="C150" s="82">
         <v>9.9</v>
       </c>
       <c r="D150" s="3">
@@ -42209,10 +42209,10 @@
       <c r="A151" s="11">
         <v>1971</v>
       </c>
-      <c r="B151" s="94">
+      <c r="B151" s="82">
         <v>42.5</v>
       </c>
-      <c r="C151" s="94">
+      <c r="C151" s="82">
         <v>8.6999999999999993</v>
       </c>
       <c r="D151" s="3">
@@ -42226,10 +42226,10 @@
       <c r="A152" s="11">
         <v>1972</v>
       </c>
-      <c r="B152" s="94">
+      <c r="B152" s="82">
         <v>43.2</v>
       </c>
-      <c r="C152" s="94">
+      <c r="C152" s="82">
         <v>8.8000000000000007</v>
       </c>
       <c r="D152" s="3">
@@ -42243,10 +42243,10 @@
       <c r="A153" s="11">
         <v>1973</v>
       </c>
-      <c r="B153" s="94">
+      <c r="B153" s="82">
         <v>45.8</v>
       </c>
-      <c r="C153" s="94">
+      <c r="C153" s="82">
         <v>8.1999999999999993</v>
       </c>
       <c r="D153" s="3">
@@ -42260,10 +42260,10 @@
       <c r="A154" s="11">
         <v>1974</v>
       </c>
-      <c r="B154" s="94">
+      <c r="B154" s="82">
         <v>44.9</v>
       </c>
-      <c r="C154" s="94">
+      <c r="C154" s="82">
         <v>7.5</v>
       </c>
       <c r="D154" s="3">
@@ -42277,10 +42277,10 @@
       <c r="A155" s="11">
         <v>1975</v>
       </c>
-      <c r="B155" s="94">
+      <c r="B155" s="82">
         <v>40.4</v>
       </c>
-      <c r="C155" s="94">
+      <c r="C155" s="82">
         <v>7.2</v>
       </c>
       <c r="D155" s="3">
@@ -42294,10 +42294,10 @@
       <c r="A156" s="11">
         <v>1976</v>
       </c>
-      <c r="B156" s="94">
+      <c r="B156" s="82">
         <v>39.299999999999997</v>
       </c>
-      <c r="C156" s="94">
+      <c r="C156" s="82">
         <v>7.6</v>
       </c>
       <c r="D156" s="3">
@@ -42311,10 +42311,10 @@
       <c r="A157" s="11">
         <v>1977</v>
       </c>
-      <c r="B157" s="94">
+      <c r="B157" s="82">
         <v>38.5</v>
       </c>
-      <c r="C157" s="94">
+      <c r="C157" s="82">
         <v>7.2</v>
       </c>
       <c r="D157" s="3">
@@ -42328,10 +42328,10 @@
       <c r="A158" s="11">
         <v>1978</v>
       </c>
-      <c r="B158" s="94">
+      <c r="B158" s="82">
         <v>36.4</v>
       </c>
-      <c r="C158" s="94">
+      <c r="C158" s="82">
         <v>6.5</v>
       </c>
       <c r="D158" s="3">
@@ -42345,10 +42345,10 @@
       <c r="A159" s="11">
         <v>1979</v>
       </c>
-      <c r="B159" s="94">
+      <c r="B159" s="82">
         <v>36.9</v>
       </c>
-      <c r="C159" s="94">
+      <c r="C159" s="82">
         <v>6.4</v>
       </c>
       <c r="D159" s="3">
@@ -42362,10 +42362,10 @@
       <c r="A160" s="11">
         <v>1980</v>
       </c>
-      <c r="B160" s="94">
+      <c r="B160" s="82">
         <v>36.299999999999997</v>
       </c>
-      <c r="C160" s="94">
+      <c r="C160" s="82">
         <v>6.3</v>
       </c>
       <c r="D160" s="3">
@@ -42379,10 +42379,10 @@
       <c r="A161" s="11">
         <v>1981</v>
       </c>
-      <c r="B161" s="94">
+      <c r="B161" s="82">
         <v>36.299999999999997</v>
       </c>
-      <c r="C161" s="94">
+      <c r="C161" s="82">
         <v>6.1</v>
       </c>
       <c r="D161" s="3">
@@ -42396,10 +42396,10 @@
       <c r="A162" s="11">
         <v>1982</v>
       </c>
-      <c r="B162" s="94">
+      <c r="B162" s="82">
         <v>33.6</v>
       </c>
-      <c r="C162" s="94">
+      <c r="C162" s="82">
         <v>5.8</v>
       </c>
       <c r="D162" s="3">
@@ -42413,10 +42413,10 @@
       <c r="A163" s="11">
         <v>1983</v>
       </c>
-      <c r="B163" s="94">
+      <c r="B163" s="82">
         <v>36</v>
       </c>
-      <c r="C163" s="94">
+      <c r="C163" s="82">
         <v>5.7</v>
       </c>
       <c r="D163" s="3">
@@ -42430,10 +42430,10 @@
       <c r="A164" s="11">
         <v>1984</v>
       </c>
-      <c r="B164" s="94">
+      <c r="B164" s="82">
         <v>34.1</v>
       </c>
-      <c r="C164" s="94">
+      <c r="C164" s="82">
         <v>5.6</v>
       </c>
       <c r="D164" s="3">
@@ -42447,10 +42447,10 @@
       <c r="A165" s="11">
         <v>1985</v>
       </c>
-      <c r="B165" s="94">
+      <c r="B165" s="82">
         <v>35.5</v>
       </c>
-      <c r="C165" s="94">
+      <c r="C165" s="82">
         <v>5.5</v>
       </c>
       <c r="D165" s="3">
@@ -42464,10 +42464,10 @@
       <c r="A166" s="11">
         <v>1986</v>
       </c>
-      <c r="B166" s="94">
+      <c r="B166" s="82">
         <v>33.9</v>
       </c>
-      <c r="C166" s="94">
+      <c r="C166" s="82">
         <v>5.3</v>
       </c>
       <c r="D166" s="3">
@@ -42481,10 +42481,10 @@
       <c r="A167" s="11">
         <v>1987</v>
       </c>
-      <c r="B167" s="94">
+      <c r="B167" s="82">
         <v>36.200000000000003</v>
       </c>
-      <c r="C167" s="94">
+      <c r="C167" s="82">
         <v>5.3</v>
       </c>
       <c r="D167" s="3">
@@ -42498,10 +42498,10 @@
       <c r="A168" s="11">
         <v>1988</v>
       </c>
-      <c r="B168" s="94">
+      <c r="B168" s="82">
         <v>33.5</v>
       </c>
-      <c r="C168" s="94">
+      <c r="C168" s="82">
         <v>5.3</v>
       </c>
       <c r="D168" s="3">
@@ -42515,10 +42515,10 @@
       <c r="A169" s="11">
         <v>1989</v>
       </c>
-      <c r="B169" s="94">
+      <c r="B169" s="82">
         <v>32.9</v>
       </c>
-      <c r="C169" s="94">
+      <c r="C169" s="82">
         <v>5.3</v>
       </c>
       <c r="D169" s="3">
@@ -42532,10 +42532,10 @@
       <c r="A170" s="11">
         <v>1990</v>
       </c>
-      <c r="B170" s="94">
+      <c r="B170" s="82">
         <v>27.9</v>
       </c>
-      <c r="C170" s="94">
+      <c r="C170" s="82">
         <v>5.6</v>
       </c>
       <c r="D170" s="3">
@@ -42549,10 +42549,10 @@
       <c r="A171" s="11">
         <v>1991</v>
       </c>
-      <c r="B171" s="94">
+      <c r="B171" s="82">
         <v>27.5</v>
       </c>
-      <c r="C171" s="94">
+      <c r="C171" s="82">
         <v>5.5</v>
       </c>
       <c r="D171" s="3">
@@ -42566,10 +42566,10 @@
       <c r="A172" s="11">
         <v>1992</v>
       </c>
-      <c r="B172" s="94">
+      <c r="B172" s="82">
         <v>27.1</v>
       </c>
-      <c r="C172" s="94">
+      <c r="C172" s="82">
         <v>5.4</v>
       </c>
       <c r="D172" s="3">
@@ -42583,10 +42583,10 @@
       <c r="A173" s="11">
         <v>1993</v>
       </c>
-      <c r="B173" s="94">
+      <c r="B173" s="82">
         <v>26.8</v>
       </c>
-      <c r="C173" s="94">
+      <c r="C173" s="82">
         <v>5.3</v>
       </c>
       <c r="D173" s="3">
@@ -42600,10 +42600,10 @@
       <c r="A174" s="11">
         <v>1994</v>
       </c>
-      <c r="B174" s="94">
+      <c r="B174" s="82">
         <v>26.3</v>
       </c>
-      <c r="C174" s="94">
+      <c r="C174" s="82">
         <v>5.3</v>
       </c>
       <c r="D174" s="3">
@@ -42617,10 +42617,10 @@
       <c r="A175" s="11">
         <v>1995</v>
       </c>
-      <c r="B175" s="94">
+      <c r="B175" s="82">
         <v>25.9</v>
       </c>
-      <c r="C175" s="94">
+      <c r="C175" s="82">
         <v>5.2</v>
       </c>
       <c r="D175" s="3">
@@ -42634,10 +42634,10 @@
       <c r="A176" s="11">
         <v>1996</v>
       </c>
-      <c r="B176" s="94">
+      <c r="B176" s="82">
         <v>25.4</v>
       </c>
-      <c r="C176" s="94">
+      <c r="C176" s="82">
         <v>5.2</v>
       </c>
       <c r="D176" s="3">
@@ -42651,10 +42651,10 @@
       <c r="A177" s="11">
         <v>1997</v>
       </c>
-      <c r="B177" s="94">
+      <c r="B177" s="82">
         <v>24.8</v>
       </c>
-      <c r="C177" s="94">
+      <c r="C177" s="82">
         <v>5.0999999999999996</v>
       </c>
       <c r="D177" s="3">
@@ -42668,10 +42668,10 @@
       <c r="A178" s="11">
         <v>1998</v>
       </c>
-      <c r="B178" s="94">
+      <c r="B178" s="82">
         <v>24.3</v>
       </c>
-      <c r="C178" s="94">
+      <c r="C178" s="82">
         <v>5.0999999999999996</v>
       </c>
       <c r="D178" s="3">
@@ -42685,10 +42685,10 @@
       <c r="A179" s="11">
         <v>1999</v>
       </c>
-      <c r="B179" s="94">
+      <c r="B179" s="82">
         <v>23.9</v>
       </c>
-      <c r="C179" s="94">
+      <c r="C179" s="82">
         <v>5.0999999999999996</v>
       </c>
       <c r="D179" s="3">
@@ -42702,10 +42702,10 @@
       <c r="A180" s="11">
         <v>2000</v>
       </c>
-      <c r="B180" s="94">
+      <c r="B180" s="82">
         <v>23.4</v>
       </c>
-      <c r="C180" s="94">
+      <c r="C180" s="82">
         <v>5.0999999999999996</v>
       </c>
       <c r="D180" s="3">
@@ -42719,10 +42719,10 @@
       <c r="A181" s="11">
         <v>2001</v>
       </c>
-      <c r="B181" s="94">
+      <c r="B181" s="82">
         <v>23</v>
       </c>
-      <c r="C181" s="94">
+      <c r="C181" s="82">
         <v>5.0999999999999996</v>
       </c>
       <c r="D181" s="3">
@@ -42736,10 +42736,10 @@
       <c r="A182" s="11">
         <v>2002</v>
       </c>
-      <c r="B182" s="94">
+      <c r="B182" s="82">
         <v>22.6</v>
       </c>
-      <c r="C182" s="94">
+      <c r="C182" s="82">
         <v>5.0999999999999996</v>
       </c>
       <c r="D182" s="3">
@@ -42753,10 +42753,10 @@
       <c r="A183" s="11">
         <v>2003</v>
       </c>
-      <c r="B183" s="94">
+      <c r="B183" s="82">
         <v>22.2</v>
       </c>
-      <c r="C183" s="94">
+      <c r="C183" s="82">
         <v>5.0999999999999996</v>
       </c>
       <c r="D183" s="3">
@@ -42770,10 +42770,10 @@
       <c r="A184" s="11">
         <v>2004</v>
       </c>
-      <c r="B184" s="94">
+      <c r="B184" s="82">
         <v>21.8</v>
       </c>
-      <c r="C184" s="94">
+      <c r="C184" s="82">
         <v>5.2</v>
       </c>
       <c r="D184" s="3">
@@ -42787,10 +42787,10 @@
       <c r="A185" s="11">
         <v>2005</v>
       </c>
-      <c r="B185" s="94">
+      <c r="B185" s="82">
         <v>21.5</v>
       </c>
-      <c r="C185" s="94">
+      <c r="C185" s="82">
         <v>5.2</v>
       </c>
       <c r="D185" s="3">
@@ -42804,10 +42804,10 @@
       <c r="A186" s="11">
         <v>2006</v>
       </c>
-      <c r="B186" s="94">
+      <c r="B186" s="82">
         <v>21.1</v>
       </c>
-      <c r="C186" s="94">
+      <c r="C186" s="82">
         <v>5.3</v>
       </c>
       <c r="D186" s="3">
@@ -42821,10 +42821,10 @@
       <c r="A187" s="11">
         <v>2007</v>
       </c>
-      <c r="B187" s="94">
+      <c r="B187" s="82">
         <v>20.8</v>
       </c>
-      <c r="C187" s="94">
+      <c r="C187" s="82">
         <v>5.3</v>
       </c>
       <c r="D187" s="3">
@@ -42838,10 +42838,10 @@
       <c r="A188" s="11">
         <v>2008</v>
       </c>
-      <c r="B188" s="94">
+      <c r="B188" s="82">
         <v>20.399999999999999</v>
       </c>
-      <c r="C188" s="94">
+      <c r="C188" s="82">
         <v>5.4</v>
       </c>
       <c r="D188" s="3">
@@ -42855,10 +42855,10 @@
       <c r="A189" s="11">
         <v>2009</v>
       </c>
-      <c r="B189" s="94">
+      <c r="B189" s="82">
         <v>20.100000000000001</v>
       </c>
-      <c r="C189" s="94">
+      <c r="C189" s="82">
         <v>5.5</v>
       </c>
       <c r="D189" s="3">
@@ -42872,10 +42872,10 @@
       <c r="A190" s="11">
         <v>2010</v>
       </c>
-      <c r="B190" s="94">
+      <c r="B190" s="82">
         <v>19.7</v>
       </c>
-      <c r="C190" s="94">
+      <c r="C190" s="82">
         <v>5.6</v>
       </c>
       <c r="D190" s="3">
@@ -42889,10 +42889,10 @@
       <c r="A191" s="11">
         <v>2011</v>
       </c>
-      <c r="B191" s="94">
+      <c r="B191" s="82">
         <v>19.399999999999999</v>
       </c>
-      <c r="C191" s="94">
+      <c r="C191" s="82">
         <v>5.6</v>
       </c>
       <c r="D191" s="3">
@@ -42906,10 +42906,10 @@
       <c r="A192" s="11">
         <v>2012</v>
       </c>
-      <c r="B192" s="94">
+      <c r="B192" s="82">
         <v>19.2</v>
       </c>
-      <c r="C192" s="94">
+      <c r="C192" s="82">
         <v>5.7</v>
       </c>
       <c r="D192" s="3">
@@ -42923,10 +42923,10 @@
       <c r="A193" s="11">
         <v>2013</v>
       </c>
-      <c r="B193" s="94">
+      <c r="B193" s="82">
         <v>19</v>
       </c>
-      <c r="C193" s="94">
+      <c r="C193" s="82">
         <v>5.7</v>
       </c>
       <c r="D193" s="3">
@@ -42940,10 +42940,10 @@
       <c r="A194" s="11">
         <v>2014</v>
       </c>
-      <c r="B194" s="94">
+      <c r="B194" s="82">
         <v>18.7</v>
       </c>
-      <c r="C194" s="94">
+      <c r="C194" s="82">
         <v>5.7</v>
       </c>
       <c r="D194" s="3">
@@ -42957,10 +42957,10 @@
       <c r="A195" s="11">
         <v>2015</v>
       </c>
-      <c r="B195" s="95">
+      <c r="B195" s="83">
         <v>18.5</v>
       </c>
-      <c r="C195" s="95">
+      <c r="C195" s="83">
         <v>5.8</v>
       </c>
       <c r="D195" s="3">
@@ -42974,10 +42974,10 @@
       <c r="A196" s="11">
         <v>2016</v>
       </c>
-      <c r="B196" s="95">
+      <c r="B196" s="83">
         <v>18.100000000000001</v>
       </c>
-      <c r="C196" s="95">
+      <c r="C196" s="83">
         <v>5.8</v>
       </c>
       <c r="D196" s="3">
@@ -42991,10 +42991,10 @@
       <c r="A197" s="11">
         <v>2017</v>
       </c>
-      <c r="B197" s="95">
+      <c r="B197" s="83">
         <v>17.8</v>
       </c>
-      <c r="C197" s="95">
+      <c r="C197" s="83">
         <v>5.9</v>
       </c>
       <c r="D197" s="3">
@@ -43008,10 +43008,10 @@
       <c r="A198" s="11">
         <v>2018</v>
       </c>
-      <c r="B198" s="95">
+      <c r="B198" s="83">
         <v>17.5</v>
       </c>
-      <c r="C198" s="95">
+      <c r="C198" s="83">
         <v>6</v>
       </c>
       <c r="D198" s="3">
@@ -43025,10 +43025,10 @@
       <c r="A199" s="11">
         <v>2019</v>
       </c>
-      <c r="B199" s="95">
+      <c r="B199" s="83">
         <v>17.100000000000001</v>
       </c>
-      <c r="C199" s="95">
+      <c r="C199" s="83">
         <v>6</v>
       </c>
       <c r="D199" s="3">
@@ -43042,10 +43042,10 @@
       <c r="A200" s="11">
         <v>2020</v>
       </c>
-      <c r="B200" s="95">
+      <c r="B200" s="83">
         <v>16.8</v>
       </c>
-      <c r="C200" s="95">
+      <c r="C200" s="83">
         <v>6.1</v>
       </c>
       <c r="D200" s="3">
@@ -43059,10 +43059,10 @@
       <c r="A201" s="11">
         <v>2021</v>
       </c>
-      <c r="B201" s="94">
+      <c r="B201" s="82">
         <v>16.3</v>
       </c>
-      <c r="C201" s="94">
+      <c r="C201" s="82">
         <v>9.5</v>
       </c>
       <c r="D201" s="3">
@@ -43076,10 +43076,10 @@
       <c r="A202" s="11">
         <v>2022</v>
       </c>
-      <c r="B202" s="94">
+      <c r="B202" s="82">
         <v>16.100000000000001</v>
       </c>
-      <c r="C202" s="94">
+      <c r="C202" s="82">
         <v>6.1</v>
       </c>
       <c r="D202" s="3">
@@ -43093,10 +43093,10 @@
       <c r="A203" s="11">
         <v>2023</v>
       </c>
-      <c r="B203" s="94">
+      <c r="B203" s="82">
         <v>15.8</v>
       </c>
-      <c r="C203" s="94">
+      <c r="C203" s="82">
         <v>6.1</v>
       </c>
       <c r="D203" s="3">

--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBC62F3-557F-466E-8DE3-26C9F45408BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F035C17-7CD5-4DD3-B1C5-04F29AF53427}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="4" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="6" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="9" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="185">
   <si>
     <t>год</t>
   </si>
@@ -643,6 +643,9 @@
   </si>
   <si>
     <t>MX-смертность</t>
+  </si>
+  <si>
+    <t>на начало года</t>
   </si>
 </sst>
 </file>
@@ -8332,6 +8335,11 @@
       <c r="G4" s="88"/>
       <c r="H4" s="88"/>
       <c r="I4" s="88"/>
+      <c r="M4" s="88" t="s">
+        <v>184</v>
+      </c>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
       <c r="Q4" s="86" t="s">
         <v>168</v>
       </c>
@@ -15554,7 +15562,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="D137:F137"/>
     <mergeCell ref="B3:C4"/>
     <mergeCell ref="Q4:R4"/>
@@ -15562,6 +15570,7 @@
     <mergeCell ref="D3:J3"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:I4"/>
+    <mergeCell ref="M4:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F035C17-7CD5-4DD3-B1C5-04F29AF53427}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3883571C-4892-466E-BD59-345D9D5CEEBC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="6" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
+    <workbookView xWindow="5850" yWindow="2085" windowWidth="23985" windowHeight="21000" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="9" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="220">
   <si>
     <t>год</t>
   </si>
@@ -589,9 +589,6 @@
     <t>ожидаемые</t>
   </si>
   <si>
-    <t>Фактическая рождаемость и смертность:</t>
-  </si>
-  <si>
     <t>1959-2023 по Росстату</t>
   </si>
   <si>
@@ -646,6 +643,114 @@
   </si>
   <si>
     <t>на начало года</t>
+  </si>
+  <si>
+    <t>Страницы RSFSR, NR, MR, BR проводят исчисление для территорий РСФСР-1991 (без Тувы), Новороссии, Малороссии и Белоруссии.</t>
+  </si>
+  <si>
+    <t>Страница USSR сводит их итоги в исчисление для территории СССР в текущих границах на даты переписей населения.</t>
+  </si>
+  <si>
+    <t>Страница USSR-Simplifed даёт сокращённый вариант итогов со страницы USSR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Листы NR, MR и BR структурно повторяют расчёт для территории РСФСР-1991. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Их отличие состоит только в величине исходного населения на январь 1917 года, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">в базовых значениях рождаемости и смертности, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">а также в положении той точки модельных кривых RB/RD, которая принимается за опорную для соответствующей территории. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тем самым сохраняется единый принцип расчёта, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">а территориальные различия учитываются не через изменение самой модели, </t>
+  </si>
+  <si>
+    <t>а через изменение её начальных условий и фазового сдвига по траектории демографического перехода.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Главная таблица на странице USSR представляет собой сводный расчёт ожидаемой численности населения территории СССР по датам переписей и для нескольких последующих контрольных дат. </t>
+  </si>
+  <si>
+    <t>В отличие от погодовых таблиц для РСФСР-1991, Новороссии, Малороссии и Белоруссии, она не производит самостоятельного год за годом исчисления</t>
+  </si>
+  <si>
+    <t>демографической динамики, а сводит в единую систему уже полученные для этих четырёх территорий ретропрогнозные величины. Для каждой даты переписи в</t>
+  </si>
+  <si>
+    <t>таблицу вносятся ожидаемые величины населения РСФСР-1991, Новороссии, Малороссии и Белоруссии, полученные по отдельным расчётам, после чего к ним</t>
+  </si>
+  <si>
+    <t>добавляется фактическая численность тех частей СССР, для которых контрфактическое моделирование в настоящей работе не производится. Тем самым образуется</t>
+  </si>
+  <si>
+    <t>составная ожидаемая численность населения СССР, но лишь после специальной территориальной корректировки: для переписей 1926-1939 гг. из суммы вычитается</t>
+  </si>
+  <si>
+    <t xml:space="preserve">расчётные таксоны к реальным границам СССР на дату данной переписи и делает итоговое сопоставление территориально корректным. </t>
+  </si>
+  <si>
+    <t>население тех частей Новороссии, Малороссии и Белоруссии, которые на соответствующий момент ещё не входили в состав СССР. Эта операция приводит</t>
+  </si>
+  <si>
+    <t>Иными словами, ожидаемая численность населения СССР в таблице определяется как сумма контрфактических величин для четырёх моделируемых восточнославянских</t>
+  </si>
+  <si>
+    <t>территорий и фактической численности прочих республик и областей, входивших в состав СССР на соответствующую дату, за вычетом тех частей моделируемых</t>
+  </si>
+  <si>
+    <t>территорий, которые тогда ещё находились вне его государственных границ. Для переписей 1959-1989 гг. к этой сумме уже добавляется фактическое население</t>
+  </si>
+  <si>
+    <t>бывших подавстрийских земель, включённых в СССР в 1939-1945 гг., а также Тувы. Полученная итоговая величина сопоставляется с фактической численностью</t>
+  </si>
+  <si>
+    <t>населения СССР в тех же границах, после чего исчисляются абсолютная величина демографического дефицита и его относительный размер. Тем самым таблица USSR</t>
+  </si>
+  <si>
+    <t>служит не самостоятельной моделью для всего СССР как однородного целого, а инструментом территориально корректного сведения частичных ретропрогнозов в</t>
+  </si>
+  <si>
+    <t>единую консервативную оценку населения СССР в его текущих на каждую дату границах.</t>
+  </si>
+  <si>
+    <t>Страница USSR сводит в одну таблицу контрфактические расчёты для РСФСР-1991, Новороссии, Малороссии и Белоруссии, добавляя к ним фактическую численность</t>
+  </si>
+  <si>
+    <t>остальных частей СССР по переписям. Для ранних переписей из суммы вычитается население тех частей Новороссии, Малороссии и Белоруссии, которые на</t>
+  </si>
+  <si>
+    <t>соответствующий момент ещё не входили в состав СССР; для поздних переписей, напротив, добавляется фактическое население территорий, включённых в СССР в</t>
+  </si>
+  <si>
+    <t>1939-1945 гг., а также Тувы. В результате таблица даёт ожидаемую численность населения СССР в его реальных на каждую дату границах и позволяет напрямую</t>
+  </si>
+  <si>
+    <t>сопоставить её с фактической переписной численностью, исчислив абсолютные и относительные размеры демографического дефицита.</t>
+  </si>
+  <si>
+    <t>Страница USSR-Simplified даёт компактное представление тех же итогов, что и страница USSR, но без промежуточных сводных колонок. Она служит сокращённой</t>
+  </si>
+  <si>
+    <t>таблицей результатов, в которой для каждой даты непосредственно сопоставляются ожидаемая и фактическая численность населения СССР в соответствующих</t>
+  </si>
+  <si>
+    <t>границах, а также исчисленные на этой основе абсолютные и относительные размеры демографического дефицита.</t>
+  </si>
+  <si>
+    <t>Ретропрогноз динамики демографического перехода для населения территории РСФСР-1991 (без Тувы),</t>
+  </si>
+  <si>
+    <t>и территорий Новороссии, Малороссии, Белоруссии и СССР</t>
+  </si>
+  <si>
+    <t>Фактическая рождаемость и смертность в РСФСР (источники):</t>
   </si>
 </sst>
 </file>
@@ -8257,31 +8362,207 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE2E9CE-51C0-4757-B29D-171216549950}">
-  <dimension ref="A4:B7"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="37" t="s">
+        <v>218</v>
+      </c>
+    </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>171</v>
+      <c r="A4" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>167</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8336,12 +8617,12 @@
       <c r="H4" s="88"/>
       <c r="I4" s="88"/>
       <c r="M4" s="88" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N4" s="88"/>
       <c r="O4" s="88"/>
       <c r="Q4" s="86" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R4" s="86"/>
       <c r="S4" s="87" t="s">
@@ -9820,7 +10101,7 @@
         <v>2.0359915872036938</v>
       </c>
       <c r="V33" s="74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W33" s="74"/>
       <c r="X33" s="74"/>
@@ -10853,7 +11134,7 @@
         <v>0.4433261442607237</v>
       </c>
       <c r="V50" s="74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W50" s="74"/>
       <c r="X50" s="74"/>
@@ -32140,7 +32421,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -39775,7 +40056,7 @@
   <sheetData>
     <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -39783,16 +40064,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="71" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="D4" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="71" t="s">
+      <c r="E4" s="71" t="s">
         <v>176</v>
-      </c>
-      <c r="E4" s="71" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -41446,7 +41727,7 @@
     </row>
     <row r="104" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A104" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -41454,16 +41735,16 @@
         <v>0</v>
       </c>
       <c r="B106" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="C106" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="C106" s="76" t="s">
-        <v>183</v>
-      </c>
       <c r="D106" s="76" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E106" s="76" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">

--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3883571C-4892-466E-BD59-345D9D5CEEBC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E824598-23C9-48A5-A613-973777022993}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5850" yWindow="2085" windowWidth="23985" windowHeight="21000" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="9" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="221">
   <si>
     <t>год</t>
   </si>
@@ -752,6 +752,9 @@
   <si>
     <t>Фактическая рождаемость и смертность в РСФСР (источники):</t>
   </si>
+  <si>
+    <t>!!! Белоруссия без Смоленской</t>
+  </si>
 </sst>
 </file>
 
@@ -762,7 +765,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,6 +821,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -998,7 +1009,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1223,6 +1234,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -8362,7 +8374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE2E9CE-51C0-4757-B29D-171216549950}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.35">
@@ -8558,6 +8570,11 @@
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A51" s="96" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/demographic-transition-retro-forecast.xlsx
+++ b/demographic-transition-retro-forecast.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E824598-23C9-48A5-A613-973777022993}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B2AC3D-DB9D-498D-B9E7-75124105D7B1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{573FC42F-0BD4-4412-A5CF-D809ABCC1B4D}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="222">
   <si>
     <t>год</t>
   </si>
@@ -755,6 +755,9 @@
   <si>
     <t>!!! Белоруссия без Смоленской</t>
   </si>
+  <si>
+    <t>!!! Также Вайнштейн стр. 455</t>
+  </si>
 </sst>
 </file>
 
@@ -765,7 +768,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -828,6 +831,14 @@
     <font>
       <b/>
       <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1009,7 +1020,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1198,6 +1209,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1234,7 +1246,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -8374,7 +8386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE2E9CE-51C0-4757-B29D-171216549950}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.35">
@@ -8573,8 +8585,13 @@
       </c>
     </row>
     <row r="51" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A51" s="96" t="s">
+      <c r="A51" s="84" t="s">
         <v>220</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="97" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -8606,46 +8623,46 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84" t="s">
+      <c r="C3" s="85"/>
+      <c r="D3" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="88" t="s">
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88" t="s">
+      <c r="E4" s="89"/>
+      <c r="F4" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="M4" s="88" t="s">
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="M4" s="89" t="s">
         <v>183</v>
       </c>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="Q4" s="86" t="s">
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="Q4" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="R4" s="86"/>
-      <c r="S4" s="87" t="s">
+      <c r="R4" s="87"/>
+      <c r="S4" s="88" t="s">
         <v>164</v>
       </c>
-      <c r="T4" s="87"/>
+      <c r="T4" s="88"/>
     </row>
     <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -15636,11 +15653,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="84" t="s">
+      <c r="D137" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="84"/>
-      <c r="F137" s="84"/>
+      <c r="E137" s="85"/>
+      <c r="F137" s="85"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -15896,16 +15913,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="84" t="s">
+      <c r="D4" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84" t="s">
+      <c r="E4" s="85"/>
+      <c r="F4" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -20473,11 +20490,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="84" t="s">
+      <c r="D137" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="84"/>
-      <c r="F137" s="84"/>
+      <c r="E137" s="85"/>
+      <c r="F137" s="85"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -20728,16 +20745,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="84" t="s">
+      <c r="D4" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84" t="s">
+      <c r="E4" s="85"/>
+      <c r="F4" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -25314,11 +25331,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="84" t="s">
+      <c r="D137" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="84"/>
-      <c r="F137" s="84"/>
+      <c r="E137" s="85"/>
+      <c r="F137" s="85"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -25568,16 +25585,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D4" s="84" t="s">
+      <c r="D4" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84" t="s">
+      <c r="E4" s="85"/>
+      <c r="F4" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -30150,11 +30167,11 @@
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="84" t="s">
+      <c r="D137" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="84"/>
-      <c r="F137" s="84"/>
+      <c r="E137" s="85"/>
+      <c r="F137" s="85"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
@@ -30448,15 +30465,15 @@
       <c r="P5" s="63"/>
       <c r="Q5" s="63"/>
       <c r="R5" s="63"/>
-      <c r="S5" s="89" t="s">
+      <c r="S5" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="90"/>
-      <c r="U5" s="90"/>
-      <c r="V5" s="89" t="s">
+      <c r="T5" s="91"/>
+      <c r="U5" s="91"/>
+      <c r="V5" s="90" t="s">
         <v>156</v>
       </c>
-      <c r="W5" s="90"/>
+      <c r="W5" s="91"/>
       <c r="X5" s="64"/>
       <c r="Y5" s="63"/>
     </row>
@@ -31839,21 +31856,21 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88" t="s">
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89" t="s">
         <v>137</v>
       </c>
-      <c r="I5" s="88"/>
-      <c r="J5" s="85" t="s">
+      <c r="I5" s="89"/>
+      <c r="J5" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="K5" s="84"/>
+      <c r="K5" s="85"/>
     </row>
     <row r="6" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
@@ -32477,20 +32494,20 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="92" t="s">
+      <c r="A11" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91" t="s">
+      <c r="C11" s="92"/>
+      <c r="D11" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="E11" s="91"/>
+      <c r="E11" s="92"/>
     </row>
     <row r="12" spans="1:20" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
+      <c r="A12" s="94"/>
       <c r="B12" s="34" t="s">
         <v>98</v>
       </c>
@@ -32512,10 +32529,10 @@
       <c r="J12" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="94" t="s">
+      <c r="K12" s="95" t="s">
         <v>152</v>
       </c>
-      <c r="L12" s="95"/>
+      <c r="L12" s="96"/>
       <c r="M12" s="51" t="s">
         <v>153</v>
       </c>
@@ -32528,10 +32545,10 @@
       <c r="Q12" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="R12" s="94" t="s">
+      <c r="R12" s="95" t="s">
         <v>152</v>
       </c>
-      <c r="S12" s="95"/>
+      <c r="S12" s="96"/>
       <c r="T12" s="51" t="s">
         <v>153</v>
       </c>
